--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>To veier: rutene `POST` og `PATCH /api/projects`, og databasefunksjonen `koe_register_project`, som drift kaller gjennom `scripts/catenda_admin.py`. Etter vedtaket i B-02 punkt 4 skal bare drift registrere prosjekter; det er ikke bygget (F1). En migrasjon legger inn prosjektet `oslobygg` som startrad.</t>
+          <t>Registreres av drift gjennom databasefunksjonen `koe_register_project` (`scripts/catenda_admin.py`). `POST /api/projects` svarer 403 utenfor utviklingsmodus. En prosjektadministrator kan endre navn, beskrivelse og innstillinger og deaktivere prosjektet (`PATCH`). At runtime-rollen heller ikke skal kunne kalle funksjonen, gjelder databaserettighetene og hører til F1 (B-02 punkt 4). En migrasjon legger inn prosjektet `oslobygg`, og det er i dag basens eneste prosjekt (DM-03).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>backend/routes/project_routes.py; databasefunksjonen koe_register_project</t>
+          <t>databasefunksjonen koe_register_project; backend/routes/project_routes.py (PATCH; POST bare i utviklingsmodus); migrasjonen 20260911073600_projects.sql (startraden)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>MS-10, MS-12</t>
+          <t>MS-10, MS-12, DM-03</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen. L 29.09: rutene, migrasjonene og `scripts/catenda_admin.py`.</t>
+          <t>K 29.09: kolonnene og fremmednøklene i testbasen, startraden i testbasen og en telling i prosjektet. L 29.09: rutene, med vakten mot `POST` utenfor utviklingsmodus, migrasjonene og `scripts/catenda_admin.py`.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -437,11 +437,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,27 +493,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Kan bygges opp igjen</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Personopplysninger</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Skrives av</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Funn i hovedplanen</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Belegg</t>
         </is>
       </c>
     </row>
@@ -574,27 +550,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>nei. Journalen er kilden alt annet regnes fra.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
           <t>`actorid` peker på en bruker. Fritekst i `data` og `comment` kan inneholde personopplysninger. Vurderingen hører til DPIA-en.</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>backend/routes/event_routes.py; backend/services/sak_creation_service.py; backend/services/forsering_service.py; backend/services/endringsordre_service.py; backend/services/approval_service.py; backend/services/catenda_webhook_service.py (via sak_creation_service)</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>MS-01, MS-02, MS-03, AR-02</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen og prosjektet, og skrankene (også CASCADE) i testbasen. L 29.09: kallerne av `append`/`append_batch` og `create_sak`.</t>
         </is>
       </c>
     </row>
@@ -651,27 +607,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
           <t>`aktor_id` peker på forfatteren. `tekst` og `kommentar` er fritekst.</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>backend/routes/event_routes.py; backend/repositories/postgres/notat.py</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>MS-05</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøkkelen i testbasen. L 29.09: sletting i lageret. Skjermingen: AGENTS.md og `lib/auth/event_visibility.py`, ikke kontrollert på nytt 29.09.</t>
         </is>
       </c>
     </row>
@@ -728,27 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>delvis. `cached_*` og `last_event_at` kan regnes ut av hendelsene. Om registerkolonnene også kan det, er ikke kontrollert.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
           <t>`created_by` identifiserer den som opprettet saken (tre verdiformer, MG-04).</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/sak_creation_service.py; backend/services/endringsordre_service.py; backend/routes/event_routes.py (update_cache); backend/routes/forsering_routes.py (update_cache); backend/routes/approval_routes.py (update_cache)</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>MS-06, MS-07, DA-14, MG-04, DM-01</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen og prosjektet, og kolonnekommentarene (DM-01). L 29.09: kallerne av `create` og `update_cache`.</t>
         </is>
       </c>
     </row>
@@ -805,27 +721,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ikke kontrollert. Koblingene finnes trolig også som hendelser (`FORSERING_KOE_*`, `EO_KOE_*`), men det er ikke sjekket at de to alltid er like.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/forsering_service.py; backend/services/endringsordre_service.py</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>DA-13, MS-08, DB-04</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fraværet av fremmednøkler i testbasen. L 29.09: kallerne av `add_relation`, `add_relations_batch` og `remove_relation`.</t>
         </is>
       </c>
     </row>
@@ -882,27 +778,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
           <t>`created_by` identifiserer den som opprettet prosjektet.</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_register_project; backend/routes/project_routes.py (PATCH; POST bare i utviklingsmodus); migrasjonen 20260911073600_projects.sql (startraden)</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>MS-10, MS-12, DM-03</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen, startraden i testbasen og en telling i prosjektet. L 29.09: rutene, med vakten mot `POST` utenfor utviklingsmodus, migrasjonene og `scripts/catenda_admin.py`.</t>
         </is>
       </c>
     </row>
@@ -959,27 +835,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>ikke relevant; tabellen skal fjernes.</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
           <t>`user_email`, `display_name`, `external_id`.</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>triggerfunksjonen auto_create_project_membership</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>DA-10, MS-15, AR-07</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og triggeren i testbasen. D 20.09: ingen leser (databaseauditen).</t>
         </is>
       </c>
     </row>
@@ -1036,27 +892,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>nei. `id` må være stabil, fordi journalen viser til den.</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
           <t>`email` og `name`.</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_resolve_identity</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>MG-02</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen. L 29.09: funksjonen i migrasjonene og kallerne i `auth_service`, `catenda_webhook_service` og `koe_reconcile_memberships`.</t>
         </is>
       </c>
     </row>
@@ -1113,27 +949,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
           <t>`subject` er en ekstern identifikator for en person.</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_resolve_identity</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>DA-07, MG-02</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøkkelen i testbasen. L 29.09: funksjonen i migrasjonene; søket etter tabellnavnet i Python-koden gir bare to docstringer.</t>
         </is>
       </c>
     </row>
@@ -1190,23 +1006,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>nei, men tapet betyr bare at brukerne må logge inn igjen.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
           <t>Knyttet til en bruker gjennom `user_id`.</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>backend/routes/auth_routes.py; backend/scripts/sync_catenda_memberships.py</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen. L 29.09: rutene og skriptet.</t>
         </is>
       </c>
     </row>
@@ -1263,23 +1063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>nei, men radene er kortlevde.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>backend/routes/auth_routes.py</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen. L 29.09: rutene.</t>
         </is>
       </c>
     </row>
@@ -1336,27 +1120,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>delvis. Fra Catenda, bortsett fra `viewer_override`.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
           <t>`user_email`, `display_name` og `catenda_subject`.</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_reconcile_memberships; backend/repositories/auth_repository.py (deactivate_user_projects, viewer_override); backend/routes/membership_routes.py</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>DB-05</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen. L 29.09: funksjonen i migrasjonene og kallerne i `auth_service` og `membership_routes`.</t>
         </is>
       </c>
     </row>
@@ -1413,23 +1177,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>ja, ved neste synkronisering.</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_reconcile_memberships</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen. L 29.09: funksjonen i migrasjonene.</t>
         </is>
       </c>
     </row>
@@ -1486,27 +1234,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_register_project</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>MS-12</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen. L 29.09: funksjonen og skriptet.</t>
         </is>
       </c>
     </row>
@@ -1563,27 +1291,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_register_project</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>MS-12</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøkkelen i testbasen. L 29.09: funksjonen. Bruken ved webhook er ikke kontrollert 29.09.</t>
         </is>
       </c>
     </row>
@@ -1640,23 +1348,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>nei. Hvilket team som er hvilken side, er et valg drift gjør.</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>databasefunksjonen koe_set_contract_teams; databasefunksjonen koe_register_project</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøkkelen i testbasen. L 29.09: funksjonene og skriptet.</t>
         </is>
       </c>
     </row>
@@ -1713,27 +1405,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>ja, i prinsippet fra Catenda.</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Ingen funnet</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>DM-02, DA-15</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: lesere og skrivere i repoet og Git-historikken. K 29.09: ingen funksjon, trigger eller Edge Function i prosjektet nevner tabellen, og statistikken viser 0 rader.</t>
         </is>
       </c>
     </row>
@@ -1790,27 +1462,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
           <t>`linked_by` identifiserer den som koblet (e-post, lest i ruta).</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>backend/routes/bim_link_routes.py</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>DA-15, MS-13, MS-14</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøkkelen i testbasen. L 29.09: rutene.</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1519,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>ikke relevant; tabellen skal fjernes.</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
           <t>`email`.</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Ingen funnet</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>DA-09, MS-15</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene i testbasen. D 20.09: ingen lesere. L 29.09: `MagicLinkManager`.</t>
         </is>
       </c>
     </row>
@@ -1944,27 +1576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>ikke relevant; tabellen skal fjernes.</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
           <t>`display_name`, `department` og koblingen til en bruker.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Ingen funnet</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>DA-08, MS-15</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>K 29.09: kolonnene og fremmednøklene i testbasen. D 20.09: ingen kallere.</t>
         </is>
       </c>
     </row>
@@ -2021,27 +1633,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
           <t>`oppdatert_av` og fritekst i `innhold`.</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/utkast_registry.py</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>AR-03</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og rutene.</t>
         </is>
       </c>
     </row>
@@ -2098,27 +1690,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
           <t>Godkjennere og saksbehandlere i JSON-dokumentet; ikke kontrollert i detalj.</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/approval_service.py</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>AR-03, MG-05</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og `ApprovalService`.</t>
         </is>
       </c>
     </row>
@@ -2175,27 +1747,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/approval_service.py</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>AR-03</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og `publish`/`deliver`.</t>
         </is>
       </c>
     </row>
@@ -2252,27 +1804,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
           <t>Godkjennere i JSON-dokumentet; ikke kontrollert i detalj.</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/eo_approval_service.py</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>AR-03</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og `EOApprovalService`.</t>
         </is>
       </c>
     </row>
@@ -2329,27 +1861,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
           <t>Filinnholdet kan inneholde personopplysninger; ikke kontrollert.</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/vedlegg_registry.py</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>AR-03, MS-11</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og modulheaderen.</t>
         </is>
       </c>
     </row>
@@ -2406,27 +1918,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
           <t>Ingen kjente.</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>backend/services/catenda_delivery_status.py</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>AR-03</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: tabelldefinisjonen og kallerne i `event_routes`.</t>
         </is>
       </c>
     </row>
@@ -2441,14 +1933,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2472,11 +1963,6 @@
           <t>Hvor fra appen lagres</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Belegg</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2499,11 +1985,6 @@
           <t>Forserings- og endringsordretjenesten (`create_topic`, `create_topic_relations`), webhook-tjenesten, synkroniseringstjenesten og hendelsesrutene (`create_comment`).</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: kallene i tjenestene og rutene. Hvilke hendelser som gir kommentar, er ikke kontrollert (fase 1c).</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2526,11 +2007,6 @@
           <t>Hendelses- og vedleggsrutene og webhook-tjenesten.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: kallene til `upload_document` og `create_document_reference`. Mappestrukturen og navngivingen er ikke kontrollert (B-03).</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2551,11 +2027,6 @@
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>`lib/security/webhook_security.py`, ved hver webhook.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>L 29.09: modulen. Om Redis brukes i et utrullet miljø, er ikke kontrollert.</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2676,60 +2147,24 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Belegg: K</t>
+          <t>Ikke kontrollert</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>kjørt og observert (med dato)</t>
+          <t>Står der påstanden ikke er kontrollert. Registeret bygges i runder.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Belegg: L</t>
+          <t>Detaljer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>lest i kode eller migrasjonsfil (med dato)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Belegg: D</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>kontrollert i databasekatalogen tidligere (med dato)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Belegg: H</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>historisk dokumentert i en audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Ikke kontrollert</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Står der påstanden ikke er kontrollert. Registeret bygges i runder.</t>
+          <t>Hvem som skriver hver tabell, belegg og funn står i docs/datamodell/tabeller.md i repoet.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3317,7 +3317,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`.</t>
+          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`. Sakstypen settes også når hendelsen kommer i en KOE-sak, og ingen regel stopper det (DM-07).</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3193,7 +3193,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Første hendelse i en sak: tittel, sakstype og kobling til Catenda. Feltene ligger på toppnivå i modellen og i `data` i journalen.</t>
+          <t>Første hendelse i en sak: tittel, sakstype og kobling til Catenda. Feltene ligger på toppnivå i modellen og i `data` i journalen. Sender klienten dem i `data`, som skjemaet for ny sak gjør, lagres `data` slik klienten sendte den, også med nøkler modellen ikke kjenner (DM-06).</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Tabeller" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Utenfor databasene" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hendelsestyper" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Hendelsesfelt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Om registeret" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Relasjoner" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dataflyt" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Utenfor databasene" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Hendelsestyper" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hendelsesfelt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Om registeret" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,12 +529,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Delvis. En ny topic i Catenda oppretter en sak med første hendelse via webhook. Ellers kommer innholdet fra brukerne i appen.</t>
+          <t>Delvis. En ny topic i Catenda oppretter en sak med første hendelse via webhook. Ellers kommer innholdet fra brukerne i appen. Dataflyt: fra Catenda i C01, C05; til Catenda i C06, C07, C14, C15 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>`sak_id` → `sak_metadata.sak_id` (fremmednøkkel, ON DELETE CASCADE). Én rad per sak og versjonsnummer (`UNIQUE (sak_id, versjon)`), og `event_id` er unik. `actorid` er `app_users.id`, uten fremmednøkkel. `referstoid` viser etter navnet til en annen hendelse, uten fremmednøkkel; bruken er ikke kontrollert.</t>
+          <t>Nøkler: primærnøkkel (id); unik (event_id); unik (sak_id, versjon). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); actorid → app_users.id (uten fremmednøkkel); actorteam → catenda_contract_teams.team_id (uten fremmednøkkel); referstoid → hendelse.event_id (uten fremmednøkkel); data → vedlegg_ids[] → vedlegg.vedlegg_id (uten fremmednøkkel). Vises til fra: approvals.body → items[].claimId (uten fremmednøkkel); approvals.body → packages[].eventIds[] (uten fremmednøkkel); catenda_delivery_status.event_id (uten fremmednøkkel); notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -584,12 +586,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>`sak_id` → `sak_metadata.sak_id` (fremmednøkkel). `aktor_id` er `app_users.id`, `aktor_team_id` er Catenda-team-ID, begge uten fremmednøkkel. `refererer_til_event_id` kan vise til en hendelse, uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); aktor_id → app_users.id (uten fremmednøkkel); aktor_team_id → catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -641,12 +643,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_topic_id`, `catenda_board_id` og `catenda_project_id` er ID-er fra Catenda.</t>
+          <t>Delvis. `catenda_topic_id`, `catenda_board_id` og `catenda_project_id` er ID-er fra Catenda. Dataflyt: fra Catenda i C01, C15; til Catenda i C01, C15 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Primærnøkkel `sak_id`. `hendelse`, `notat`, `sak_bim_links` og `magic_links` har fremmednøkkel hit. `sak_relations` viser hit uten fremmednøkkel. `prosjekt_id` viser til `projects.id` uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); created_by → app_users.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel); catenda_board_id → catenda_topic_board_configs.topic_board_id (uten fremmednøkkel). Vises til fra: approval_outbox.case_id (uten fremmednøkkel); approvals.case_id (uten fremmednøkkel); catenda_delivery_status.case_id (uten fremmednøkkel); eo_approvals.body → packages[].sakId (uten fremmednøkkel); eo_approvals.body → packages[].request.koe_sak_ids[] (uten fremmednøkkel); hendelse.sak_id (fremmednøkkel, ON DELETE CASCADE); magic_links.sak_id (fremmednøkkel, ON DELETE CASCADE); notat.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_bim_links.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_relations.source_sak_id (uten fremmednøkkel); sak_relations.target_sak_id (uten fremmednøkkel); utkast.case_id (uten fremmednøkkel); vedlegg.case_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -688,7 +690,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Når KOE-er legges til eller fjernes fra en forsering eller en endringsordre (forsering- og endringsordretjenesten).</t>
+          <t>Når en forsering opprettes gjennom `/api/forsering/opprett`, og når en endringsordre opprettes eller KOE-er legges til eller fjernes fra den (forsering- og endringsordretjenesten). Å legge til eller fjerne KOE-er fra en forsering endrer bare Catenda, ikke denne tabellen (dataflyten, C11). Skriptet `scripts/backfill_relations.py` kaller lageret uten autorisert prosjekt, og over PostgreSQL avvises da hver skriving (`krev_autorisert_prosjekt`).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,12 +700,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: fra Catenda i C10 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>`source_sak_id` og `target_sak_id` viser til `sak_metadata.sak_id`, uten fremmednøkler (DB-04, B-01). `prosjekt_id` settes av serveren.</t>
+          <t>Nøkler: primærnøkkel (id); unik (source_sak_id, target_sak_id, relation_type). Viser til: source_sak_id → sak_metadata.sak_id (uten fremmednøkkel); target_sak_id → sak_metadata.sak_id (uten fremmednøkkel); prosjekt_id → projects.id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -745,7 +747,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Registreres av drift gjennom databasefunksjonen `koe_register_project` (`scripts/catenda_admin.py`). `POST /api/projects` svarer 403 utenfor utviklingsmodus. En prosjektadministrator kan endre navn, beskrivelse og innstillinger og deaktivere prosjektet (`PATCH`). At runtime-rollen heller ikke skal kunne kalle funksjonen, gjelder databaserettighetene og hører til F1 (B-02 punkt 4). En migrasjon legger inn prosjektet `oslobygg`, og det er i dag basens eneste prosjekt (DM-03).</t>
+          <t>Registreres av drift gjennom databasefunksjonen `koe_register_project` (`scripts/catenda_admin.py`). `POST /api/projects` svarer 403 utenfor utviklingsmodus. En prosjektadministrator kan endre navn, beskrivelse og innstillinger og deaktivere prosjektet (`PATCH`). Driftsskriptet `catenda_admin.py sync-name` oppdaterer navnet direkte fra Catenda, utenom databasefunksjonen. At runtime-rollen heller ikke skal kunne kalle funksjonen, gjelder databaserettighetene og hører til F1 (B-02 punkt 4). En migrasjon legger inn prosjektet `oslobygg`, og det er i dag basens eneste prosjekt (DM-03).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -755,12 +757,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nei, ikke direkte. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`.</t>
+          <t>Nei, ikke direkte. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`. Dataflyt: fra Catenda i C18, C20 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Primærnøkkel `id`. `app_project_memberships`, `app_membership_sync`, `catenda_project_configs` og `project_memberships` har fremmednøkkel hit. `prosjekt_id` i andre tabeller viser hit uten fremmednøkkel. Triggeren `trg_auto_membership_on_project_create` skriver `project_memberships` ved ny rad.</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: app_membership_sync.project_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); approval_outbox.project (uten fremmednøkkel); approvals.project (uten fremmednøkkel); catenda_delivery_status.project (uten fremmednøkkel); catenda_models_cache.prosjekt_id (uten fremmednøkkel); catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); eo_approvals.project (uten fremmednøkkel); hendelse.prosjekt_id (uten fremmednøkkel); notat.prosjekt_id (uten fremmednøkkel); project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.prosjekt_id (uten fremmednøkkel); sak_relations.prosjekt_id (uten fremmednøkkel); utkast.project (uten fremmednøkkel); vedlegg.project (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -812,12 +814,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>`project_id` → `projects.id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (project_id, user_email). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -869,12 +871,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ja. E-post og navn kommer fra Catenda-profilen og medlemslisten.</t>
+          <t>Ja. E-post og navn kommer fra Catenda-profilen og medlemslisten. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Primærnøkkel `id`. `app_identities`, `app_sessions` og `app_project_memberships` har fremmednøkkel hit. `hendelse.actorid` og `notat.aktor_id` viser hit uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: app_identities.user_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.user_id (fremmednøkkel, ON DELETE CASCADE); app_sessions.user_id (fremmednøkkel, ON DELETE CASCADE); hendelse.actorid (uten fremmednøkkel); notat.aktor_id (uten fremmednøkkel); sak_metadata.created_by (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -926,12 +928,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ja. Subjektet er Catenda-ID-en.</t>
+          <t>Ja. Subjektet er Catenda-ID-en. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>`user_id` → `app_users.id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_project_memberships.catenda_subject (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -983,12 +985,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>`user_id` → `app_users.id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1040,12 +1042,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Nei, men raden hører til en innlogging hos Catenda.</t>
+          <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Ingen fremmednøkler.</t>
+          <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1097,12 +1099,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Ja. Medlemslisten hentes fra Catenda-prosjektet.</t>
+          <t>Ja. Medlemslisten hentes fra Catenda-prosjektet. Dataflyt: fra Catenda i C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>`project_id` → `projects.id` og `user_id` → `app_users.id` (fremmednøkler).</t>
+          <t>Nøkler: primærnøkkel (id); unik (project_id, catenda_subject); unik (project_id, user_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE); catenda_subject → app_identities.subject (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1154,12 +1156,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_project_id` er en Catenda-ID.</t>
+          <t>Delvis. `catenda_project_id` er en Catenda-ID. Dataflyt: fra Catenda i C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>`project_id` → `projects.id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1211,12 +1213,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ja. ID-ene er Catenda-ID-er, oppgitt ved registrering.</t>
+          <t>Ja. ID-ene er Catenda-ID-er, oppgitt ved registrering. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>`internal_project_id` → `projects.id` (fremmednøkkel). `catenda_topic_board_configs` og `catenda_contract_teams` har fremmednøkkel hit.</t>
+          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → projects.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_membership_sync.catenda_project_id (uten fremmednøkkel); catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE CASCADE); catenda_models_cache.catenda_project_id (uten fremmednøkkel); catenda_topic_board_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1268,12 +1270,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Ja. `topic_board_id` er en Catenda-ID.</t>
+          <t>Ja. `topic_board_id` er en Catenda-ID. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>`internal_project_id` → `catenda_project_configs.internal_project_id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (topic_board_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: sak_metadata.catenda_board_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1325,12 +1327,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Ja. `team_id` er en Catenda-ID.</t>
+          <t>Ja. `team_id` er en Catenda-ID. Dataflyt: fra Catenda i C18, C19 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>`internal_project_id` → `catenda_project_configs.internal_project_id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: hendelse.actorteam (uten fremmednøkkel); notat.aktor_team_id (uten fremmednøkkel); utkast.team (uten fremmednøkkel); vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1382,12 +1384,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Ja, etter formålet. Hvordan den skulle fylles, er ikke kjent.</t>
+          <t>Ja, etter formålet. Hvordan den skulle fylles, er ikke kjent. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>`prosjekt_id` viser til `projects.id` uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (id); unik (catenda_project_id, model_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1439,12 +1441,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Modell- og objekt-ID-ene er fra Catenda.</t>
+          <t>Delvis. Modell- og objekt-ID-ene er fra Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>`sak_id` → `sak_metadata.sak_id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1496,12 +1498,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>`sak_id` → `sak_metadata.sak_id` (fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (token). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1553,12 +1555,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>`user_id` → `auth.users` (fremmednøkkel til Supabase-plattformens tabell) og `manager_id` → `user_groups.id`. Fremmednøkkelen til `auth.users` må løses hvis basen flyttes fra Supabase (B-12).</t>
+          <t>Nøkler: primærnøkkel (id); unik (user_id). Viser til: manager_id → user_groups.id (fremmednøkkel, ON DELETE SET NULL); user_id → auth.users.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1610,12 +1612,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Nei. Teamet er en Catenda-team-ID.</t>
+          <t>Nei. Teamet er en Catenda-team-ID. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Nøkkel: prosjekt, sak, spor, revisjon og team. Viser til saken og teamet uten fremmednøkler.</t>
+          <t>Nøkler: primærnøkkel (project, case_id, spor, revisjon, team). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); team → catenda_contract_teams.team_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1667,12 +1669,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Nøkkel: prosjekt og sak. Publiserte hendelser lagres i `hendelse`, og varslingsjobben i `approval_outbox`.</t>
+          <t>Nøkler: primærnøkkel (project, case_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); body → items[].claimId → hendelse.event_id (uten fremmednøkkel); body → packages[].eventIds[] → hendelse.event_id (uten fremmednøkkel). Vises til fra: approval_outbox.id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1724,12 +1726,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: fra Catenda i C07 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>`id` er pakkens ID i `approvals`.</t>
+          <t>Nøkler: primærnøkkel (id). Viser til: id → approvals.body → packages[].id (uten fremmednøkkel); project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1781,12 +1783,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Nøkkel: prosjekt. Viser til endringsordresakene uten fremmednøkler.</t>
+          <t>Nøkler: primærnøkkel (project). Viser til: project → projects.id (uten fremmednøkkel); body → packages[].sakId → sak_metadata.sak_id (uten fremmednøkkel); body → packages[].request.koe_sak_ids[] → sak_metadata.sak_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1838,12 +1840,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting.</t>
+          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting. Dataflyt: fra Catenda i C05, C08; til Catenda i C08 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Nøkkel: prosjekt, sak og `vedlegg_id`. Hendelser viser til `vedlegg_id`, uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (project, case_id, vedlegg_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); lastet_opp_team → catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: hendelse.data → vedlegg_ids[] (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1895,12 +1897,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Nei, men statusen gjelder et kall til Catenda.</t>
+          <t>Nei, men statusen gjelder et kall til Catenda. Dataflyt: fra Catenda i C06 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Nøkkel: prosjekt, sak og `event_id`. Viser til `hendelse.event_id` uten fremmednøkkel.</t>
+          <t>Nøkler: primærnøkkel (project, case_id, event_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); event_id → hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1930,6 +1932,5217 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fra tabell</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fra kolonne</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Til tabell</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Til kolonne</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Antall</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ved sletting</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Beskrivelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Saken hendelsen hører til. Slettes saken i saksregisteret, sletter basen journalen med (ON DELETE CASCADE); basen verner ikke journalen (MS-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Saken notatet er skrevet i.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>sak_bim_links</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Saken BIM-objektet er koblet til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>magic_links</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Saken lenken gjaldt. Tabellen er en rest (MS-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet koblingen til Catenda gjelder. Én konfigurasjon per prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>catenda_topic_board_configs</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet topic boardet hører til. Et prosjekt kan ha flere boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet teamet representerer TE eller BH i.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>app_identities</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren den eksterne identiteten tilhører.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>app_sessions</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren som er logget inn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet medlemskapet gjelder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren som er medlem. Én rad per prosjekt og bruker (UNIQUE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>app_membership_sync</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet synkroniseringen gjelder. Én rad per prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>project_memberships</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet i den eldre medlemslisten. Tabellen er en rest (MS-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>user_groups</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>manager_id</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>user_groups</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Lederen i brukergruppen. Tabellen er en rest (MS-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>user_groups</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>auth.users</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren i Supabase-plattformens egen tabell, ikke `app_users`. Må løses om basen flyttes fra Supabase (B-12). Tabellen er en rest (MS-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet hendelsen er skrevet i. Stemples av serveren fra autorisert kontekst, uten default (AGENTS.md, sikkerhetsinvariantene).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>actorid</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Den som sendte hendelsen. Verdien er `app_users.id` og aldri et navn (AGENTS.md). Kolonnen er `text`, `id` er `uuid`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>actorteam</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Teamet avsenderen satt i, utledet fra teammedlemskapet i Catenda da hendelsen ble skrevet. Tom når teamet ikke var entydig. Lagres som 32 heksadesimaler uten bindestreker (`catenda_id`), mens `team_id` er `uuid`; en sammenstilling må normalisere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>referstoid</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Kravet et svar gjelder (`refererer_til_event_id`), i samme sak. Forretningsreglene for svar sammenlikner den med sporets gjeldende krav.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>data → vedlegg_ids[]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg_id</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>mange til mange</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Vedleggene hendelsen sender. Leveringen til Catenda starter fra disse referansene etter at hendelsen er lagret. Sammenlikningen normaliserer med `catenda_id`. Går på tvers av lagene: journalen i PostgreSQL, registeret i SQLite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet notatet er skrevet i.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Forfatteren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Skjermingen går på denne verdien; uten den vises notatet til ingen (AGENTS.md). Samme verdiform som `hendelse.actorteam`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen notatet kommenterer, om noen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet saken tilhører. Tilgangskontrollen holder hver forespørsel mot denne verdien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Den som opprettet saken. Bare delvis en kobling: verdien har tre former, og bare én av dem er `app_users.id` (MG-04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Catenda-prosjektet saken ble opprettet i. Kolonnen er `text`, målet er `uuid`. Levering til Catenda bruker i dag den globale innstillingen, ikke denne verdien (INT-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>catenda_board_id</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>catenda_topic_board_configs</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>topic_board_id</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Topic boardet sakens topic ligger på. Kolonnen er `text`, målet er `uuid`. Levering til Catenda leser boardet herfra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>sak_relations</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>source_sak_id</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Forseringen eller endringsordren som omfatter en annen sak. Fremmednøkkelen mangler (DB-04); hvordan relasjoner skal lagres, er B-01. Opprettes en forsering gjennom `/api/forsering/opprett`, er verdien topicens GUID, og saken har da ingen rad i `sak_metadata`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>sak_relations</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>target_sak_id</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>KOE-saken som inngår i forseringen eller endringsordren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>sak_relations</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet relasjonen er skrevet i, stemplet fra autorisert kontekst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>catenda_subject</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>app_identities</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Personen i Catenda. `koe_reconcile_memberships` løser subjektet til `user_id` gjennom `koe_resolve_identity`, så de to kolonnene peker på samme person. Kontraktssiden slås opp med subjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>app_membership_sync</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Catenda-prosjektet synkroniseringen hentet fra. `ensure_fresh` godtar bare en synkronisering av prosjektets nåværende Catenda-prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>catenda_models_cache</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet modellene gjelder. BIM-rutene slår opp på denne. Tabellen fylles ikke (DM-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>catenda_models_cache</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_configs</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>catenda_project_id</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Catenda-prosjektet modellene ligger i. Kolonnen er `text`, målet er `uuid`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>utkast</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet utkastet er skrevet i.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>utkast</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Saken utkastet gjelder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>utkast</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som eier utkastet. Uten entydig team finnes det ikke noe utkast. Samme verdiform som `hendelse.actorteam`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet godkjenningen hører til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Saken. Ett dokument per prosjekt og sak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>body → items[].claimId</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Kravet en forberedt svarpost gjelder. Posten er ugyldig om et nyere krav eller en tilbaketrekking er kommet i sporet. Ved publisering blir verdien `refererer_til_event_id` i svaret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>body → packages[].eventIds[]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>mange til mange</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsene en publisert pakke ble til i journalen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>approval_outbox</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>approvals</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>body → packages[].id</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Pakken varslingsjobben gjelder. Én jobb per pakke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>approval_outbox</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>approval_outbox</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>eo_approvals</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet. Ett dokument per prosjekt med alle endringsordrene til godkjenning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>eo_approvals</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>body → packages[].sakId</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Saks-ID-en endringsordren er reservert under. Saken finnes først når ordren er utstedt; fram til da peker verdien på en sak som ikke finnes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>eo_approvals</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>body → packages[].request.koe_sak_ids[]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>mange til mange</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>KOE-sakene endringsordren skal omfatte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Saken vedlegget er lastet opp i. Nedlasting krever at vedlegget står på nøyaktig denne saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>lastet_opp_team</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som lastet opp. Et vedlegg som ikke er sendt, er synlig bare for dette teamet. Samme verdiform som `hendelse.actorteam`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Saken banneret vises på.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen kvitteringen gjelder. Kvitteringen skrives før hendelsen lagres; ved lesing teller bare kvitteringer for hendelser som finnes i journalen.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pil</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Flyt</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Retning</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Utløses av</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fra</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Til</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Catenda-endepunkt</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kode eller databasefunksjon</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C01.1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Webhook-reservasjon</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Innkommende POST fra Catenda</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/catenda_webhook_routes.py:webhook; backend/lib/security/webhook_security.py:is_duplicate_event</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Varselets ID, så samme varsel ikke behandles to ganger. Reserveres før behandlingen (INT-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C01.2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topic board</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_project_resolver.py:CatendaProjectResolver.resolve; backend/services/catenda_project_resolver_factory.py:_make_bimsync_lookup.lookup</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>`bimsync_project_id` for boardet i varselet, kontrollert mot prosjektet i varselet og i registeret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C01.3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService.handle_new_topic_created; backend/services/sak_creation_service.py:SakCreationService.create_sak</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Tittel og topictype, som blir sakstypen. `sak_metadata` får også topic-, board- og prosjekt-ID; journalen får `sak_opprettet`. Boardet er det fra varselet, ikke den globale innstillingen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C01.3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService.handle_new_topic_created; backend/services/sak_creation_service.py:SakCreationService.create_sak</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Tittel og topictype, som blir sakstypen. `sak_metadata` får også topic-, board- og prosjekt-ID; journalen får `sak_opprettet`. Boardet er det fra varselet, ikke den globale innstillingen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C01.4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService._aktor_id; backend/repositories/auth_repository.py:AuthRepository.identity; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Forfatterens Catenda-ID (`bimsync_creation_author.user.ref`), løst til `app_users.id`. Raden opprettes bare om den mangler; normalt finnes den fra medlemssynkroniseringen (C04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C01.4</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>app_identities</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService._aktor_id; backend/repositories/auth_repository.py:AuthRepository.identity; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Forfatterens Catenda-ID (`bimsync_creation_author.user.ref`), løst til `app_users.id`. Raden opprettes bare om den mangler; normalt finnes den fra medlemssynkroniseringen (C04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C01.5</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService._contract_side; backend/services/auth_service.py:AuthService.contract_membership_for_subject; backend/lib/auth/catenda_oauth.py:CatendaOAuth.team_members</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Hvilket kontraktsteam forfatteren sitter i, for hvert team i `catenda_contract_teams`. Gir `actorrole`; teamet lagres ikke for denne hendelsen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>C01.6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjekter</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService.handle_new_topic_created</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektnavnet, brukt i kommentaren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C01.7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>C01 Ny topic blir en sak</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.created` fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;`. Validatoren avviser `bcf.issue.created` (INT-03).</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/comments</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService.handle_new_topic_created</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Saks-ID, sakstype og lenke til saken i appen. Feiler kallet, står saken likevel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>C02.1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>C02 Endring på en topic</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.modified` eller `issue.status.changed` fra Catenda.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Webhook-reservasjon</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Innkommende POST fra Catenda</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/catenda_webhook_routes.py:webhook; backend/lib/security/webhook_security.py:is_duplicate_event</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Varselets ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C02.2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>C02 Endring på en topic</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Webhook `issue.modified` eller `issue.status.changed` fra Catenda.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Innkommende POST fra Catenda</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_webhook_service.py:WebhookService.handle_topic_modification</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Topicens ID, slått opp i `sak_metadata`, og hva som er endret. Skrives bare til loggen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>C03.1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>C03 Innlogging</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/auth/catenda/callback` når Catenda sender brukeren tilbake.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: OAuth-token</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>POST /oauth2/token</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/auth_routes.py:callback; backend/lib/auth/catenda_oauth.py:CatendaOAuth.exchange</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Brukerens tilgangstoken. Lagres ikke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C03.2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>C03 Innlogging</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/auth/catenda/callback` når Catenda sender brukeren tilbake.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: innlogget bruker</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/user</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.login; backend/lib/auth/catenda_oauth.py:CatendaOAuth.user; backend/repositories/auth_repository.py:AuthRepository.identity; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Catenda-ID, e-post og navn. E-post og navn oppdateres ved hver innlogging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>C03.2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>C03 Innlogging</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/auth/catenda/callback` når Catenda sender brukeren tilbake.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: innlogget bruker</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>app_identities</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/user</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.login; backend/lib/auth/catenda_oauth.py:CatendaOAuth.user; backend/repositories/auth_repository.py:AuthRepository.identity; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Catenda-ID, e-post og navn. E-post og navn oppdateres ved hver innlogging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>C03.3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>C03 Innlogging</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/auth/catenda/callback` når Catenda sender brukeren tilbake.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjekter</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>app_project_memberships</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects (sidevis)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.login; backend/lib/auth/catenda_oauth.py:CatendaOAuth.projects; backend/repositories/auth_repository.py:AuthRepository.deactivate_user_projects</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektene brukeren ser i Catenda. Medlemskap i registrerte prosjekter brukeren ikke lenger ser, deaktiveres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>C04.1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>C04 Medlemslisten synkroniseres</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Innlogging (C03); tilgangskontrollen, når kopien er eldre enn `AUTH_MEMBERSHIP_MAX_AGE_SECONDS` (standard 900 sekunder); `POST /api/projects/&lt;id&gt;/members/sync`; og driftsskriptene `sync_catenda_memberships.py` og `catenda_admin.py sync-members`.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjektmedlemmer</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>app_project_memberships</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/members?userType=user (sidevis)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.sync; backend/lib/auth/catenda_oauth.py:CatendaOAuth.members; backend/repositories/auth_repository.py:AuthRepository.reconcile; databasefunksjon:koe_reconcile_memberships</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Hvert medlem med Catenda-ID, e-post, navn og rolle. Catenda-prosjektet er prosjektets eget fra `catenda_project_configs`. Funksjonen oppdaterer medlemskapene og skriver tidspunktet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C04.1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>C04 Medlemslisten synkroniseres</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Innlogging (C03); tilgangskontrollen, når kopien er eldre enn `AUTH_MEMBERSHIP_MAX_AGE_SECONDS` (standard 900 sekunder); `POST /api/projects/&lt;id&gt;/members/sync`; og driftsskriptene `sync_catenda_memberships.py` og `catenda_admin.py sync-members`.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjektmedlemmer</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>app_membership_sync</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/members?userType=user (sidevis)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.sync; backend/lib/auth/catenda_oauth.py:CatendaOAuth.members; backend/repositories/auth_repository.py:AuthRepository.reconcile; databasefunksjon:koe_reconcile_memberships</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Hvert medlem med Catenda-ID, e-post, navn og rolle. Catenda-prosjektet er prosjektets eget fra `catenda_project_configs`. Funksjonen oppdaterer medlemskapene og skriver tidspunktet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>C04.2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>C04 Medlemslisten synkroniseres</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Innlogging (C03); tilgangskontrollen, når kopien er eldre enn `AUTH_MEMBERSHIP_MAX_AGE_SECONDS` (standard 900 sekunder); `POST /api/projects/&lt;id&gt;/members/sync`; og driftsskriptene `sync_catenda_memberships.py` og `catenda_admin.py sync-members`.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjektmedlemmer</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>app_users</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/members?userType=user (sidevis)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.sync; backend/repositories/auth_repository.py:AuthRepository.reconcile; databasefunksjon:koe_reconcile_memberships; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Hver person løst til en brukerrad. E-post og navn oppdateres fra medlemslisten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C04.2</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>C04 Medlemslisten synkroniseres</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Innlogging (C03); tilgangskontrollen, når kopien er eldre enn `AUTH_MEMBERSHIP_MAX_AGE_SECONDS` (standard 900 sekunder); `POST /api/projects/&lt;id&gt;/members/sync`; og driftsskriptene `sync_catenda_memberships.py` og `catenda_admin.py sync-members`.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjektmedlemmer</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>app_identities</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/members?userType=user (sidevis)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/auth_service.py:AuthService.sync; backend/repositories/auth_repository.py:AuthRepository.reconcile; databasefunksjon:koe_reconcile_memberships; databasefunksjon:koe_resolve_identity</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Hver person løst til en brukerrad. E-post og navn oppdateres fra medlemslisten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C05.1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>C05 Kontraktsside og team ved skriving</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Hver rute med `require_contract_role`, og lesing av interne notater, utkast og vedlegg som ikke er sendt.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>backend/lib/auth/contract_role.py:require_contract_role; backend/lib/auth/event_visibility.py:reader_contract_team; backend/services/auth_service.py:AuthService.contract_membership; backend/services/auth_service.py:AuthService.contract_membership_for_subject; backend/lib/auth/catenda_oauth.py:CatendaOAuth.team_members</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Side og team. Blir `actorrole` og `actorteam` i hendelsen, `aktor_rolle` og `aktor_team_id` i notatet, `team` og `kontraktsside` i utkastet, og `lastet_opp_rolle` og `lastet_opp_team` i vedlegget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C05.1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>C05 Kontraktsside og team ved skriving</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Hver rute med `require_contract_role`, og lesing av interne notater, utkast og vedlegg som ikke er sendt.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>notat</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>backend/lib/auth/contract_role.py:require_contract_role; backend/lib/auth/event_visibility.py:reader_contract_team; backend/services/auth_service.py:AuthService.contract_membership; backend/services/auth_service.py:AuthService.contract_membership_for_subject; backend/lib/auth/catenda_oauth.py:CatendaOAuth.team_members</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Side og team. Blir `actorrole` og `actorteam` i hendelsen, `aktor_rolle` og `aktor_team_id` i notatet, `team` og `kontraktsside` i utkastet, og `lastet_opp_rolle` og `lastet_opp_team` i vedlegget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C05.1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>C05 Kontraktsside og team ved skriving</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Hver rute med `require_contract_role`, og lesing av interne notater, utkast og vedlegg som ikke er sendt.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>utkast</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>backend/lib/auth/contract_role.py:require_contract_role; backend/lib/auth/event_visibility.py:reader_contract_team; backend/services/auth_service.py:AuthService.contract_membership; backend/services/auth_service.py:AuthService.contract_membership_for_subject; backend/lib/auth/catenda_oauth.py:CatendaOAuth.team_members</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Side og team. Blir `actorrole` og `actorteam` i hendelsen, `aktor_rolle` og `aktor_team_id` i notatet, `team` og `kontraktsside` i utkastet, og `lastet_opp_rolle` og `lastet_opp_team` i vedlegget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C05.1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>C05 Kontraktsside og team ved skriving</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hver rute med `require_contract_role`, og lesing av interne notater, utkast og vedlegg som ikke er sendt.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>backend/lib/auth/contract_role.py:require_contract_role; backend/lib/auth/event_visibility.py:reader_contract_team; backend/services/auth_service.py:AuthService.contract_membership; backend/services/auth_service.py:AuthService.contract_membership_for_subject; backend/lib/auth/catenda_oauth.py:CatendaOAuth.team_members</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Side og team. Blir `actorrole` og `actorteam` i hendelsen, `aktor_rolle` og `aktor_team_id` i notatet, `team` og `kontraktsside` i utkastet, og `lastet_opp_rolle` og `lastet_opp_team` i vedlegget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>C06.1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>C06 Hendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/events` for en sak med topic, når Catenda er slått på. `POST /api/events/batch` sender ikke til Catenda (RV-10).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentbiblioteket</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>POST /v2/projects/{catenda_project_id}/libraries/{library_id}/items</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/event_routes.py:_post_to_catenda; backend/routes/event_routes.py:_upload_and_link_pdf; backend/services/catenda_service.py:CatendaService.upload_document</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>PDF av brevet eller saken. Et frosset brev i hendelsen gjøres til PDF og må komme gjennom; ellers lages PDF-en på serveren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C06.2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>C06 Hendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/events` for en sak med topic, når Catenda er slått på. `POST /api/events/batch` sender ikke til Catenda (RV-10).</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentreferanser</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/document_references</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/event_routes.py:_upload_and_link_pdf; backend/services/catenda_service.py:CatendaService.create_document_reference</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Dokument-ID-en fra opplastingen, først med og så uten bindestreker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>C06.3</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>C06 Hendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/events` for en sak med topic, når Catenda er slått på. `POST /api/events/batch` sender ikke til Catenda (RV-10).</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/comments</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/event_routes.py:_post_catenda_comment; backend/services/catenda_service.py:CatendaService.create_comment</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Tekst laget av hendelsen og sakens tilstand, med lenke til saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>C06.4</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>C06 Hendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/events` for en sak med topic, når Catenda er slått på. `POST /api/events/batch` sender ikke til Catenda (RV-10).</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/event_routes.py:_sync_topic_status; backend/services/catenda_service.py:CatendaService.update_topic_status</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Ny topicstatus når sakens overordnede status er endret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>C06.5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>C06 Hendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/events` for en sak med topic, når Catenda er slått på. `POST /api/events/batch` sender ikke til Catenda (RV-10).</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: svar på kallene</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Ingen egne kall; utfallet av pilene over</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/event_routes.py:submit_event; backend/services/catenda_delivery_status.py:CatendaDeliveryStatus.record</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>`pending` før hendelsen lagres. Så `delivered` bare når PDF, kommentar og status alle lyktes, ellers `failed`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>C07.1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>C07 Godkjent BH-svar publiseres</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/cases/&lt;sak_id&gt;/approvals` med `action: publish`, etter intern godkjenning.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentbiblioteket</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>POST /v2/projects/{catenda_project_id}/libraries/{library_id}/items</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/approval_routes.py:approvals.dispatch; backend/routes/event_routes.py:_post_to_catenda; backend/routes/event_routes.py:_upload_and_link_pdf</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Det godkjente brevet som PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>C07.2</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>C07 Godkjent BH-svar publiseres</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/cases/&lt;sak_id&gt;/approvals` med `action: publish`, etter intern godkjenning.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentreferanser</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/document_references</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/approval_routes.py:approvals.dispatch; backend/routes/event_routes.py:_upload_and_link_pdf</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Dokument-ID-en fra opplastingen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>C07.3</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>C07 Godkjent BH-svar publiseres</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/cases/&lt;sak_id&gt;/approvals` med `action: publish`, etter intern godkjenning.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/comments</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/approval_routes.py:approvals.dispatch; backend/routes/event_routes.py:_post_catenda_comment</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Kommentar laget av den siste publiserte hendelsen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>C07.4</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>C07 Godkjent BH-svar publiseres</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/cases/&lt;sak_id&gt;/approvals` med `action: publish`, etter intern godkjenning.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/approval_routes.py:approvals.dispatch; backend/routes/event_routes.py:_sync_topic_status</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Topicstatus når sakens status er endret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>C07.5</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>C07 Godkjent BH-svar publiseres</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/cases/&lt;sak_id&gt;/approvals` med `action: publish`, etter intern godkjenning.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: svar på kallene</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>approval_outbox</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Ingen egne kall; utfallet av pilene over</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/approval_service.py:ApprovalService.deliver</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>`delivered`, `failed` eller `not_configured`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>C08.1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>C08 Vedlegg sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Etter at en hendelse med `vedlegg_ids` er lagret: `POST /api/events`, `POST /api/events/batch` og publisering av en godkjent pakke. `POST /api/cases/&lt;sak_id&gt;/vedlegg/retry` prøver på nytt.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentbiblioteket</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>POST /v2/projects/{catenda_project_id}/libraries/{library_id}/items</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/vedlegg_routes.py:lever_vedlegg_for_hendelser; backend/services/catenda_service.py:CatendaService.upload_document</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Filinnholdet i `innhold`, med filnavnet, til mappen `folder_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>C08.2</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>C08 Vedlegg sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Etter at en hendelse med `vedlegg_ids` er lagret: `POST /api/events`, `POST /api/events/batch` og publisering av en godkjent pakke. `POST /api/cases/&lt;sak_id&gt;/vedlegg/retry` prøver på nytt.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentbiblioteket</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Svar på opplastingen</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/vedlegg_routes.py:lever_vedlegg_for_hendelser; backend/services/vedlegg_registry.py:VedleggRegistry.mark_uploaded</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Dokument-ID-en i Catenda, i `catenda_item_id`. Lagres før koblingen, så et nytt forsøk ikke laster opp dokumentet to ganger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>C08.3</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>C08 Vedlegg sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Etter at en hendelse med `vedlegg_ids` er lagret: `POST /api/events`, `POST /api/events/batch` og publisering av en godkjent pakke. `POST /api/cases/&lt;sak_id&gt;/vedlegg/retry` prøver på nytt.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentreferanser</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/document_references</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/vedlegg_routes.py:lever_vedlegg_for_hendelser; backend/services/catenda_service.py:CatendaService.create_document_reference</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Dokument-ID-en, koblet til sakens topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>C08.4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>C08 Vedlegg sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Etter at en hendelse med `vedlegg_ids` er lagret: `POST /api/events`, `POST /api/events/batch` og publisering av en godkjent pakke. `POST /api/cases/&lt;sak_id&gt;/vedlegg/retry` prøver på nytt.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: svar på kallene</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Svar på koblingen</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/vedlegg_routes.py:lever_vedlegg_for_hendelser; backend/services/vedlegg_registry.py:VedleggRegistry.mark_delivered</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Status `delivered`. Det mellomlagrede innholdet slettes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>C09.1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>C09 Vedlegg lastes ned</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/cases/&lt;sak_id&gt;/vedlegg/&lt;vedlegg_id&gt;` for et vedlegg som er levert.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: dokumentbiblioteket</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/libraries/{library_id}/items/{item_id}</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/vedlegg_routes.py:last_ned_vedlegg; backend/services/catenda_service.py:CatendaService.download_document</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Filinnholdet, sendt rett til brukeren. Appen beholder ingen kopi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>C10.1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>C10 Forsering opprettes</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/opprett`. Frontenden kaller ikke ruta.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/forsering_service.py:ForseringService.opprett_forseringssak</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Tittel med de avslåtte sakene, begrunnelsen og typen `Forsering`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>C10.2</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>C10 Forsering opprettes</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/opprett`. Frontenden kaller ikke ruta.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>GET og PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/forsering_service.py:ForseringService.opprett_forseringssak</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Toveis relasjoner mellom forseringen og hver avslåtte sak. Sak-ID-ene sendes som topic-GUID-er, og klienten avviser en ID som ikke er en GUID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>C10.3</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>C10 Forsering opprettes</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/opprett`. Frontenden kaller ikke ruta.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>sak_relations</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Svar på POST topics</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/forsering_service.py:ForseringService.opprett_forseringssak</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Topicens GUID blir forseringens sak-ID i `source_sak_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>C11.1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>C11 KOE legges til eller fjernes fra en forsering</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/&lt;sak_id&gt;/relatert` og `DELETE /api/forsering/&lt;sak_id&gt;/relatert/&lt;koe_sak_id&gt;`. Frontenden kaller ikke rutene.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>GET og PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/base_sak_service.py:BaseSakService.legg_til_relatert_sak</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Toveis relasjon mellom forseringen og KOE-saken, med sak-ID-ene som topic-GUID-er.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>C11.2</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>C11 KOE legges til eller fjernes fra en forsering</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/&lt;sak_id&gt;/relatert` og `DELETE /api/forsering/&lt;sak_id&gt;/relatert/&lt;koe_sak_id&gt;`. Frontenden kaller ikke rutene.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics/{related_topic_guid}</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/base_sak_service.py:BaseSakService.fjern_relatert_sak</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Begge retningene av relasjonen fjernes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>C12.1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>C12 Relaterte saker hentes fra Catenda</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/forsering/&lt;sak_id&gt;/relaterte` og `/kontekst`, og `GET /api/endringsordre/&lt;sak_id&gt;/relaterte` og `/kontekst`.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics?includeBimsyncProjectTopics=true</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/base_sak_service.py:BaseSakService.hent_relaterte_saker</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>GUID-ene til de relaterte topicene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>C12.2</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>C12 Relaterte saker hentes fra Catenda</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/forsering/&lt;sak_id&gt;/relaterte` og `/kontekst`, og `GET /api/endringsordre/&lt;sak_id&gt;/relaterte` og `/kontekst`.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{related_topic_guid}</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/base_sak_service.py:BaseSakService.hent_relaterte_saker</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Tittelen på hver relaterte topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>C13.1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>C13 Saker fra topiclisten</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/forsering/kandidater` og `GET /api/forsering/by-relatert/&lt;sak_id&gt;`, som søker gjennom alle saker.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics (sidevis)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/forsering_service.py:ForseringService.hent_kandidat_koe_saker</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Topic-GUID-ene, oversatt til sak-ID-er, for å finne KOE-saker med avslått fristkrav.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>C13.2</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>C13 Saker fra topiclisten</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/forsering/kandidater` og `GET /api/forsering/by-relatert/&lt;sak_id&gt;`, som søker gjennom alle saker.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics (sidevis)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/forsering_service.py:ForseringService.finn_forseringer_for_sak; backend/lib/helpers/sak_lookup.py:get_all_sak_ids</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Topic-GUID-ene, oversatt til sak-ID-er, for å finne forseringer som omfatter en sak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>C14.1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>C14 Forseringshendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/&lt;sak_id&gt;/bh-respons`, `POST /api/forsering/&lt;sak_id&gt;/stopp` og `PUT /api/forsering/&lt;sak_id&gt;/kostnader`.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/comments</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/forsering_routes.py:_sync_forsering_to_catenda; backend/services/catenda_sync_service.py:CatendaSyncService._post_comment; backend/services/catenda_service.py:CatendaService.create_comment</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Tekst laget av hendelsen, med lenke til saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>C14.2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>C14 Forseringshendelse sendes til Catenda</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/forsering/&lt;sak_id&gt;/bh-respons`, `POST /api/forsering/&lt;sak_id&gt;/stopp` og `PUT /api/forsering/&lt;sak_id&gt;/kostnader`.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/catenda_sync_service.py:CatendaSyncService._update_status; backend/services/catenda_service.py:CatendaService.update_topic_status</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Ny topicstatus når sakens status er endret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>C15.1</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>C15 Endringsordre opprettes eller endres</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/endringsordre/opprett`, utstedelse etter godkjenning, og `POST /api/endringsordre/&lt;sak_id&gt;/koe` og `DELETE …/koe/&lt;koe_sak_id&gt;`.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{topic_board_id}/topics</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/endringsordre_service.py:EndringsordreService._sync_to_catenda</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Tittel `Endringsordre &lt;nummer&gt;`, beskrivelsen og typen `Endringsordre`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>C15.2</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>C15 Endringsordre opprettes eller endres</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/endringsordre/opprett`, utstedelse etter godkjenning, og `POST /api/endringsordre/&lt;sak_id&gt;/koe` og `DELETE …/koe/&lt;koe_sak_id&gt;`.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: topics</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Svar på POST topics</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/endringsordre_service.py:EndringsordreService._sync_to_catenda; backend/repositories/postgres/sak_metadata.py:PostgresSakMetadataRepository.set_catenda_mapping</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Topicens GUID, boardet og Catenda-prosjektet, lagret straks, også om en relasjon senere feiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>C15.3</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>C15 Endringsordre opprettes eller endres</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/endringsordre/opprett`, utstedelse etter godkjenning, og `POST /api/endringsordre/&lt;sak_id&gt;/koe` og `DELETE …/koe/&lt;koe_sak_id&gt;`.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>GET og PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/endringsordre_service.py:EndringsordreService._sync_to_catenda</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Toveis relasjoner mellom den nye endringsordren og KOE-sakene, med KOE-sakenes topic-ID fra `sak_metadata`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>C15.4</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>C15 Endringsordre opprettes eller endres</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/endringsordre/opprett`, utstedelse etter godkjenning, og `POST /api/endringsordre/&lt;sak_id&gt;/koe` og `DELETE …/koe/&lt;koe_sak_id&gt;`.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>GET og PUT /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/endringsordre_service.py:EndringsordreService.legg_til_koe</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Toveis relasjon, etter at `eo_koe_lagt_til` og raden i `sak_relations` er skrevet. Sak-ID-ene sendes som topic-GUID-er.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>C15.5</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>C15 Endringsordre opprettes eller endres</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>inn og ut</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>`POST /api/endringsordre/opprett`, utstedelse etter godkjenning, og `POST /api/endringsordre/&lt;sak_id&gt;/koe` og `DELETE …/koe/&lt;koe_sak_id&gt;`.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: relaterte topics</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}/related_topics/{related_topic_guid}</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>backend/services/endringsordre_service.py:EndringsordreService.fjern_koe</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Begge retningene fjernes, etter `eo_koe_fjernet` og slettingen i `sak_relations`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>C16.1</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>C16 BIM-objekter vises</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/bim/ifc-products`, `GET /api/bim/ifc-types` og `GET /api/saker/&lt;sak_id&gt;/bim-links/&lt;link_id&gt;/related`.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: BIM-modeller (IFC)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/ifc/products, POST samme sti ved søk, og GET …/ifc/products/ifctypes</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/bim_link_routes.py:list_ifc_products</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Objektene i modellene, med antall per IFC-type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>C16.2</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>C16 BIM-objekter vises</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/bim/ifc-products`, `GET /api/bim/ifc-types` og `GET /api/saker/&lt;sak_id&gt;/bim-links/&lt;link_id&gt;/related`.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: BIM-modeller (IFC)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/ifc/products/ifctypes</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/bim_link_routes.py:list_ifc_types</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Antall objekter per IFC-type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>C16.3</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>C16 BIM-objekter vises</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/bim/ifc-products`, `GET /api/bim/ifc-types` og `GET /api/saker/&lt;sak_id&gt;/bim-links/&lt;link_id&gt;/related`.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: BIM-modeller (IFC)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/ifc/products/{object_id}/relations</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/bim_link_routes.py:get_related_bim_objects</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Objektene et koblet objekt er relatert til, gruppert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>C17.1</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>C17 Kontroll av tilkoblingen og en bruker</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/health/catenda` og `POST /api/validate-user`.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjekter</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/utility_routes.py:catenda_health_check</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Om integrasjonsklienten får en prosjektliste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>C17.2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>C17 Kontroll av tilkoblingen og en bruker</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>`GET /api/health/catenda` og `POST /api/validate-user`.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjektmedlemmer</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/members</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>backend/routes/utility_routes.py:validate_user</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Om en e-post er medlem i det globale Catenda-prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>C18.1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>C18 Prosjekt registreres av drift</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>`scripts/catenda_admin.py register`.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjekter</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/catenda_admin.py:cmd_register; backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektnavnet, når drift ikke har oppgitt det.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>C18.2</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>C18 Prosjekt registreres av drift</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>`scripts/catenda_admin.py register`.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/catenda_admin.py:cmd_register; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project; databasefunksjon:koe_set_contract_teams</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet. ID-ene kommer fra drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>C19.1</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>C19 Kontraktsteam endres av drift</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>`scripts/catenda_admin.py contract-teams` med `--bh` og `--te`.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/catenda_admin.py:cmd_contract_teams; backend/repositories/auth_repository.py:AuthRepository.set_contract_teams; databasefunksjon:koe_set_contract_teams</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>C20.1</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>C20 Prosjektnavn hentes på nytt av drift</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>`scripts/catenda_admin.py sync-name`.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: prosjekter</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/scripts/catenda_admin.py:cmd_sync_name</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektnavnet i Catenda, for hvert registrert prosjekt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1984,7 +7197,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Forserings- og endringsordretjenesten (`create_topic`, `create_topic_relations`), webhook-tjenesten, synkroniseringstjenesten og hendelsesrutene (`create_comment`).</t>
+          <t>Forserings- og endringsordretjenesten (`create_topic`, `create_topic_relations`), webhook-tjenesten, synkroniseringstjenesten og hendelsesrutene (`create_comment`). Kommentar skrives når en topic blir en sak (C01), når en hendelse sendes med `POST /api/events` (C06), når et godkjent BH-svar publiseres (C07), og etter tre av forseringsrutene (C14); se `relasjoner.md`.</t>
         </is>
       </c>
     </row>
@@ -2006,7 +7219,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hendelses- og vedleggsrutene og webhook-tjenesten.</t>
+          <t>Hendelsesruta, publisering av godkjente BH-svar og leveringen av vedlegg (C06, C07, C08). Opplastingen i webhook-tjenesten har ingen kaller.</t>
         </is>
       </c>
     </row>
@@ -2037,7 +7250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3613,7 +8826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13273,13 +18486,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13409,46 +18622,82 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hendelsestyper</t>
+          <t>Relasjoner</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Én rad per hendelsestype i tabellen hendelse. Innholdet ligger i kolonnen data og varierer med typen. Interne notater ligger i tabellen notat.</t>
+          <t>Én rad per kobling mellom to tabeller. «Fremmednøkkel» håndheves av basen; «Uten fremmednøkkel» er en kobling koden bruker, som ingenting i basen håndhever. Nøklene og fremmednøklene er lest fra databasekatalogen.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Hendelsesfelt</t>
+          <t>Dataflyt</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Feltene i data per hendelsestype, generert fra modellene i koden. Delmodellene, som varselinformasjon og brev, står til slutt.</t>
+          <t>Én rad per pil mellom en tabell og Catenda, med endepunktet og koden eller databasefunksjonen som gjør kallet. «Appen, lagres ikke» betyr at dataene brukes eller vises uten å bli lagret.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Kilde for bestemmelsen</t>
+          <t>Diagrammer</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>vedtak: et vedtak i hovedplanen eller en ADR. kode: koden oppgir bestemmelsen, ikke kontrollert mot standardteksten. oppdragsgiver: oppdragsgivers svar.</t>
+          <t>ER-diagrammene og flytdiagrammene står i docs/datamodell/relasjoner.md i repoet, generert fra de samme registrene.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Hendelsestyper</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Én rad per hendelsestype i tabellen hendelse. Innholdet ligger i kolonnen data og varierer med typen. Interne notater ligger i tabellen notat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsesfelt</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Feltene i data per hendelsestype, generert fra modellene i koden. Delmodellene, som varselinformasjon og brev, står til slutt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Kilde for bestemmelsen</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>vedtak: et vedtak i hovedplanen eller en ADR. kode: koden oppgir bestemmelsen, ikke kontrollert mot standardteksten. oppdragsgiver: oppdragsgivers svar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Detaljer om hendelsene</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Innsendingsveier, forretningsregler, belegg og funn står i docs/datamodell/hendelser.md i repoet.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
+          <t>Delvis. `aktor_rolle` og `aktor_team_id` er utledet av teammedlemskapet i Catenda da notatet ble skrevet. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: fra Catenda i C10 (arket Dataflyt).</t>
+          <t>Delvis. En forsering opprettet gjennom `/api/forsering/opprett` får topicens GUID fra Catenda som sak-ID. Ellers er koblingene appens egne. Dataflyt: fra Catenda i C10 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nei, ikke direkte. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`. Dataflyt: fra Catenda i C18, C20 (arket Dataflyt).</t>
+          <t>Delvis. Navnet kan hentes fra Catenda-prosjektet når drift registrerer prosjektet eller kjører `sync-name`. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`. Dataflyt: fra Catenda i C18, C20 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (sak_id, fag, COALESCE(model_id, ''::text), COALESCE(object_global_id, ''::text)). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Nei. Teamet er en Catenda-team-ID. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
+          <t>Delvis. Teamet og kontraktssiden er utledet av teammedlemskapet i Catenda. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: fra Catenda i C07 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: kvittering for kall til Catenda i C07 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting. Dataflyt: fra Catenda i C05, C08; til Catenda i C08 (arket Dataflyt).</t>
+          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting. Dataflyt: fra Catenda i C05, C08; til Catenda i C08; kvittering for kall til Catenda i C08 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Nei, men statusen gjelder et kall til Catenda. Dataflyt: fra Catenda i C06 (arket Dataflyt).</t>
+          <t>Nei, men statusen gjelder et kall til Catenda. Dataflyt: kvittering for kall til Catenda i C06 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -5300,7 +5300,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>PDF av brevet eller saken. Et frosset brev i hendelsen gjøres til PDF og må komme gjennom; ellers lages PDF-en på serveren.</t>
+          <t>Det frosne brevet i hendelsen som PDF, og bare det. En hendelse uten brev laster ikke opp noe.</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>`pending` før hendelsen lagres. Så `delivered` bare når PDF, kommentar og status alle lyktes, ellers `failed`.</t>
+          <t>`pending` før hendelsen lagres. Så `delivered` når kommentar og status lyktes, og brevet er lastet opp når hendelsen har et; ellers `failed`.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -4115,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>C17 Kontroll av tilkoblingen og en bruker</t>
+          <t>C17 Kontroll av tilkoblingen</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>`GET /api/health/catenda` og `POST /api/validate-user`.</t>
+          <t>`GET /api/health/catenda`.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6905,12 +6905,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>C17.2</t>
+          <t>C18.1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C17 Kontroll av tilkoblingen og en bruker</t>
+          <t>C18 Prosjekt registreres av drift</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -6920,39 +6920,39 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>`GET /api/health/catenda` og `POST /api/validate-user`.</t>
+          <t>`scripts/catenda_admin.py register`.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Catenda: prosjektmedlemmer</t>
+          <t>Catenda: prosjekter</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Appen, lagres ikke</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>GET /v2/projects/{catenda_project_id}/members</t>
+          <t>GET /v2/projects/{catenda_project_id}</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>backend/routes/utility_routes.py:validate_user</t>
+          <t>backend/scripts/catenda_admin.py:cmd_register; backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Om en e-post er medlem i det globale Catenda-prosjektet.</t>
+          <t>Prosjektnavnet, når drift ikke har oppgitt det.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>C18.1</t>
+          <t>C18.2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -6972,39 +6972,39 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Catenda: prosjekter</t>
+          <t>Catenda: team og teammedlemmer</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>GET /v2/projects/{catenda_project_id}</t>
+          <t>GET /v2/projects/{catenda_project_id}/teams</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>backend/scripts/catenda_admin.py:cmd_register; backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project</t>
+          <t>backend/scripts/catenda_admin.py:cmd_register; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project; databasefunksjon:koe_set_contract_teams</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Prosjektnavnet, når drift ikke har oppgitt det.</t>
+          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet. ID-ene kommer fra drift.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>C18.2</t>
+          <t>C19.1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C18 Prosjekt registreres av drift</t>
+          <t>C19 Kontraktsteam endres av drift</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>`scripts/catenda_admin.py register`.</t>
+          <t>`scripts/catenda_admin.py contract-teams` med `--bh` og `--te`.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7034,24 +7034,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>backend/scripts/catenda_admin.py:cmd_register; backend/repositories/auth_repository.py:AuthRepository.register_project; databasefunksjon:koe_register_project; databasefunksjon:koe_set_contract_teams</t>
+          <t>backend/scripts/catenda_admin.py:cmd_contract_teams; backend/repositories/auth_repository.py:AuthRepository.set_contract_teams; databasefunksjon:koe_set_contract_teams</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet. ID-ene kommer fra drift.</t>
+          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>C19.1</t>
+          <t>C20.1</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C19 Kontraktsteam endres av drift</t>
+          <t>C20 Prosjektnavn hentes på nytt av drift</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7061,77 +7061,30 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>`scripts/catenda_admin.py contract-teams` med `--bh` og `--te`.</t>
+          <t>`scripts/catenda_admin.py sync-name`.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Catenda: team og teammedlemmer</t>
+          <t>Catenda: prosjekter</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>GET /v2/projects/{catenda_project_id}/teams</t>
+          <t>GET /v2/projects/{catenda_project_id}</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>backend/scripts/catenda_admin.py:cmd_contract_teams; backend/repositories/auth_repository.py:AuthRepository.set_contract_teams; databasefunksjon:koe_set_contract_teams</t>
+          <t>backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/scripts/catenda_admin.py:cmd_sync_name</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>C20.1</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>C20 Prosjektnavn hentes på nytt av drift</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>inn</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>`scripts/catenda_admin.py sync-name`.</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Catenda: prosjekter</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>GET /v2/projects/{catenda_project_id}</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/scripts/catenda_admin.py:cmd_sync_name</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Prosjektnavnet i Catenda, for hvert registrert prosjekt.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -7209,7 +7209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7696,17 +7696,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_trukket</t>
+          <t>frist_innsigelse_sendt</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TE trekker fristkravet.</t>
+          <t>BH gjør gjeldende at varselet om fristforlengelse kom for sent, før TE har spesifisert kravet. En egen handling: den setter ikke resultat, gjør ikke sporet avslått og åpner ikke forsering.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Ingen egen bestemmelse.</t>
+          <t>§ 5 tredje ledd (innsigelse uten ugrunnet opphold) mot varsel etter § 33.4.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>vedtak: nøytralt fristvarsel i 3.1 (23.09); oppdragsgiver, 2026-10-04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Frist blir `trukket`. Er vederlag også `ikke_relevant`, `utkast` eller `trukket`, blir grunnlaget `trukket` (omvendt kaskade).</t>
+          <t>`frist_varsel_ok` blir `false` og `begrunnelse_varsel` settes. Status, `bh_resultat` og `respons_event_id` står urørt.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BH svarer på ansvarsgrunnlaget: godkjent, avslått eller frafalt pålegg, og om grunnlaget er varslet i tide.</t>
+          <t>BH ber TE spesifisere fristkravet. TE må da uten ugrunnet opphold angi dager eller begrunne hvorfor grunnlaget mangler, ellers tapes kravet. En egen handling: den setter ikke resultat, gjør ikke sporet avslått og åpner ikke forsering. Forespørselen sendes per brev, så `brev` er påkrevd.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>grunnlag</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7768,17 +7768,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>§ 32.2 (varslet i tide, bare ved endring), § 32.3 bokstav c (frafall av pålegg). Passivitet etter § 32.3 annet ledd varsles, men trekkes ikke av systemet.</t>
+          <t>§ 33.6.2 første til tredje ledd.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (GrunnlagResponsData, GrunnlagResponsResultat); vedtak: B-13 i 3.1 (24.09)</t>
+          <t>vedtak: nøytralt fristvarsel i 3.1 (23.09); oppdragsgiver, 2026-10-04</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>`godkjent` gir `laast` når grunnlaget ikke er merket for sent varslet; merket for sent varslet gir `under_forhandling`. `avslatt` gir `avslatt`, og `frafalt` gir `trukket`. Svaret knyttes til gjeldende versjon av grunnlaget.</t>
+          <t>`har_bh_foresporsel` blir `true`, `dato_bh_foresporsel` og `foresporsel_krav_id` settes, og `frist_for_spesifisering` får svarfristen. Status, `bh_resultat` og `respons_event_id` står urørt.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7790,22 +7790,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>frist_krav_trukket</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BH endrer sitt svar på ansvarsgrunnlaget («snuoperasjon»).</t>
+          <t>TE trekker fristkravet.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>grunnlag</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7815,17 +7815,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Som `respons_grunnlag`.</t>
+          <t>Ingen egen bestemmelse.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>kode: samme datamodell som respons_grunnlag</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_grunnlag`. Krever et tidligere svar på gjeldende versjon (PREVIOUS_RESPONSE).</t>
+          <t>Frist blir `trukket`. Er vederlag også `ikke_relevant`, `utkast` eller `trukket`, blir grunnlaget `trukket` (omvendt kaskade).</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BH svarer på vederlagskravet: varsler i tide, metode, beløp per post, samlet resultat og eventuelt subsidiært standpunkt.</t>
+          <t>BH svarer på ansvarsgrunnlaget: godkjent, avslått eller frafalt pålegg, og om grunnlaget er varslet i tide.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>grunnlag</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7862,17 +7862,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>§ 34.1.2 og § 34.1.3 (preklusjon), § 34.3.3 (justerte enhetspriser), § 30.2 (tilbakeholdelse ved manglende overslag).</t>
+          <t>§ 32.2 (varslet i tide, bare ved endring), § 32.3 bokstav c (frafall av pålegg). Passivitet etter § 32.3 annet ledd varsles, men trekkes ikke av systemet.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (VederlagResponsData, SubsidiaerTrigger); vedtak: B-13 i 3.1 (24.09)</t>
+          <t>kode: backend/models/events.py (GrunnlagResponsData, GrunnlagResponsResultat); vedtak: B-13 i 3.1 (24.09)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`; `hold_tilbake` gir `under_behandling`. Godkjent beløp, metode, varselvurderinger og subsidiært standpunkt settes. Resultatet lagres slik det er sendt, også når vurderingene i samme svar gir et annet (BR-01).</t>
+          <t>`godkjent` gir `laast` når grunnlaget ikke er merket for sent varslet; merket for sent varslet gir `under_forhandling`. `avslatt` gir `avslatt`, og `frafalt` gir `trukket`. Svaret knyttes til gjeldende versjon av grunnlaget.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BH endrer sitt svar på vederlagskravet, for eksempel ved å oppheve en tilbakeholdelse.</t>
+          <t>BH endrer sitt svar på ansvarsgrunnlaget («snuoperasjon»).</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>grunnlag</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7909,17 +7909,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Som `respons_vederlag`. Kommentaren ved typen nevner opphevet tilbakeholdelse (§ 30.2).</t>
+          <t>Som `respons_grunnlag`.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>kode: kommentaren ved EventType.RESPONS_VEDERLAG_OPPDATERT</t>
+          <t>kode: samme datamodell som respons_grunnlag</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_vederlag`. Uten `beregnings_resultat` står statusen, og bare feltene som sendes, endres.</t>
+          <t>Samme behandling som `respons_grunnlag`. Krever et tidligere svar på gjeldende versjon (PREVIOUS_RESPONSE).</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BH svarer på fristkravet: varsler i tide, om forholdet har hindret fremdriften, antall dager og eventuelt subsidiært standpunkt.</t>
+          <t>BH svarer på vederlagskravet: varsler i tide, metode, beløp per post, samlet resultat og eventuelt subsidiært standpunkt.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>§ 33.1 (fremdriftshindring), § 33.4 og § 33.6 (preklusjon og reduksjon), § 33.6.2 (forespørsel om spesifisering), § 33.7 (svarplikt ved spesifisert krav) og § 5 (innsigelse mot sen varsling).</t>
+          <t>§ 34.1.2 og § 34.1.3 (preklusjon), § 34.3.3 (justerte enhetspriser), § 30.2 (tilbakeholdelse ved manglende overslag).</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (FristResponsData, SubsidiaerTrigger); vedtak: ADR-001, nøytralt fristvarsel i 3.1 (23.09), B-13 i 3.1 (24.09)</t>
+          <t>kode: backend/models/events.py (VederlagResponsData, SubsidiaerTrigger); vedtak: B-13 i 3.1 (24.09)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar med dager på et nøytralt varsel godtas (TFR-06).</t>
+          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`; `hold_tilbake` gir `under_behandling`. Godkjent beløp, metode, varselvurderinger og subsidiært standpunkt settes. Resultatet lagres slik det er sendt, også når vurderingene i samme svar gir et annet (BR-01).</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BH endrer sitt svar på fristkravet.</t>
+          <t>BH endrer sitt svar på vederlagskravet, for eksempel ved å oppheve en tilbakeholdelse.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8003,17 +8003,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Som `respons_frist`.</t>
+          <t>Som `respons_vederlag`. Kommentaren ved typen nevner opphevet tilbakeholdelse (§ 30.2).</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>kode: samme datamodell som respons_frist</t>
+          <t>kode: kommentaren ved EventType.RESPONS_VEDERLAG_OPPDATERT</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_frist`. Uten `beregnings_resultat` står statusen.</t>
+          <t>Samme behandling som `respons_vederlag`. Uten `beregnings_resultat` står statusen, og bare feltene som sendes, endres.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8025,22 +8025,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TE godtar BHs svar på ett spor, angitt i `spor`.</t>
+          <t>BH svarer på fristkravet: varsler i tide, om forholdet har hindret fremdriften, antall dager og eventuelt subsidiært standpunkt.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>valgt i hendelsen</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Ingen egen bestemmelse.</t>
+          <t>§ 33.1 (fremdriftshindring), § 33.4 og § 33.6 (preklusjon og reduksjon), § 33.6.2 (forespørsel om spesifisering), § 33.7 (svarplikt ved spesifisert krav) og § 5 (innsigelse mot sen varsling).</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>kode: backend/models/events.py (FristResponsData, SubsidiaerTrigger); vedtak: ADR-001, nøytralt fristvarsel i 3.1 (23.09), B-13 i 3.1 (24.09)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>TEs aksept settes på sporet. Statusen følger BHs svar og forbedrer det aldri: avslag gir `avslatt_akseptert`, godkjent og delvis godkjent gir `godkjent`, og `hold_tilbake` og `frafalt` lar statusen stå (vedtaket 19.09, TFR-01).</t>
+          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar på et krav uten dager avvises (§ 33.7, TFR-06); før det sendes `frist_innsigelse_sendt` eller `frist_foresporsel_sendt`.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8072,42 +8072,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TE varsler at arbeidet forseres etter avslått fristforlengelse, med estimert kostnad, avslåtte dager og dagmulktsats.</t>
+          <t>BH endrer sitt svar på fristkravet.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ingen</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>forsering</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>§ 33.8.</t>
+          <t>Som `respons_frist`.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (EventType, ForseringVarselData)</t>
+          <t>kode: samme datamodell som respons_frist</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Fyller forseringsdataene: varslet og iverksatt dato (begge fra `dato_iverksettelse`), estimert kostnad, avslåtte dager, dagmulktsats og maksimal kostnad, dagmulkt × dager × 1,3. Ingen sporstatus endres. Kan bare sendes én gang.</t>
+          <t>Samme behandling som `respons_frist`, også sperren mot et krav uten dager. Uten `beregnings_resultat` står statusen.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8119,42 +8119,42 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BH svarer på forseringsvarselet: forseringsrett per sak, 30 %-grensen, godkjent kostnad og særskilte krav.</t>
+          <t>TE godtar BHs svar på ett spor, angitt i `spor`.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ingen</t>
+          <t>valgt i hendelsen</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>forsering</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>§ 33.8, med særskilte krav etter § 34.1.3.</t>
+          <t>Ingen egen bestemmelse.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (ForseringResponsData)</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Lagrer BHs svar i forseringsdataene. Ingen status endres.</t>
+          <t>TEs aksept settes på sporet. Statusen følger BHs svar og forbedrer det aldri: avslag gir `avslatt_akseptert`, godkjent og delvis godkjent gir `godkjent`, og `hold_tilbake` og `frafalt` lar statusen stå (vedtaket 19.09, TFR-01).</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8166,12 +8166,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TE stopper forseringen og oppgir påløpte kostnader.</t>
+          <t>TE varsler at arbeidet forseres etter avslått fristforlengelse, med estimert kostnad, avslåtte dager og dagmulktsats.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (ForseringStoppetData)</t>
+          <t>kode: backend/models/events.py (EventType, ForseringVarselData)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Forseringen merkes stoppet med dato; påløpte kostnader settes når de er oppgitt. Kan bare skje én gang.</t>
+          <t>Fyller forseringsdataene: varslet og iverksatt dato (begge fra `dato_iverksettelse`), estimert kostnad, avslåtte dager, dagmulktsats og maksimal kostnad, dagmulkt × dager × 1,3. Ingen sporstatus endres. Kan bare sendes én gang.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -8213,17 +8213,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TE oppdaterer påløpte kostnader underveis i forseringen.</t>
+          <t>BH svarer på forseringsvarselet: forseringsrett per sak, 30 %-grensen, godkjent kostnad og særskilte krav.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -8238,17 +8238,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>§ 33.8.</t>
+          <t>§ 33.8, med særskilte krav etter § 34.1.3.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (ForseringKostnaderOppdatertData)</t>
+          <t>kode: backend/models/events.py (ForseringResponsData)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader settes. Ingen status endres.</t>
+          <t>Lagrer BHs svar i forseringsdataene. Ingen status endres.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>En KOE-sak med avslått fristkrav knyttes til forseringssaken.</t>
+          <t>TE stopper forseringen og oppgir påløpte kostnader.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Appens egen registrering.</t>
+          <t>§ 33.8.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>kode: backend/models/events.py (ForseringStoppetData)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>KOE-saken legges i listen over avslåtte fristkrav, om den ikke står der.</t>
+          <t>Forseringen merkes stoppet med dato; påløpte kostnader settes når de er oppgitt. Kan bare skje én gang.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>En KOE-sak tas ut av forseringssaken.</t>
+          <t>TE oppdaterer påløpte kostnader underveis i forseringen.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8332,17 +8332,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Appens egen registrering.</t>
+          <t>§ 33.8.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>kode: backend/models/events.py (ForseringKostnaderOppdatertData)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>KOE-saken fjernes fra listen over avslåtte fristkrav.</t>
+          <t>Påløpte kostnader settes. Ingen status endres.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8354,17 +8354,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Første hendelse i en sak: tittel, sakstype og kobling til Catenda. Feltene ligger på toppnivå i modellen og i `data` i journalen. Sender klienten dem i `data`, som skjemaet for ny sak gjør, lagres `data` slik klienten sendte den, også med nøkler modellen ikke kjenner (DM-06).</t>
+          <t>En KOE-sak med avslått fristkrav knyttes til forseringssaken.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TE eller BH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>standard, forsering, endringsordre</t>
+          <t>forsering</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Setter tittel, Catenda-topic, prosjekt- og partsnavn og sakstype. En standardsak får grunnlaget i `utkast`; en forseringssak får forseringsdata fra `forsering_data`. En ukjent sakstype blir `standard`. Forretningsreglene kjøres ikke på første hendelse i en ny sak, bare rollekontrollen i ruta.</t>
+          <t>KOE-saken legges i listen over avslåtte fristkrav, om den ikke står der.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -8401,64 +8401,64 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Internt notat, synlig bare for forfatterens eget team. Er en hendelsestype i API-et, men lagres i `notat`, ikke i journalen.</t>
+          <t>En KOE-sak tas ut av forseringssaken.</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TE eller BH</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>valgt i hendelsen</t>
+          <t>ingen</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>standard, forsering, endringsordre</t>
+          <t>forsering</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Et notat er ikke et kontraktsvarsel.</t>
+          <t>Ingen. Appens egen registrering.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09; vedtak: MS-05</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Notatet flytter ikke sakens versjon, sendes ikke til Catenda og avvises uten entydig team (MS-05).</t>
+          <t>KOE-saken fjernes fra listen over avslåtte fristkrav.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>hendelse</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BH oppretter en endringsordresak med nummer, beskrivelse og KOE-saker som inngår.</t>
+          <t>Første hendelse i en sak: tittel, sakstype og kobling til Catenda. Feltene ligger på toppnivå i modellen og i `data` i journalen. Sender klienten dem i `data`, som skjemaet for ny sak gjør, lagres `data` slik klienten sendte den, også med nøkler modellen ikke kjenner (DM-06).</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>TE eller BH</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -8468,22 +8468,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>endringsordre</t>
+          <t>standard, forsering, endringsordre</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>§ 31.3.</t>
+          <t>Ingen. Appens egen registrering.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>kode: overskriften over EO-verdiene i EventType, og kategoritabellen (EO)</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`. Sakstypen settes også når hendelsen kommer i en KOE-sak, og ingen regel stopper det (DM-07).</t>
+          <t>Setter tittel, Catenda-topic, prosjekt- og partsnavn og sakstype. En standardsak får grunnlaget i `utkast`; en forseringssak får forseringsdata fra `forsering_data`. En ukjent sakstype blir `standard`. Forretningsreglene kjøres ikke på første hendelse i en ny sak, bare rollekontrollen i ruta.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -8495,59 +8495,59 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BH knytter en KOE-sak til endringsordren.</t>
+          <t>Internt notat, synlig bare for forfatterens eget team. Er en hendelsestype i API-et, men lagres i `notat`, ikke i journalen.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>TE eller BH</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ingen</t>
+          <t>valgt i hendelsen</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>endringsordre</t>
+          <t>standard, forsering, endringsordre</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Appens egen registrering.</t>
+          <t>Ingen. Et notat er ikke et kontraktsvarsel.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>oppdragsgiver, 29.09; vedtak: MS-05</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>KOE-saken legges til endringsordrens relaterte saker, om den ikke står der.</t>
+          <t>Ingen. Notatet flytter ikke sakens versjon, sendes ikke til Catenda og avvises uten entydig team (MS-05).</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>notat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BH tar en KOE-sak ut av endringsordren.</t>
+          <t>BH oppretter en endringsordresak med nummer, beskrivelse og KOE-saker som inngår.</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Appens egen registrering.</t>
+          <t>§ 31.3.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>oppdragsgiver, 29.09</t>
+          <t>kode: overskriften over EO-verdiene i EventType, og kategoritabellen (EO)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>KOE-saken fjernes fra endringsordrens relaterte saker.</t>
+          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`. Sakstypen settes også når hendelsen kommer i en KOE-sak, og ingen regel stopper det (DM-07).</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BH utsteder endringsordren formelt: beskrivelse, konsekvenser, vederlag og fristforlengelse. Proaktivt i en endringsordresak, eller reaktivt i en KOE-sak der alle aktive spor er godkjent.</t>
+          <t>BH knytter en KOE-sak til endringsordren.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -8609,22 +8609,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>endringsordre, standard</t>
+          <t>endringsordre</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>§ 31.3, med vederlag etter § 34 og frist etter § 33.</t>
+          <t>Ingen. Appens egen registrering.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>kode: backend/models/events.py (EOUtstedtData, VederlagKompensasjon)</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>I en endringsordresak bygges endringsordren fra hendelsen, med status `utstedt`. I en KOE-sak (reaktiv) blir grunnlaget `laast`, og vederlag og frist blir `godkjent` med beløp og dager fra endringsordren; spor som er `ikke_relevant` eller `trukket`, står. De utgåtte toppnivåfeltene `endelig_vederlag` og `endelig_frist_dager` leses av projeksjonen, men lagres ikke (DM-06).</t>
+          <t>KOE-saken legges til endringsordrens relaterte saker, om den ikke står der.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -8636,17 +8636,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TE aksepterer endringsordren.</t>
+          <t>BH tar en KOE-sak ut av endringsordren.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>§ 31.3.</t>
+          <t>Ingen. Appens egen registrering.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>kode: overskriften over EO-verdiene i EventType</t>
+          <t>oppdragsgiver, 29.09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Endringsordren blir `akseptert`, med TEs kommentar og dato. Saken får samlet status `LUKKET` (vedtaket om TFR-02, 23.09).</t>
+          <t>KOE-saken fjernes fra endringsordrens relaterte saker.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8683,17 +8683,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TE bestrider endringsordren. En endringsordre forhandles ikke; er TE uenig, føres det videre i en KOE (vedtaket om TFR-02, 23.09).</t>
+          <t>BH utsteder endringsordren formelt: beskrivelse, konsekvenser, vederlag og fristforlengelse. Proaktivt i en endringsordresak, eller reaktivt i en KOE-sak der alle aktive spor er godkjent.</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>BH</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>endringsordre</t>
+          <t>endringsordre, standard</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>§ 31.3.</t>
+          <t>§ 31.3, med vederlag etter § 34 og frist etter § 33.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>kode: overskriften over EO-verdiene i EventType</t>
+          <t>kode: backend/models/events.py (EOUtstedtData, VederlagKompensasjon)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Endringsordren blir `bestridt`, med TEs begrunnelse som kommentar. Saken får samlet status `LUKKET` (TFR-02).</t>
+          <t>I en endringsordresak bygges endringsordren fra hendelsen, med status `utstedt`. I en KOE-sak (reaktiv) blir grunnlaget `laast`, og vederlag og frist blir `godkjent` med beløp og dager fra endringsordren; spor som er `ikke_relevant` eller `trukket`, står. De utgåtte toppnivåfeltene `endelig_vederlag` og `endelig_frist_dager` leses av projeksjonen, men lagres ikke (DM-06).</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -8730,45 +8730,139 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>eo_akseptert</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>TE aksepterer endringsordren.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ingen</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>endringsordre</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>§ 31.3.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>kode: overskriften over EO-verdiene i EventType</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Endringsordren blir `akseptert`, med TEs kommentar og dato. Saken får samlet status `LUKKET` (vedtaket om TFR-02, 23.09).</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>eo_bestridt</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TE bestrider endringsordren. En endringsordre forhandles ikke; er TE uenig, føres det videre i en KOE (vedtaket om TFR-02, 23.09).</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ingen</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>endringsordre</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>§ 31.3.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>kode: overskriften over EO-verdiene i EventType</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Endringsordren blir `bestridt`, med TEs begrunnelse som kommentar. Saken får samlet status `LUKKET` (TFR-02).</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>eo_revidert</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>BH reviderer en utstedt eller bestridt endringsordre.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>BH</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>ingen</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>endringsordre</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>§ 31.3.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>kode: overskriften over EO-verdiene i EventType</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Revisjonsnummeret settes, status blir `revidert`, og TEs svar nullstilles. Beskrivelse, kompensasjon, fradrag, frist og sluttdato oppdateres fra `oppdatert_data` når de er satt; `oppdatert_data.vederlag` leses ikke.</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>hendelse</t>
         </is>
@@ -8785,7 +8879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E357"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11066,12 +11160,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_trukket</t>
+          <t>frist_innsigelse_sendt</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -11086,19 +11180,19 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Valgfri begrunnelse for tilbaketrekking</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_innsigelse_sendt</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_event_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -11108,7 +11202,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -11120,7 +11214,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_innsigelse_sendt</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -11147,7 +11241,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_innsigelse_sendt</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -11174,17 +11268,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>resultat</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>GrunnlagResponsResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11194,14 +11288,14 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av ansvarsgrunnlaget</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -11216,29 +11310,29 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurderingen</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>akseptert_kategori</t>
+          <t>svarfrist</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11248,24 +11342,24 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
+          <t>Valgfri svarfrist BH oppgir. Uten den gjelder «uten ugrunnet opphold»</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_varslet_i_tide</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11275,46 +11369,46 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_foresporsel_sendt</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag</t>
+          <t>frist_krav_trukket</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -11329,7 +11423,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Valgfri begrunnelse for tilbaketrekking</t>
         </is>
       </c>
     </row>
@@ -11341,39 +11435,39 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>grunnlag_event_id</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_event_id</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11390,17 +11484,17 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -11417,17 +11511,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>resultat</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>GrunnlagResponsResultat</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -11437,24 +11531,24 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BHs vurdering av ansvarsgrunnlaget</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>resultat</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>GrunnlagResponsResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -11464,19 +11558,19 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av ansvarsgrunnlaget</t>
+          <t>BHs begrunnelse for vurderingen</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>akseptert_kategori</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -11491,24 +11585,24 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurderingen</t>
+          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>akseptert_kategori</t>
+          <t>grunnlag_varslet_i_tide</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -11518,24 +11612,24 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
+          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_varslet_i_tide</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -11545,24 +11639,24 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -11572,34 +11666,34 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -11611,39 +11705,39 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>grunnlag_event_id</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -11660,17 +11754,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -11687,17 +11781,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>resultat</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>GrunnlagResponsResultat</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -11707,19 +11801,19 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BHs vurdering av ansvarsgrunnlaget</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -11734,19 +11828,19 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>BHs begrunnelse for vurderingen</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>vederlag_krav_id</t>
+          <t>akseptert_kategori</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -11761,24 +11855,24 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til vederlagskravet som besvares</t>
+          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>grunnlag_varslet_i_tide</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -11788,24 +11882,24 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_varslet_i_tide</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -11815,24 +11909,24 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -11842,34 +11936,34 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -11881,12 +11975,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>varsel_justert_ep_ok</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -11896,7 +11990,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11908,7 +12002,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -11923,7 +12017,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for vurdering av varsler/frister</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11935,12 +12029,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>aksepterer_metode</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -11950,7 +12044,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11962,12 +12056,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>oensket_metode</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -11977,7 +12071,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -11989,12 +12083,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ep_justering_akseptert</t>
+          <t>vederlag_krav_id</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -12004,7 +12098,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
+          <t>Event-ID til vederlagskravet som besvares</t>
         </is>
       </c>
     </row>
@@ -12016,12 +12110,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>hold_tilbake</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -12031,7 +12125,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Holder BH tilbake betaling? (§30.2)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -12043,12 +12137,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>vederlagsmetode</t>
+          <t>hovedkrav_varslet_i_tide</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -12058,7 +12152,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Hvilken metode BH legger til grunn (legacy)</t>
+          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
         </is>
       </c>
     </row>
@@ -12070,12 +12164,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_vurdering</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -12085,7 +12179,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av hovedkravet</t>
+          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12191,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_godkjent_belop</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -12112,7 +12206,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for hovedkravet i NOK</t>
+          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12218,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>rigg_vurdering</t>
+          <t>varsel_justert_ep_ok</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -12139,7 +12233,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av rigg/drift-kravet</t>
+          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12245,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>rigg_godkjent_belop</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -12166,7 +12260,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for rigg/drift i NOK</t>
+          <t>Begrunnelse for vurdering av varsler/frister</t>
         </is>
       </c>
     </row>
@@ -12178,12 +12272,12 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_vurdering</t>
+          <t>aksepterer_metode</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -12193,7 +12287,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av produktivitetskravet</t>
+          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12299,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_godkjent_belop</t>
+          <t>oensket_metode</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -12220,7 +12314,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for produktivitetstap i NOK</t>
+          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
         </is>
       </c>
     </row>
@@ -12232,12 +12326,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>ep_justering_akseptert</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -12247,7 +12341,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>BHs samlede vurdering av kravets størrelse</t>
+          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -12259,12 +12353,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>total_godkjent_belop</t>
+          <t>hold_tilbake</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -12274,7 +12368,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
+          <t>Holder BH tilbake betaling? (§30.2)</t>
         </is>
       </c>
     </row>
@@ -12286,12 +12380,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>total_krevd_belop</t>
+          <t>vederlagsmetode</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -12301,7 +12395,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Totalt krevd beløp i NOK</t>
+          <t>Hvilken metode BH legger til grunn (legacy)</t>
         </is>
       </c>
     </row>
@@ -12313,12 +12407,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>hovedkrav_vurdering</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -12328,7 +12422,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>BHs vurdering av hovedkravet</t>
         </is>
       </c>
     </row>
@@ -12340,12 +12434,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifikasjon</t>
+          <t>hovedkrav_godkjent_belop</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -12355,7 +12449,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
+          <t>Godkjent beløp for hovedkravet i NOK</t>
         </is>
       </c>
     </row>
@@ -12367,12 +12461,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>rigg_vurdering</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -12382,7 +12476,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>BHs vurdering av rigg/drift-kravet</t>
         </is>
       </c>
     </row>
@@ -12394,12 +12488,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>rigg_godkjent_belop</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -12409,7 +12503,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Godkjent beløp for rigg/drift i NOK</t>
         </is>
       </c>
     </row>
@@ -12421,12 +12515,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>produktivitet_vurdering</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -12436,7 +12530,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
+          <t>BHs vurdering av produktivitetskravet</t>
         </is>
       </c>
     </row>
@@ -12448,12 +12542,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>produktivitet_godkjent_belop</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -12463,7 +12557,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Godkjent beløp for produktivitetstap i NOK</t>
         </is>
       </c>
     </row>
@@ -12475,39 +12569,39 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>BHs samlede vurdering av kravets størrelse</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>total_godkjent_belop</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -12517,24 +12611,24 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>total_krevd_belop</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -12544,24 +12638,24 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Totalt krevd beløp i NOK</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -12571,19 +12665,19 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>frist_for_spesifikasjon</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -12598,24 +12692,24 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>vederlag_krav_id</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -12625,24 +12719,24 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til vederlagskravet som besvares</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -12652,24 +12746,24 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_varslet_i_tide</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -12679,24 +12773,24 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
+          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -12706,34 +12800,34 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -12745,12 +12839,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>varsel_justert_ep_ok</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -12760,7 +12854,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12866,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -12787,7 +12881,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for vurdering av varsler/frister</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12799,12 +12893,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>aksepterer_metode</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -12814,7 +12908,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12826,12 +12920,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>oensket_metode</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -12841,7 +12935,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -12853,12 +12947,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ep_justering_akseptert</t>
+          <t>vederlag_krav_id</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -12868,7 +12962,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
+          <t>Event-ID til vederlagskravet som besvares</t>
         </is>
       </c>
     </row>
@@ -12880,12 +12974,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>hold_tilbake</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -12895,7 +12989,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Holder BH tilbake betaling? (§30.2)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -12907,12 +13001,12 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>vederlagsmetode</t>
+          <t>hovedkrav_varslet_i_tide</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -12922,7 +13016,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Hvilken metode BH legger til grunn (legacy)</t>
+          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
         </is>
       </c>
     </row>
@@ -12934,12 +13028,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_vurdering</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -12949,7 +13043,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av hovedkravet</t>
+          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12961,12 +13055,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_godkjent_belop</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -12976,7 +13070,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for hovedkravet i NOK</t>
+          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12988,12 +13082,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>rigg_vurdering</t>
+          <t>varsel_justert_ep_ok</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -13003,7 +13097,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av rigg/drift-kravet</t>
+          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -13015,12 +13109,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>rigg_godkjent_belop</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -13030,7 +13124,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for rigg/drift i NOK</t>
+          <t>Begrunnelse for vurdering av varsler/frister</t>
         </is>
       </c>
     </row>
@@ -13042,12 +13136,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_vurdering</t>
+          <t>aksepterer_metode</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -13057,7 +13151,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av produktivitetskravet</t>
+          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
         </is>
       </c>
     </row>
@@ -13069,12 +13163,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_godkjent_belop</t>
+          <t>oensket_metode</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -13084,7 +13178,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for produktivitetstap i NOK</t>
+          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13190,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>ep_justering_akseptert</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -13111,7 +13205,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>BHs samlede vurdering av kravets størrelse</t>
+          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13217,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>total_godkjent_belop</t>
+          <t>hold_tilbake</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -13138,7 +13232,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
+          <t>Holder BH tilbake betaling? (§30.2)</t>
         </is>
       </c>
     </row>
@@ -13150,12 +13244,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>total_krevd_belop</t>
+          <t>vederlagsmetode</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -13165,7 +13259,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Totalt krevd beløp i NOK</t>
+          <t>Hvilken metode BH legger til grunn (legacy)</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13271,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>hovedkrav_vurdering</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -13192,7 +13286,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>BHs vurdering av hovedkravet</t>
         </is>
       </c>
     </row>
@@ -13204,12 +13298,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifikasjon</t>
+          <t>hovedkrav_godkjent_belop</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -13219,7 +13313,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
+          <t>Godkjent beløp for hovedkravet i NOK</t>
         </is>
       </c>
     </row>
@@ -13231,12 +13325,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>rigg_vurdering</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -13246,7 +13340,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>BHs vurdering av rigg/drift-kravet</t>
         </is>
       </c>
     </row>
@@ -13258,12 +13352,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>rigg_godkjent_belop</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -13273,7 +13367,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Godkjent beløp for rigg/drift i NOK</t>
         </is>
       </c>
     </row>
@@ -13285,12 +13379,12 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>produktivitet_vurdering</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -13300,7 +13394,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
+          <t>BHs vurdering av produktivitetskravet</t>
         </is>
       </c>
     </row>
@@ -13312,12 +13406,12 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>produktivitet_godkjent_belop</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -13327,7 +13421,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Godkjent beløp for produktivitetstap i NOK</t>
         </is>
       </c>
     </row>
@@ -13339,39 +13433,39 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>BHs samlede vurdering av kravets størrelse</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>total_godkjent_belop</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -13381,24 +13475,24 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>total_krevd_belop</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -13408,24 +13502,24 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Totalt krevd beløp i NOK</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -13435,19 +13529,19 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>frist_for_spesifikasjon</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13462,24 +13556,24 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -13489,24 +13583,24 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -13516,24 +13610,24 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -13543,24 +13637,24 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -13570,34 +13664,34 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -13609,12 +13703,12 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -13624,7 +13718,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13636,12 +13730,12 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -13651,7 +13745,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13663,12 +13757,12 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -13678,7 +13772,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13784,12 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -13705,7 +13799,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13717,12 +13811,12 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -13732,7 +13826,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -13744,7 +13838,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -13759,7 +13853,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -13771,12 +13865,12 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -13786,7 +13880,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -13798,12 +13892,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -13813,7 +13907,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -13825,12 +13919,12 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -13840,7 +13934,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -13852,12 +13946,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>har_bh_foresporsel</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -13867,7 +13961,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
         </is>
       </c>
     </row>
@@ -13879,12 +13973,12 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>dato_bh_foresporsel</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -13894,7 +13988,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
         </is>
       </c>
     </row>
@@ -13906,12 +14000,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -13921,7 +14015,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -13933,12 +14027,12 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -13948,7 +14042,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -13960,39 +14054,39 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -14002,24 +14096,24 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -14029,24 +14123,24 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -14056,19 +14150,19 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -14083,24 +14177,24 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -14110,24 +14204,24 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -14137,24 +14231,24 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -14164,24 +14258,24 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -14191,34 +14285,34 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14324,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -14245,7 +14339,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14257,12 +14351,12 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -14272,7 +14366,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14284,12 +14378,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -14299,7 +14393,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14311,12 +14405,12 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -14326,7 +14420,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14338,12 +14432,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -14353,7 +14447,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14459,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -14380,7 +14474,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -14392,12 +14486,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -14407,7 +14501,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14419,12 +14513,12 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -14434,7 +14528,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -14446,12 +14540,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -14461,7 +14555,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14567,12 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>har_bh_foresporsel</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -14488,7 +14582,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14594,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>dato_bh_foresporsel</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -14515,7 +14609,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
         </is>
       </c>
     </row>
@@ -14527,12 +14621,12 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -14542,7 +14636,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14554,12 +14648,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -14569,7 +14663,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14581,39 +14675,39 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -14623,46 +14717,46 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Valgfri kommentar fra entreprenør</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -14672,24 +14766,24 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til fristkravet som ble avslått</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_id</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -14699,83 +14793,83 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>estimert_kostnad</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Estimert kostnad for forsering i NOK</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for forsering</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>bekreft_30_prosent</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -14785,19 +14879,19 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>dato_iverksettelse</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -14807,29 +14901,29 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>avslatte_dager</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -14839,154 +14933,154 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Antall dager som ble avslått av BH</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>dagmulktsats</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
+          <t>Valgfri kommentar fra entreprenør</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_avslag_trigger</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>vurdering_per_sak</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>liste av objekt</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av forseringsrett per sak</t>
+          <t>Event-ID til fristkravet som ble avslått</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>dager_med_forseringsrett</t>
+          <t>respons_frist_id</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Antall dager BH mener TE har forseringsrett for</t>
+          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_fortsatt_gyldig</t>
+          <t>estimert_kostnad</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
+          <t>Estimert kostnad for forsering i NOK</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_begrunnelse</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -14996,24 +15090,24 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
+          <t>Begrunnelse for forsering</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_overholdt</t>
+          <t>bekreft_30_prosent</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -15028,19 +15122,19 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
+          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_begrunnelse</t>
+          <t>dato_iverksettelse</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -15050,29 +15144,29 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
+          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>aksepterer</t>
+          <t>avslatte_dager</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -15082,19 +15176,19 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>BH aksepterer forsering</t>
+          <t>Antall dager som ble avslått av BH</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>godkjent_kostnad</t>
+          <t>dagmulktsats</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -15104,39 +15198,39 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
+          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>grunnlag_avslag_trigger</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for aksept/avslag</t>
+          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
         </is>
       </c>
     </row>
@@ -15148,12 +15242,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>vurdering_per_sak</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av objekt</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -15163,7 +15257,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Om rigg/drift-varslet var rettidig</t>
+          <t>BHs vurdering av forseringsrett per sak</t>
         </is>
       </c>
     </row>
@@ -15175,12 +15269,12 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>dager_med_forseringsrett</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -15190,7 +15284,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Om produktivitets-varslet var rettidig</t>
+          <t>Antall dager BH mener TE har forseringsrett for</t>
         </is>
       </c>
     </row>
@@ -15202,12 +15296,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>godkjent_rigg_drift</t>
+          <t>grunnlag_fortsatt_gyldig</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -15217,7 +15311,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Godkjent rigg/drift-beløp</t>
+          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
         </is>
       </c>
     </row>
@@ -15229,12 +15323,12 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>godkjent_produktivitet</t>
+          <t>grunnlag_begrunnelse</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -15244,7 +15338,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Godkjent produktivitetsbeløp</t>
+          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
         </is>
       </c>
     </row>
@@ -15256,12 +15350,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>trettiprosent_overholdt</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -15271,7 +15365,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
+          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15377,12 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>trettiprosent_begrunnelse</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -15298,7 +15392,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp</t>
+          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
         </is>
       </c>
     </row>
@@ -15310,93 +15404,93 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>aksepterer</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for subsidiært standpunkt</t>
+          <t>BH aksepterer forsering</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>dato_stoppet</t>
+          <t>godkjent_kostnad</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
+          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader ved stopp i NOK</t>
+          <t>BH's begrunnelse for aksept/avslag</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -15406,51 +15500,51 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for stopp</t>
+          <t>Om rigg/drift-varslet var rettidig</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader i NOK</t>
+          <t>Om produktivitets-varslet var rettidig</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>godkjent_rigg_drift</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -15460,51 +15554,51 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Kommentar til kostnadsoppdatering</t>
+          <t>Godkjent rigg/drift-beløp</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>godkjent_produktivitet</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Godkjent produktivitetsbeløp</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -15514,46 +15608,46 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Subsidiært godkjent beløp</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -15568,19 +15662,19 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Begrunnelse for subsidiært standpunkt</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>dato_stoppet</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -15590,51 +15684,51 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel</t>
+          <t>Påløpte kostnader ved stopp i NOK</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15649,46 +15743,46 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Begrunnelse for stopp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>sakstype</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
+          <t>Påløpte kostnader i NOK</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_navn</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -15703,19 +15797,19 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Prosjektnavn fra Catenda</t>
+          <t>Kommentar til kostnadsoppdatering</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>byggherre</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -15725,24 +15819,24 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Byggherre (BH) - fra topic custom field</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>leverandor</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15757,78 +15851,78 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>forsering_data</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>objekt</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
+          <t>koe_tittel</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
           <t>tekst</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>tekst</t>
-        </is>
-      </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Notat-tekst</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -15838,19 +15932,19 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Hvilket spor notatet gjelder</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -15865,19 +15959,19 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Sakstittel</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -15887,29 +15981,29 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>sakstype</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -15919,19 +16013,19 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>prosjekt_navn</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -15946,19 +16040,19 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel for EO-saken</t>
+          <t>Prosjektnavn fra Catenda</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>byggherre</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -15973,19 +16067,19 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Byggherre (BH) - fra topic custom field</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>leverandor</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16000,46 +16094,46 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>forsering_data</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>objekt</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16049,51 +16143,51 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Notat-tekst</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Hvilket spor notatet gjelder</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16103,24 +16197,24 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -16135,24 +16229,24 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -16162,19 +16256,19 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -16184,29 +16278,29 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Sakstittel for EO-saken</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -16216,24 +16310,24 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -16243,19 +16337,19 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16265,29 +16359,29 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -16297,19 +16391,19 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -16319,29 +16413,29 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -16351,7 +16445,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
@@ -16363,22 +16457,22 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
@@ -16390,12 +16484,12 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -16405,7 +16499,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -16417,22 +16511,22 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -16444,12 +16538,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -16459,7 +16553,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -16471,12 +16565,12 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -16486,7 +16580,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -16498,12 +16592,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -16513,7 +16607,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -16525,22 +16619,22 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -16552,22 +16646,22 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -16579,39 +16673,39 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>akseptert</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -16621,24 +16715,24 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>Om TE aksepterer</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -16648,46 +16742,46 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>TEs kommentar</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for bestridelse</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>nytt_koe_sak_id</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -16702,100 +16796,100 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>ny_revisjon_nummer</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Nytt revisjonsnummer</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>endringer_beskrivelse</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringene</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>oppdatert_data</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>EOUtstedtData</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Oppdatert EO-data (hvis endret)</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>sha</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -16805,24 +16899,24 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>SHA-konsekvenser</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>kvalitet</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -16832,24 +16926,24 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Kvalitetskonsekvenser</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>fremdrift</t>
+          <t>akseptert</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -16864,24 +16958,24 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Fremdriftskonsekvenser</t>
+          <t>Om TE aksepterer</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>pris</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -16891,46 +16985,46 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Priskonsekvenser</t>
+          <t>TEs kommentar</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>annet</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Andre konsekvenser</t>
+          <t>Begrunnelse for bestridelse</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>nytt_koe_sak_id</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -16940,24 +17034,24 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>ny_revisjon_nummer</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -16967,24 +17061,24 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Nytt revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>endringer_beskrivelse</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -16999,24 +17093,24 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Beskrivelse av endringene</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>oppdatert_data</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>EOUtstedtData</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -17026,24 +17120,24 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Oppdatert EO-data (hvis endret)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>sha</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -17053,24 +17147,24 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>SHA-konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>kvalitet</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -17080,24 +17174,24 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>Kvalitetskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>fremdrift</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -17107,24 +17201,24 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>Fremdriftskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>pris</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
@@ -17134,24 +17228,24 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>Priskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>annet</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -17161,7 +17255,7 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Andre konsekvenser</t>
         </is>
       </c>
     </row>
@@ -17173,22 +17267,22 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
@@ -17200,12 +17294,12 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -17215,7 +17309,7 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -17227,22 +17321,22 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -17254,12 +17348,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -17269,7 +17363,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -17281,12 +17375,12 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -17296,7 +17390,7 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -17308,12 +17402,12 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -17323,7 +17417,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -17335,22 +17429,22 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -17362,22 +17456,22 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -17389,39 +17483,39 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -17431,24 +17525,24 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -17458,24 +17552,24 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -17485,19 +17579,19 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -17512,154 +17606,154 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>navn</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>rolle</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>adresse</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>orgnr</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>sakId</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -17669,7 +17763,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17681,12 +17775,12 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>eventId</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -17696,7 +17790,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17708,12 +17802,12 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>sporType</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -17723,7 +17817,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17735,12 +17829,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>dato</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -17750,7 +17844,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17762,12 +17856,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>kravDato</t>
+          <t>navn</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -17777,7 +17871,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17789,12 +17883,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>rolle</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -17816,12 +17910,12 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>originalTekst</t>
+          <t>adresse</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -17831,7 +17925,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17843,12 +17937,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>redigertTekst</t>
+          <t>orgnr</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -17858,7 +17952,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17870,17 +17964,17 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>innledning</t>
+          <t>sakId</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
@@ -17897,17 +17991,17 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -17924,17 +18018,17 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>avslutning</t>
+          <t>eventId</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
@@ -17951,12 +18045,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>sporType</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -17978,17 +18072,17 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>mottaker</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
@@ -18005,22 +18099,22 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>avsender</t>
+          <t>kravDato</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18032,17 +18126,17 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>referanser</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>LetterReferences</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
@@ -18059,17 +18153,17 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>seksjoner</t>
+          <t>originalTekst</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>LetterSections</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -18086,120 +18180,120 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>redigertTekst</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>innledning</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>belop</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>Beløp for dette særskilte kravet</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>dato_klar_over</t>
+          <t>avslutning</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>dato_sendt</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -18209,56 +18303,56 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>mottaker</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>avsender</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -18268,78 +18362,78 @@
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>belop_direkte</t>
+          <t>referanser</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>LetterReferences</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>kostnads_overslag</t>
+          <t>seksjoner</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>LetterSections</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -18349,24 +18443,24 @@
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
+          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -18376,19 +18470,19 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
+          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>belop</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -18398,37 +18492,280 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
+          <t>Beløp for dette særskilte kravet</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
+          <t>Delmodell SaerskiltKravItem</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>dato_klar_over</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>tekst</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VarselInfo</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>dato_sendt</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>tekst</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VarselInfo</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>liste av tekst</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
           <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
-      <c r="B357" s="2" t="inlineStr">
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>VederlagsMetode</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>belop_direkte</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>kostnads_overslag</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>fradrag_belop</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>er_estimat</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>ja/nei</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>netto_belop</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>beregnet</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
         <is>
           <t>krevd_belop</t>
         </is>
       </c>
-      <c r="C357" s="2" t="inlineStr">
+      <c r="C366" s="2" t="inlineStr">
         <is>
           <t>tall</t>
         </is>
       </c>
-      <c r="D357" s="2" t="inlineStr">
+      <c r="D366" s="2" t="inlineStr">
         <is>
           <t>beregnet</t>
         </is>
       </c>
-      <c r="E357" s="2" t="inlineStr">
+      <c r="E366" s="2" t="inlineStr">
         <is>
           <t>Alias for netto_belop - brukes i state-modellen. Returnerer det totale kravet/kompensasjonen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Versjonen øker, og kravet settes på nytt. Et spor som er `avslatt`, `under_forhandling` eller `delvis_godkjent`, går tilbake til `sendt`.</t>
+          <t>Versjonen øker, og kravet settes på nytt. Et spor som er `avslatt`, `under_forhandling` eller `delvis_godkjent`, går tilbake til `sendt`. Har kravet dager og venter en forespørsel på svar, merkes kravet som svaret på den (`foresporsel_besvart_krav_id`, § 33.6.2 fjerde ledd).</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar på et krav uten dager avvises (§ 33.7, TFR-06); før det sendes `frist_innsigelse_sendt` eller `frist_foresporsel_sendt`.</t>
+          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar på et krav uten dager avvises (§ 33.7, TFR-06); før det sendes `frist_innsigelse_sendt` eller `frist_foresporsel_sendt`. På kravet som besvarte forespørselen med dager, avvises `spesifisert_krav_ok=false` (§ 33.6.2 fjerde ledd, #172). En senere revisjon av kravet kan møtes med § 33.6.1 (oppdragsgiver 04.10). Der § 33.6.1-spørsmålet stilles, må `spesifisert_krav_ok` sendes; ellers ville modellens standardverdi `true` bli lagret som BHs vurdering.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_frist`, også sperren mot et krav uten dager. Uten `beregnings_resultat` står statusen.</t>
+          <t>Samme behandling som `respons_frist`, også sperren mot et krav uten dager og mot § 33.6.1 på kravet som besvarte forespørselen. Uten `beregnings_resultat` står statusen.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -7872,7 +7872,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>`godkjent` gir `laast` når grunnlaget ikke er merket for sent varslet; merket for sent varslet gir `under_forhandling`. `avslatt` gir `avslatt`, og `frafalt` gir `trukket`. Svaret knyttes til gjeldende versjon av grunnlaget.</t>
+          <t>`godkjent` gir `laast` når grunnlaget ikke er merket for sent varslet; merket for sent varslet gir `under_forhandling`. `avslatt` gir `avslatt`, og `frafalt` gir `trukket`. Svaret knyttes til gjeldende versjon av grunnlaget. Serveren avviser et svar med en annen `regelversjon` enn sin egen, `grunnlag_varslet_i_tide` utenfor § 32.2 og `frafalt` utenfor pålegg (B-13).</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`; `hold_tilbake` gir `under_behandling`. Godkjent beløp, metode, varselvurderinger og subsidiært standpunkt settes. Resultatet lagres slik det er sendt, også når vurderingene i samme svar gir et annet (BR-01).</t>
+          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`; `hold_tilbake` gir `under_behandling`. Godkjent beløp, metode, varselvurderinger og subsidiært standpunkt settes. Serveren regner ut resultat, beløp og subsidiært standpunkt av vurderingene og kravet, og avviser et svar der klientens verdier, eller `regelversjon`, ikke er like serverens (B-13, BR-01). Hele svaret kreves. Serverens verdier, avrundet til øre, lagres.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_vederlag`. Uten `beregnings_resultat` står statusen, og bare feltene som sendes, endres.</t>
+          <t>Samme behandling som `respons_vederlag`, også kravet om hele svaret (B-13).</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar på et krav uten dager avvises (§ 33.7, TFR-06); før det sendes `frist_innsigelse_sendt` eller `frist_foresporsel_sendt`. På kravet som besvarte forespørselen med dager, avvises `spesifisert_krav_ok=false` (§ 33.6.2 fjerde ledd, #172). En senere revisjon av kravet kan møtes med § 33.6.1 (oppdragsgiver 04.10). Der § 33.6.1-spørsmålet stilles, må `spesifisert_krav_ok` sendes; ellers ville modellens standardverdi `true` bli lagret som BHs vurdering.</t>
+          <t>Status følger `beregnings_resultat`: `godkjent`, `delvis_godkjent` eller `avslatt`. Godkjente dager, ny sluttdato, varselvurderinger, vilkåret og subsidiært standpunkt settes. Et svar på et krav uten dager avvises (§ 33.7, TFR-06); før det sendes `frist_innsigelse_sendt` eller `frist_foresporsel_sendt`. Serveren regner ut resultat, dager og subsidiært standpunkt av vurderingene og kravet, og avviser et svar der klientens verdier, eller `regelversjon`, ikke er like serverens (B-13, BR-01). Hele svaret kreves: et varselspørsmål som stilles, må besvares, også `spesifisert_krav_ok`, som modellen ellers ville satt til `true`. På kravet som besvarte forespørselen med dager, avvises `spesifisert_krav_ok=false` (§ 33.6.2 fjerde ledd, #172). En senere revisjon av kravet kan møtes med § 33.6.1 (oppdragsgiver 04.10).</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Samme behandling som `respons_frist`, også sperren mot et krav uten dager og mot § 33.6.1 på kravet som besvarte forespørselen. Uten `beregnings_resultat` står statusen.</t>
+          <t>Samme behandling som `respons_frist`, også sperren mot et krav uten dager, mot § 33.6.1 på kravet som besvarte forespørselen, og kravet om hele svaret (B-13).</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11489,12 +11489,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -11516,12 +11516,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>resultat</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>GrunnlagResponsResultat</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av ansvarsgrunnlaget</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>resultat</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>GrunnlagResponsResultat</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurderingen</t>
+          <t>BHs vurdering av ansvarsgrunnlaget</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>akseptert_kategori</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
+          <t>BHs begrunnelse for vurderingen</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11597,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_varslet_i_tide</t>
+          <t>akseptert_kategori</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
+          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
         </is>
       </c>
     </row>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>grunnlag_varslet_i_tide</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
         </is>
       </c>
     </row>
@@ -11651,12 +11651,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -11678,49 +11678,49 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>respons_grunnlag_oppdatert</t>
+          <t>respons_grunnlag</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_event_id</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -11732,12 +11732,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>grunnlag_event_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -11786,12 +11786,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>resultat</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>GrunnlagResponsResultat</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av ansvarsgrunnlaget</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -11813,12 +11813,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurderingen</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11840,12 +11840,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>akseptert_kategori</t>
+          <t>resultat</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>GrunnlagResponsResultat</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
+          <t>BHs vurdering av ansvarsgrunnlaget</t>
         </is>
       </c>
     </row>
@@ -11867,12 +11867,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_varslet_i_tide</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
+          <t>BHs begrunnelse for vurderingen</t>
         </is>
       </c>
     </row>
@@ -11894,12 +11894,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>akseptert_kategori</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>BH kan akseptere men kategorisere annerledes (f.eks. fra 'prosjektering' til 'arbeidsgrunnlag')</t>
         </is>
       </c>
     </row>
@@ -11921,12 +11921,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>grunnlag_varslet_i_tide</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>§32.2: Var grunnlagsvarselet rettidig? Kun relevant for ENDRING-kategorien.</t>
         </is>
       </c>
     </row>
@@ -11948,39 +11948,39 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -11990,34 +11990,34 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag</t>
+          <t>respons_grunnlag_oppdatert</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12083,12 +12083,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>vederlag_krav_id</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til vederlagskravet som besvares</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -12137,12 +12137,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_varslet_i_tide</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -12164,12 +12164,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>vederlag_krav_id</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
+          <t>Event-ID til vederlagskravet som besvares</t>
         </is>
       </c>
     </row>
@@ -12191,12 +12191,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>varsel_justert_ep_ok</t>
+          <t>hovedkrav_varslet_i_tide</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
+          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
         </is>
       </c>
     </row>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for vurdering av varsler/frister</t>
+          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>aksepterer_metode</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
+          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -12299,12 +12299,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>oensket_metode</t>
+          <t>varsel_justert_ep_ok</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -12314,7 +12314,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
+          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ep_justering_akseptert</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
+          <t>Begrunnelse for vurdering av varsler/frister</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>hold_tilbake</t>
+          <t>aksepterer_metode</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Holder BH tilbake betaling? (§30.2)</t>
+          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12380,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>vederlagsmetode</t>
+          <t>oensket_metode</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Hvilken metode BH legger til grunn (legacy)</t>
+          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
         </is>
       </c>
     </row>
@@ -12407,12 +12407,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_vurdering</t>
+          <t>ep_justering_akseptert</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av hovedkravet</t>
+          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -12434,12 +12434,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_godkjent_belop</t>
+          <t>hold_tilbake</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for hovedkravet i NOK</t>
+          <t>Holder BH tilbake betaling? (§30.2)</t>
         </is>
       </c>
     </row>
@@ -12461,12 +12461,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>rigg_vurdering</t>
+          <t>vederlagsmetode</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av rigg/drift-kravet</t>
+          <t>Hvilken metode BH legger til grunn (legacy)</t>
         </is>
       </c>
     </row>
@@ -12488,12 +12488,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>rigg_godkjent_belop</t>
+          <t>hovedkrav_vurdering</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for rigg/drift i NOK</t>
+          <t>BHs vurdering av hovedkravet</t>
         </is>
       </c>
     </row>
@@ -12515,12 +12515,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_vurdering</t>
+          <t>hovedkrav_godkjent_belop</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av produktivitetskravet</t>
+          <t>Godkjent beløp for hovedkravet i NOK</t>
         </is>
       </c>
     </row>
@@ -12542,12 +12542,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_godkjent_belop</t>
+          <t>rigg_vurdering</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for produktivitetstap i NOK</t>
+          <t>BHs vurdering av rigg/drift-kravet</t>
         </is>
       </c>
     </row>
@@ -12569,12 +12569,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>rigg_godkjent_belop</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>BHs samlede vurdering av kravets størrelse</t>
+          <t>Godkjent beløp for rigg/drift i NOK</t>
         </is>
       </c>
     </row>
@@ -12596,12 +12596,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>total_godkjent_belop</t>
+          <t>produktivitet_vurdering</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
+          <t>BHs vurdering av produktivitetskravet</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>total_krevd_belop</t>
+          <t>produktivitet_godkjent_belop</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Totalt krevd beløp i NOK</t>
+          <t>Godkjent beløp for produktivitetstap i NOK</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>BHs samlede vurdering av kravets størrelse</t>
         </is>
       </c>
     </row>
@@ -12677,12 +12677,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifikasjon</t>
+          <t>total_godkjent_belop</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
+          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
         </is>
       </c>
     </row>
@@ -12704,12 +12704,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>total_krevd_belop</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Totalt krevd beløp i NOK</t>
         </is>
       </c>
     </row>
@@ -12731,12 +12731,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -12758,12 +12758,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>frist_for_spesifikasjon</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -12785,12 +12785,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -12812,39 +12812,39 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -12854,19 +12854,19 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -12881,34 +12881,34 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>respons_vederlag_oppdatert</t>
+          <t>respons_vederlag</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -12920,12 +12920,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12947,7 +12947,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>vederlag_krav_id</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til vederlagskravet som besvares</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12974,12 +12974,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_varslet_i_tide</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -13028,12 +13028,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -13055,12 +13055,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>vederlag_krav_id</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
+          <t>Event-ID til vederlagskravet som besvares</t>
         </is>
       </c>
     </row>
@@ -13082,12 +13082,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>varsel_justert_ep_ok</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -13109,12 +13109,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>hovedkrav_varslet_i_tide</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for vurdering av varsler/frister</t>
+          <t>Er vederlagskravet varslet i tide? (§34.1.2) - kun relevant for SVIKT/ANDRE</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>aksepterer_metode</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
+          <t>Er rigg/drift-kravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -13163,12 +13163,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>oensket_metode</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
+          <t>Er produktivitetskravet varslet i tide? (§34.1.3)</t>
         </is>
       </c>
     </row>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ep_justering_akseptert</t>
+          <t>varsel_justert_ep_ok</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
+          <t>Er det varslet om justerte enhetspriser uten ugrunnet opphold? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>hold_tilbake</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Holder BH tilbake betaling? (§30.2)</t>
+          <t>Begrunnelse for vurdering av varsler/frister</t>
         </is>
       </c>
     </row>
@@ -13244,12 +13244,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>vederlagsmetode</t>
+          <t>aksepterer_metode</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Hvilken metode BH legger til grunn (legacy)</t>
+          <t>Aksepterer BH den foreslåtte vederlagsmetoden?</t>
         </is>
       </c>
     </row>
@@ -13271,12 +13271,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_vurdering</t>
+          <t>oensket_metode</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av hovedkravet</t>
+          <t>Metode BH ønsker dersom foreslått metode ikke aksepteres</t>
         </is>
       </c>
     </row>
@@ -13298,12 +13298,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>hovedkrav_godkjent_belop</t>
+          <t>ep_justering_akseptert</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for hovedkravet i NOK</t>
+          <t>Aksepterer BH justering av enhetspriser? (§34.3.3)</t>
         </is>
       </c>
     </row>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>rigg_vurdering</t>
+          <t>hold_tilbake</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>BelopVurdering</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av rigg/drift-kravet</t>
+          <t>Holder BH tilbake betaling? (§30.2)</t>
         </is>
       </c>
     </row>
@@ -13352,12 +13352,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>rigg_godkjent_belop</t>
+          <t>vederlagsmetode</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for rigg/drift i NOK</t>
+          <t>Hvilken metode BH legger til grunn (legacy)</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_vurdering</t>
+          <t>hovedkrav_vurdering</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av produktivitetskravet</t>
+          <t>BHs vurdering av hovedkravet</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_godkjent_belop</t>
+          <t>hovedkrav_godkjent_belop</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Godkjent beløp for produktivitetstap i NOK</t>
+          <t>Godkjent beløp for hovedkravet i NOK</t>
         </is>
       </c>
     </row>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>rigg_vurdering</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>BHs samlede vurdering av kravets størrelse</t>
+          <t>BHs vurdering av rigg/drift-kravet</t>
         </is>
       </c>
     </row>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>total_godkjent_belop</t>
+          <t>rigg_godkjent_belop</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
+          <t>Godkjent beløp for rigg/drift i NOK</t>
         </is>
       </c>
     </row>
@@ -13487,12 +13487,12 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>total_krevd_belop</t>
+          <t>produktivitet_vurdering</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>BelopVurdering</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Totalt krevd beløp i NOK</t>
+          <t>BHs vurdering av produktivitetskravet</t>
         </is>
       </c>
     </row>
@@ -13514,12 +13514,12 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>produktivitet_godkjent_belop</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Godkjent beløp for produktivitetstap i NOK</t>
         </is>
       </c>
     </row>
@@ -13541,12 +13541,12 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifikasjon</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
+          <t>BHs samlede vurdering av kravets størrelse</t>
         </is>
       </c>
     </row>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>total_godkjent_belop</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Totalt godkjent beløp i NOK (hovedkrav + særskilte krav)</t>
         </is>
       </c>
     </row>
@@ -13595,12 +13595,12 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>total_krevd_belop</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>VederlagBeregningResultat</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Totalt krevd beløp i NOK</t>
         </is>
       </c>
     </row>
@@ -13622,12 +13622,12 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>frist_for_spesifikasjon</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -13676,39 +13676,39 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagBeregningResultat</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -13718,24 +13718,24 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -13745,24 +13745,24 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Subsidiært godkjent beløp i NOK (totalt)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -13772,34 +13772,34 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_vederlag_oppdatert</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13838,12 +13838,12 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13865,12 +13865,12 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -13892,12 +13892,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -14000,12 +14000,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -14054,12 +14054,12 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14081,12 +14081,12 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>har_bh_foresporsel</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
         </is>
       </c>
     </row>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>dato_bh_foresporsel</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14189,12 +14189,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
@@ -14216,12 +14216,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
@@ -14243,12 +14243,12 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14270,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -14297,39 +14297,39 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -14339,24 +14339,24 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -14366,24 +14366,24 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -14393,19 +14393,19 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -14420,34 +14420,34 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>respons_frist</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -14459,12 +14459,12 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -14540,12 +14540,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -14702,12 +14702,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14729,12 +14729,12 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>har_bh_foresporsel</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>dato_bh_foresporsel</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14810,12 +14810,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14918,34 +14918,34 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -14960,132 +14960,132 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Valgfri kommentar fra entreprenør</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til fristkravet som ble avslått</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_id</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>estimert_kostnad</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Estimert kostnad for forsering i NOK</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -15095,24 +15095,24 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for forsering</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>bekreft_30_prosent</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -15122,24 +15122,24 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
+          <t>Valgfri kommentar fra entreprenør</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>dato_iverksettelse</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
@@ -15161,12 +15161,12 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>avslatte_dager</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Antall dager som ble avslått av BH</t>
+          <t>Event-ID til fristkravet som ble avslått</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15188,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>dagmulktsats</t>
+          <t>respons_frist_id</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
+          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
         </is>
       </c>
     </row>
@@ -15215,66 +15215,66 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_avslag_trigger</t>
+          <t>estimert_kostnad</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
+          <t>Estimert kostnad for forsering i NOK</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>vurdering_per_sak</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>liste av objekt</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av forseringsrett per sak</t>
+          <t>Begrunnelse for forsering</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>dager_med_forseringsrett</t>
+          <t>bekreft_30_prosent</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -15284,105 +15284,105 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Antall dager BH mener TE har forseringsrett for</t>
+          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_fortsatt_gyldig</t>
+          <t>dato_iverksettelse</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
+          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_begrunnelse</t>
+          <t>avslatte_dager</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
+          <t>Antall dager som ble avslått av BH</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_overholdt</t>
+          <t>dagmulktsats</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
+          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_begrunnelse</t>
+          <t>grunnlag_avslag_trigger</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
+          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
         </is>
       </c>
     </row>
@@ -15404,22 +15404,22 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>aksepterer</t>
+          <t>vurdering_per_sak</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av objekt</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>BH aksepterer forsering</t>
+          <t>BHs vurdering av forseringsrett per sak</t>
         </is>
       </c>
     </row>
@@ -15431,12 +15431,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>godkjent_kostnad</t>
+          <t>dager_med_forseringsrett</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
+          <t>Antall dager BH mener TE har forseringsrett for</t>
         </is>
       </c>
     </row>
@@ -15458,22 +15458,22 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>grunnlag_fortsatt_gyldig</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for aksept/avslag</t>
+          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
         </is>
       </c>
     </row>
@@ -15485,12 +15485,12 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>grunnlag_begrunnelse</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Om rigg/drift-varslet var rettidig</t>
+          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>trettiprosent_overholdt</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Om produktivitets-varslet var rettidig</t>
+          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
         </is>
       </c>
     </row>
@@ -15539,12 +15539,12 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>godkjent_rigg_drift</t>
+          <t>trettiprosent_begrunnelse</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Godkjent rigg/drift-beløp</t>
+          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
         </is>
       </c>
     </row>
@@ -15566,22 +15566,22 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>godkjent_produktivitet</t>
+          <t>aksepterer</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Godkjent produktivitetsbeløp</t>
+          <t>BH aksepterer forsering</t>
         </is>
       </c>
     </row>
@@ -15593,12 +15593,12 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>godkjent_kostnad</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
+          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
         </is>
       </c>
     </row>
@@ -15620,22 +15620,22 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp</t>
+          <t>BH's begrunnelse for aksept/avslag</t>
         </is>
       </c>
     </row>
@@ -15647,12 +15647,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -15662,46 +15662,46 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for subsidiært standpunkt</t>
+          <t>Om rigg/drift-varslet var rettidig</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>dato_stoppet</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
+          <t>Om produktivitets-varslet var rettidig</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>godkjent_rigg_drift</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -15716,24 +15716,24 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader ved stopp i NOK</t>
+          <t>Godkjent rigg/drift-beløp</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>godkjent_produktivitet</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -15743,51 +15743,51 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for stopp</t>
+          <t>Godkjent produktivitetsbeløp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader i NOK</t>
+          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -15797,19 +15797,19 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Kommentar til kostnadsoppdatering</t>
+          <t>Subsidiært godkjent beløp</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -15819,24 +15819,24 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Begrunnelse for subsidiært standpunkt</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>dato_stoppet</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15846,51 +15846,51 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Påløpte kostnader ved stopp i NOK</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -15905,46 +15905,46 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Begrunnelse for stopp</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Påløpte kostnader i NOK</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -15954,24 +15954,24 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel</t>
+          <t>Kommentar til kostnadsoppdatering</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -15981,24 +15981,24 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>sakstype</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16013,19 +16013,19 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_navn</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16035,24 +16035,24 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Prosjektnavn fra Catenda</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>byggherre</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Byggherre (BH) - fra topic custom field</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>leverandor</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
@@ -16106,66 +16106,66 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>forsering_data</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>objekt</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
+          <t>Sakstittel</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
+          <t>catenda_topic_id</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
           <t>tekst</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>tekst</t>
-        </is>
-      </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Notat-tekst</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>sakstype</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -16175,19 +16175,19 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Hvilket spor notatet gjelder</t>
+          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>prosjekt_navn</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16197,24 +16197,24 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Prosjektnavn fra Catenda</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>byggherre</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -16224,29 +16224,29 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Byggherre (BH) - fra topic custom field</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>leverandor</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -16256,24 +16256,24 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>forsering_data</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>objekt</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -16283,19 +16283,19 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel for EO-saken</t>
+          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -16305,29 +16305,29 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Notat-tekst</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -16337,19 +16337,19 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Hvilket spor notatet gjelder</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16364,19 +16364,19 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -16386,51 +16386,51 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -16445,19 +16445,19 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Sakstittel for EO-saken</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -16467,29 +16467,29 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -16499,19 +16499,19 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -16526,24 +16526,24 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -16553,46 +16553,46 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
@@ -16619,22 +16619,22 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
@@ -16646,12 +16646,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -16673,22 +16673,22 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -16700,12 +16700,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -16727,12 +16727,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -16754,12 +16754,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -16781,12 +16781,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -16808,12 +16808,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -16835,12 +16835,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -16872,12 +16872,12 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -16899,12 +16899,12 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -16916,39 +16916,39 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>akseptert</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
@@ -16958,24 +16958,24 @@
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Om TE aksepterer</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -16985,132 +16985,132 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>TEs kommentar</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for bestridelse</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>nytt_koe_sak_id</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>ny_revisjon_nummer</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Nytt revisjonsnummer</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>endringer_beskrivelse</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringene</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>oppdatert_data</t>
+          <t>akseptert</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>EOUtstedtData</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
@@ -17120,24 +17120,24 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Oppdatert EO-data (hvis endret)</t>
+          <t>Om TE aksepterer</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>sha</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -17147,51 +17147,51 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>SHA-konsekvenser</t>
+          <t>TEs kommentar</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>kvalitet</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Kvalitetskonsekvenser</t>
+          <t>Begrunnelse for bestridelse</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>fremdrift</t>
+          <t>nytt_koe_sak_id</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -17201,105 +17201,105 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Fremdriftskonsekvenser</t>
+          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>pris</t>
+          <t>ny_revisjon_nummer</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Priskonsekvenser</t>
+          <t>Nytt revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>annet</t>
+          <t>endringer_beskrivelse</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Andre konsekvenser</t>
+          <t>Beskrivelse av endringene</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>oppdatert_data</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOUtstedtData</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Oppdatert EO-data (hvis endret)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>sha</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -17309,51 +17309,51 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>SHA-konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>kvalitet</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Kvalitetskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>fremdrift</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -17363,24 +17363,24 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Fremdriftskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>pris</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
@@ -17390,24 +17390,24 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>Priskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>annet</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>Andre konsekvenser</t>
         </is>
       </c>
     </row>
@@ -17429,22 +17429,22 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
@@ -17456,12 +17456,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -17483,22 +17483,22 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -17510,12 +17510,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -17537,12 +17537,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -17564,12 +17564,12 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17591,12 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -17618,12 +17618,12 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -17645,12 +17645,12 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -17682,12 +17682,12 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -17709,12 +17709,12 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -17726,34 +17726,34 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -17768,24 +17768,24 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -17795,24 +17795,24 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -17822,100 +17822,100 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>navn</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>rolle</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>adresse</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -17937,12 +17937,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>orgnr</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -17964,12 +17964,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>sakId</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17991,12 +17991,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -18018,12 +18018,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>eventId</t>
+          <t>navn</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -18045,12 +18045,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>sporType</t>
+          <t>rolle</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -18072,12 +18072,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>dato</t>
+          <t>adresse</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>kravDato</t>
+          <t>orgnr</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -18126,12 +18126,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>sakId</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -18153,12 +18153,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>originalTekst</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -18180,12 +18180,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>redigertTekst</t>
+          <t>eventId</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -18207,17 +18207,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>innledning</t>
+          <t>sporType</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -18234,17 +18234,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -18261,22 +18261,22 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>avslutning</t>
+          <t>kravDato</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18288,7 +18288,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -18315,17 +18315,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>mottaker</t>
+          <t>originalTekst</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -18342,17 +18342,17 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>avsender</t>
+          <t>redigertTekst</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -18369,17 +18369,17 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>referanser</t>
+          <t>innledning</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>LetterReferences</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -18396,17 +18396,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>seksjoner</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>LetterSections</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -18423,206 +18423,206 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>avslutning</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>belop</t>
+          <t>mottaker</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Beløp for dette særskilte kravet</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>dato_klar_over</t>
+          <t>avsender</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>dato_sendt</t>
+          <t>referanser</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterReferences</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>seksjoner</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>LetterSections</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>belop_direkte</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -18632,19 +18632,19 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>kostnads_overslag</t>
+          <t>belop</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -18659,24 +18659,24 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
+          <t>Beløp for dette særskilte kravet</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>dato_klar_over</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -18686,24 +18686,24 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
+          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>dato_sendt</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -18713,34 +18713,34 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
+          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VederlagKompensasjon</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>metode</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
+          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
         </is>
       </c>
     </row>
@@ -18752,20 +18752,182 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
+          <t>metode</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>VederlagsMetode</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>belop_direkte</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>kostnads_overslag</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>fradrag_belop</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>er_estimat</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>ja/nei</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>nei</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>netto_belop</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>beregnet</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Delmodell VederlagKompensasjon</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
           <t>krevd_belop</t>
         </is>
       </c>
-      <c r="C366" s="2" t="inlineStr">
+      <c r="C372" s="2" t="inlineStr">
         <is>
           <t>tall</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr">
+      <c r="D372" s="2" t="inlineStr">
         <is>
           <t>beregnet</t>
         </is>
       </c>
-      <c r="E366" s="2" t="inlineStr">
+      <c r="E372" s="2" t="inlineStr">
         <is>
           <t>Alias for netto_belop - brukes i state-modellen. Returnerer det totale kravet/kompensasjonen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8577,7 +8577,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`. Sakstypen settes også når hendelsen kommer i en KOE-sak, og ingen regel stopper det (DM-07).</t>
+          <t>Saken blir en endringsordresak, og endringsordren får status `utkast`. Skrives i samme transaksjon som `sak_opprettet` og `eo_utstedt`. I en KOE-sak avvises hendelsen av `IS_EO_CASE` (DM-07, rettet 05.10).</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>TEs aksept settes på sporet. Statusen følger BHs svar og forbedrer det aldri: avslag gir `avslatt_akseptert`, godkjent og delvis godkjent gir `godkjent`, og `hold_tilbake` og `frafalt` lar statusen stå (vedtaket 19.09, TFR-01).</t>
+          <t>TEs aksept settes på sporet. Statusen følger BHs svar og forbedrer det aldri: avslag gir `avslatt_akseptert`, godkjent og delvis godkjent gir `godkjent`, og `hold_tilbake` og `frafalt` lar statusen stå (vedtaket 19.09, TFR-01). Godtar TE avslaget på grunnlaget, blir saken `LUKKET_AVSLATT`, uansett vederlag og frist, og lukket for alle hendelser utenom endringsordrens (vedtaket 05.10, #213).</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -7748,7 +7748,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BH ber TE spesifisere fristkravet. TE må da uten ugrunnet opphold angi dager eller begrunne hvorfor grunnlaget mangler, ellers tapes kravet. En egen handling: den setter ikke resultat, gjør ikke sporet avslått og åpner ikke forsering. Forespørselen sendes per brev, så `brev` er påkrevd.</t>
+          <t>BH ber TE spesifisere fristkravet. TE må da uten ugrunnet opphold angi dager eller begrunne hvorfor grunnlaget mangler, ellers tapes kravet. En egen handling: den setter ikke resultat, gjør ikke sporet avslått og åpner ikke forsering. Forespørselen sendes per brev, så `brev` er påkrevd. Den faste teksten i `backend/constants/frist_foresporsel.json` må stå uendret i både `begrunnelse` og brevets begrunnelse (#173).</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>vedtak: nøytralt fristvarsel i 3.1 (23.09); oppdragsgiver, 2026-10-04</t>
+          <t>vedtak: nøytralt fristvarsel i 3.1 (23.09); oppdragsgiver, 2026-10-04 og 2026-10-05</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E372"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14081,12 +14081,12 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14108,12 +14108,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14135,12 +14135,12 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
@@ -14189,12 +14189,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14216,12 +14216,12 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14270,12 +14270,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14297,12 +14297,12 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
@@ -14324,12 +14324,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
@@ -14351,12 +14351,12 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14378,34 +14378,34 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -14420,34 +14420,34 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14459,12 +14459,12 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>regelversjon</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14540,12 +14540,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14594,12 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14729,12 +14729,12 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>har_bh_foresporsel</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Har BH sendt forespørsel om spesifisering? (§33.6.2). Relevant kun hvis krav er sent.</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
@@ -14756,12 +14756,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>dato_bh_foresporsel</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Dato BH sendte forespørsel om spesifisering (§33.6.2) - YYYY-MM-DD. Brukes for å beregne om TEs svar kom i tide.</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14810,12 +14810,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -14837,12 +14837,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>frist_for_spesifisering</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14864,12 +14864,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
@@ -14918,12 +14918,12 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14945,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14972,39 +14972,39 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -15014,46 +15014,46 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Valgfri kommentar fra entreprenør</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -15063,29 +15063,29 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Event-ID til fristkravet som ble avslått</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>respons_frist_id</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -15095,51 +15095,51 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>estimert_kostnad</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Valgfri kommentar fra entreprenør</t>
+          <t>Estimert kostnad for forsering i NOK</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Begrunnelse for forsering</t>
         </is>
       </c>
     </row>
@@ -15161,22 +15161,22 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>bekreft_30_prosent</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til fristkravet som ble avslått</t>
+          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_id</t>
+          <t>dato_iverksettelse</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
+          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -15215,12 +15215,12 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>estimert_kostnad</t>
+          <t>avslatte_dager</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Estimert kostnad for forsering i NOK</t>
+          <t>Antall dager som ble avslått av BH</t>
         </is>
       </c>
     </row>
@@ -15242,12 +15242,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>dagmulktsats</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -15257,7 +15257,7 @@
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for forsering</t>
+          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
         </is>
       </c>
     </row>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>bekreft_30_prosent</t>
+          <t>grunnlag_avslag_trigger</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -15284,46 +15284,46 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
+          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>dato_iverksettelse</t>
+          <t>vurdering_per_sak</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av objekt</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
+          <t>BHs vurdering av forseringsrett per sak</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>avslatte_dager</t>
+          <t>dager_med_forseringsrett</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -15333,56 +15333,56 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Antall dager som ble avslått av BH</t>
+          <t>Antall dager BH mener TE har forseringsrett for</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>dagmulktsats</t>
+          <t>grunnlag_fortsatt_gyldig</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
+          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_avslag_trigger</t>
+          <t>grunnlag_begrunnelse</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
+          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
         </is>
       </c>
     </row>
@@ -15404,12 +15404,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>vurdering_per_sak</t>
+          <t>trettiprosent_overholdt</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>liste av objekt</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -15419,7 +15419,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av forseringsrett per sak</t>
+          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
         </is>
       </c>
     </row>
@@ -15431,12 +15431,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>dager_med_forseringsrett</t>
+          <t>trettiprosent_begrunnelse</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Antall dager BH mener TE har forseringsrett for</t>
+          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_fortsatt_gyldig</t>
+          <t>aksepterer</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
+          <t>BH aksepterer forsering</t>
         </is>
       </c>
     </row>
@@ -15485,12 +15485,12 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_begrunnelse</t>
+          <t>godkjent_kostnad</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
+          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
         </is>
       </c>
     </row>
@@ -15512,22 +15512,22 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_overholdt</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
+          <t>BH's begrunnelse for aksept/avslag</t>
         </is>
       </c>
     </row>
@@ -15539,12 +15539,12 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_begrunnelse</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
+          <t>Om rigg/drift-varslet var rettidig</t>
         </is>
       </c>
     </row>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>aksepterer</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>BH aksepterer forsering</t>
+          <t>Om produktivitets-varslet var rettidig</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>godkjent_kostnad</t>
+          <t>godkjent_rigg_drift</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
+          <t>Godkjent rigg/drift-beløp</t>
         </is>
       </c>
     </row>
@@ -15620,22 +15620,22 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>godkjent_produktivitet</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for aksept/avslag</t>
+          <t>Godkjent produktivitetsbeløp</t>
         </is>
       </c>
     </row>
@@ -15647,12 +15647,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Om rigg/drift-varslet var rettidig</t>
+          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
         </is>
       </c>
     </row>
@@ -15674,12 +15674,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Om produktivitets-varslet var rettidig</t>
+          <t>Subsidiært godkjent beløp</t>
         </is>
       </c>
     </row>
@@ -15701,12 +15701,12 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>godkjent_rigg_drift</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -15716,51 +15716,51 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Godkjent rigg/drift-beløp</t>
+          <t>Begrunnelse for subsidiært standpunkt</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>godkjent_produktivitet</t>
+          <t>dato_stoppet</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Godkjent produktivitetsbeløp</t>
+          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -15770,24 +15770,24 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
+          <t>Påløpte kostnader ved stopp i NOK</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -15797,46 +15797,46 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp</t>
+          <t>Begrunnelse for stopp</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for subsidiært standpunkt</t>
+          <t>Påløpte kostnader i NOK</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>dato_stoppet</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15846,51 +15846,51 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
+          <t>Kommentar til kostnadsoppdatering</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader ved stopp i NOK</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -15905,24 +15905,24 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for stopp</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -15932,19 +15932,19 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader i NOK</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -15959,19 +15959,19 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Kommentar til kostnadsoppdatering</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -15981,24 +15981,24 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16008,24 +16008,24 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Sakstittel</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16035,24 +16035,24 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>sakstype</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>prosjekt_navn</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Prosjektnavn fra Catenda</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>byggherre</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel</t>
+          <t>Byggherre (BH) - fra topic custom field</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>leverandor</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
         </is>
       </c>
     </row>
@@ -16160,12 +16160,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>sakstype</t>
+          <t>forsering_data</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>objekt</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -16175,19 +16175,19 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
+          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_navn</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -16197,29 +16197,29 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Prosjektnavn fra Catenda</t>
+          <t>Notat-tekst</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>byggherre</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -16229,19 +16229,19 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Byggherre (BH) - fra topic custom field</t>
+          <t>Hvilket spor notatet gjelder</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>leverandor</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -16251,83 +16251,83 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>forsering_data</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>objekt</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Notat-tekst</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -16337,7 +16337,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Hvilket spor notatet gjelder</t>
+          <t>Sakstittel for EO-saken</t>
         </is>
       </c>
     </row>
@@ -16349,7 +16349,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16359,12 +16359,12 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -16386,51 +16386,51 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -16445,19 +16445,19 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel for EO-saken</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -16467,24 +16467,24 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -16499,19 +16499,19 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -16526,24 +16526,24 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -16553,19 +16553,19 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -16580,24 +16580,24 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -16619,22 +16619,22 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -16646,12 +16646,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -16673,22 +16673,22 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -16700,12 +16700,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -16727,12 +16727,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -16754,12 +16754,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -16781,12 +16781,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -16808,12 +16808,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
@@ -16835,12 +16835,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -16862,12 +16862,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
@@ -16889,12 +16889,12 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
@@ -16916,22 +16916,22 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
@@ -16943,22 +16943,22 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
@@ -16970,39 +16970,39 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>akseptert</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -17012,127 +17012,127 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>Om TE aksepterer</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>TEs kommentar</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>Begrunnelse for bestridelse</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>nytt_koe_sak_id</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>akseptert</t>
+          <t>ny_revisjon_nummer</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Om TE aksepterer</t>
+          <t>Nytt revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>endringer_beskrivelse</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -17142,56 +17142,56 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>TEs kommentar</t>
+          <t>Beskrivelse av endringene</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>oppdatert_data</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOUtstedtData</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for bestridelse</t>
+          <t>Oppdatert EO-data (hvis endret)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>nytt_koe_sak_id</t>
+          <t>sha</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -17201,78 +17201,78 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
+          <t>SHA-konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>ny_revisjon_nummer</t>
+          <t>kvalitet</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Nytt revisjonsnummer</t>
+          <t>Kvalitetskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>endringer_beskrivelse</t>
+          <t>fremdrift</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringene</t>
+          <t>Fremdriftskonsekvenser</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>oppdatert_data</t>
+          <t>pris</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>EOUtstedtData</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Oppdatert EO-data (hvis endret)</t>
+          <t>Priskonsekvenser</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>sha</t>
+          <t>annet</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -17309,51 +17309,51 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>SHA-konsekvenser</t>
+          <t>Andre konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>kvalitet</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Kvalitetskonsekvenser</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>fremdrift</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -17363,51 +17363,51 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Fremdriftskonsekvenser</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>pris</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>Priskonsekvenser</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>annet</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Andre konsekvenser</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -17429,22 +17429,22 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -17456,12 +17456,12 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -17483,22 +17483,22 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -17510,12 +17510,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -17537,12 +17537,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -17564,12 +17564,12 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17591,12 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -17618,12 +17618,12 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
@@ -17645,12 +17645,12 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -17672,12 +17672,12 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
@@ -17699,12 +17699,12 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
@@ -17726,22 +17726,22 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
@@ -17753,22 +17753,22 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
@@ -17780,39 +17780,39 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -17822,100 +17822,100 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>navn</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17937,12 +17937,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>rolle</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17964,12 +17964,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>adresse</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -17991,12 +17991,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>orgnr</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -18018,12 +18018,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>navn</t>
+          <t>sakId</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -18045,12 +18045,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>rolle</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -18072,12 +18072,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>adresse</t>
+          <t>eventId</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -18099,12 +18099,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>orgnr</t>
+          <t>sporType</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>sakId</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -18158,7 +18158,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>kravDato</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18180,12 +18180,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>eventId</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -18207,12 +18207,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>sporType</t>
+          <t>originalTekst</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -18234,12 +18234,12 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>dato</t>
+          <t>redigertTekst</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -18261,22 +18261,22 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>kravDato</t>
+          <t>innledning</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18288,17 +18288,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -18315,17 +18315,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>originalTekst</t>
+          <t>avslutning</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -18342,12 +18342,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>redigertTekst</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -18369,17 +18369,17 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>innledning</t>
+          <t>mottaker</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -18396,17 +18396,17 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>avsender</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -18423,17 +18423,17 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>avslutning</t>
+          <t>referanser</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>LetterReferences</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -18455,12 +18455,12 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>seksjoner</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSections</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -18477,125 +18477,125 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>mottaker</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>avsender</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>referanser</t>
+          <t>belop</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>LetterReferences</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Beløp for dette særskilte kravet</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>seksjoner</t>
+          <t>dato_klar_over</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>LetterSections</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>dato_sendt</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -18605,24 +18605,24 @@
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
+          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>metode</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -18632,51 +18632,51 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
+          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>belop</t>
+          <t>metode</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>Beløp for dette særskilte kravet</t>
+          <t>Vederlagsmetode etter NS 8407 (§34)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>dato_klar_over</t>
+          <t>belop_direkte</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -18686,24 +18686,24 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
+          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>dato_sendt</t>
+          <t>kostnads_overslag</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -18713,24 +18713,24 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
+          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -18740,7 +18740,7 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
+          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
         </is>
       </c>
     </row>
@@ -18752,22 +18752,22 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
         </is>
       </c>
     </row>
@@ -18779,7 +18779,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>belop_direkte</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -18789,12 +18789,12 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>kostnads_overslag</t>
+          <t>krevd_belop</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -18816,118 +18816,10 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B369" s="2" t="inlineStr">
-        <is>
-          <t>fradrag_belop</t>
-        </is>
-      </c>
-      <c r="C369" s="2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="D369" s="2" t="inlineStr">
-        <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="inlineStr">
-        <is>
-          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B370" s="2" t="inlineStr">
-        <is>
-          <t>er_estimat</t>
-        </is>
-      </c>
-      <c r="C370" s="2" t="inlineStr">
-        <is>
-          <t>ja/nei</t>
-        </is>
-      </c>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>nei</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B371" s="2" t="inlineStr">
-        <is>
-          <t>netto_belop</t>
-        </is>
-      </c>
-      <c r="C371" s="2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>beregnet</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B372" s="2" t="inlineStr">
-        <is>
-          <t>krevd_belop</t>
-        </is>
-      </c>
-      <c r="C372" s="2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="D372" s="2" t="inlineStr">
-        <is>
-          <t>beregnet</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr">
         <is>
           <t>Alias for netto_belop - brukes i state-modellen. Returnerer det totale kravet/kompensasjonen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8879,7 +8879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14243,12 +14243,12 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14270,12 +14270,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
@@ -14297,12 +14297,12 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
@@ -14324,12 +14324,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14351,49 +14351,49 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>respons_frist</t>
+          <t>respons_frist_oppdatert</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14405,12 +14405,12 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -14432,12 +14432,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>regelversjon</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -14447,7 +14447,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
         </is>
       </c>
     </row>
@@ -14459,12 +14459,12 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>regelversjon</t>
+          <t>brev</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>LetterSnapshot</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Versjonen av reglene klienten regnet med (B-13). Kontrolleres mot regler.REGELVERSJON</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>brev</t>
+          <t>tilleggs_begrunnelse</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>LetterSnapshot</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>tilleggs_begrunnelse</t>
+          <t>original_respons_id</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
         </is>
       </c>
     </row>
@@ -14540,12 +14540,12 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>original_respons_id</t>
+          <t>respondert_versjon</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til original respons som oppdateres (for RESPONS_*_OPPDATERT)</t>
+          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>respondert_versjon</t>
+          <t>frist_varsel_ok</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Hvilken TE-versjon (0-indeksert) denne responsen gjelder. Settes automatisk av backend.</t>
+          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>frist_varsel_ok</t>
+          <t>spesifisert_krav_ok</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Er varsel om fristforlengelse sendt i tide? (§33.4). None hvis ikke relevant.</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>spesifisert_krav_ok</t>
+          <t>foresporsel_svar_ok</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
         </is>
       </c>
     </row>
@@ -14648,12 +14648,12 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>foresporsel_svar_ok</t>
+          <t>begrunnelse_varsel</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Er svar på forespørsel sendt i tide? (§33.6.2/§5). None hvis ikke relevant.</t>
+          <t>BHs begrunnelse for vurdering av varsling</t>
         </is>
       </c>
     </row>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse_varsel</t>
+          <t>vilkar_oppfylt</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse for vurdering av varsling</t>
+          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
         </is>
       </c>
     </row>
@@ -14702,12 +14702,12 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>vilkar_oppfylt</t>
+          <t>beregnings_resultat</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Har forholdet medført en faktisk fremdriftshindring? (§33.1)</t>
+          <t>BHs vurdering av antall dager (ren beregning)</t>
         </is>
       </c>
     </row>
@@ -14729,12 +14729,12 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>beregnings_resultat</t>
+          <t>godkjent_dager</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av antall dager (ren beregning)</t>
+          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
         </is>
       </c>
     </row>
@@ -14756,12 +14756,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>godkjent_dager</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Godkjent antall dager. Innvilges kun hvis Grunnlag også godkjennes.</t>
+          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>BH-godkjent ny sluttdato (YYYY-MM-DD)</t>
+          <t>Samlet begrunnelse</t>
         </is>
       </c>
     </row>
@@ -14810,12 +14810,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av SubsidiaerTrigger</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Samlet begrunnelse</t>
+          <t>Liste over årsaker til subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14837,12 +14837,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>frist_for_spesifisering</t>
+          <t>subsidiaer_resultat</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>FristBeregningResultat</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Frist for TE å levere ytterligere spesifikasjon/fremdriftsplan (YYYY-MM-DD)</t>
+          <t>Subsidiært beregningsresultat</t>
         </is>
       </c>
     </row>
@@ -14864,12 +14864,12 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>subsidiaer_godkjent_dager</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>liste av SubsidiaerTrigger</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Liste over årsaker til subsidiær vurdering</t>
+          <t>Subsidiært godkjent antall dager</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_resultat</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>FristBeregningResultat</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært beregningsresultat</t>
+          <t>BH's begrunnelse for subsidiær vurdering</t>
         </is>
       </c>
     </row>
@@ -14918,34 +14918,34 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_dager</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent antall dager</t>
+          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -14960,14 +14960,14 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for subsidiær vurdering</t>
+          <t>Valgfri kommentar fra entreprenør</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_oppdatert</t>
+          <t>te_aksepterer_respons</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -14994,12 +14994,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>frist_krav_id</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -15009,29 +15009,29 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Valgfri kommentar fra entreprenør</t>
+          <t>Event-ID til fristkravet som ble avslått</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>te_aksepterer_respons</t>
+          <t>forsering_varsel</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>respons_frist_id</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Står på toppnivå i modellen og legges i `data` ved lagring.</t>
+          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
         </is>
       </c>
     </row>
@@ -15053,12 +15053,12 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>frist_krav_id</t>
+          <t>estimert_kostnad</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til fristkravet som ble avslått</t>
+          <t>Estimert kostnad for forsering i NOK</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>respons_frist_id</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Event-ID til BH's frist-respons som utløste forseringen</t>
+          <t>Begrunnelse for forsering</t>
         </is>
       </c>
     </row>
@@ -15107,22 +15107,22 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>estimert_kostnad</t>
+          <t>bekreft_30_prosent</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Estimert kostnad for forsering i NOK</t>
+          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>dato_iverksettelse</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for forsering</t>
+          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -15161,22 +15161,22 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>bekreft_30_prosent</t>
+          <t>avslatte_dager</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>TE bekrefter at estimert kostnad er innenfor dagmulkt + 30%</t>
+          <t>Antall dager som ble avslått av BH</t>
         </is>
       </c>
     </row>
@@ -15188,12 +15188,12 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>dato_iverksettelse</t>
+          <t>dagmulktsats</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering iverksettes (YYYY-MM-DD)</t>
+          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
         </is>
       </c>
     </row>
@@ -15215,66 +15215,66 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>avslatte_dager</t>
+          <t>grunnlag_avslag_trigger</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Antall dager som ble avslått av BH</t>
+          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>dagmulktsats</t>
+          <t>vurdering_per_sak</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av objekt</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktsats i NOK per dag (påkrevd for 30%-beregning)</t>
+          <t>BHs vurdering av forseringsrett per sak</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>forsering_varsel</t>
+          <t>forsering_respons</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_avslag_trigger</t>
+          <t>dager_med_forseringsrett</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>True hvis forsering utløses av grunnlagsavslag (ikke direkte frist-avslag)</t>
+          <t>Antall dager BH mener TE har forseringsrett for</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>vurdering_per_sak</t>
+          <t>grunnlag_fortsatt_gyldig</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>liste av objekt</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>BHs vurdering av forseringsrett per sak</t>
+          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
         </is>
       </c>
     </row>
@@ -15323,12 +15323,12 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>dager_med_forseringsrett</t>
+          <t>grunnlag_begrunnelse</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Antall dager BH mener TE har forseringsrett for</t>
+          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_fortsatt_gyldig</t>
+          <t>trettiprosent_overholdt</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>BH bekrefter at frist-avslaget fortsatt står ved lag</t>
+          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>grunnlag_begrunnelse</t>
+          <t>trettiprosent_begrunnelse</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse hvis grunnlaget bestrides</t>
+          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_overholdt</t>
+          <t>aksepterer</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>BH vurderer om estimert kostnad er innenfor 30%-grensen</t>
+          <t>BH aksepterer forsering</t>
         </is>
       </c>
     </row>
@@ -15431,12 +15431,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>trettiprosent_begrunnelse</t>
+          <t>godkjent_kostnad</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>BHs begrunnelse ved avvik fra 30%-regelen</t>
+          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
         </is>
       </c>
     </row>
@@ -15458,12 +15458,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>aksepterer</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>BH aksepterer forsering</t>
+          <t>BH's begrunnelse for aksept/avslag</t>
         </is>
       </c>
     </row>
@@ -15485,12 +15485,12 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>godkjent_kostnad</t>
+          <t>rigg_varslet_i_tide</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>BH's godkjente forseringskostnad (kan være lavere enn estimert)</t>
+          <t>Om rigg/drift-varslet var rettidig</t>
         </is>
       </c>
     </row>
@@ -15512,22 +15512,22 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>produktivitet_varslet_i_tide</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>BH's begrunnelse for aksept/avslag</t>
+          <t>Om produktivitets-varslet var rettidig</t>
         </is>
       </c>
     </row>
@@ -15539,12 +15539,12 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>rigg_varslet_i_tide</t>
+          <t>godkjent_rigg_drift</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Om rigg/drift-varslet var rettidig</t>
+          <t>Godkjent rigg/drift-beløp</t>
         </is>
       </c>
     </row>
@@ -15566,12 +15566,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>produktivitet_varslet_i_tide</t>
+          <t>godkjent_produktivitet</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Om produktivitets-varslet var rettidig</t>
+          <t>Godkjent produktivitetsbeløp</t>
         </is>
       </c>
     </row>
@@ -15593,12 +15593,12 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>godkjent_rigg_drift</t>
+          <t>subsidiaer_triggers</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Godkjent rigg/drift-beløp</t>
+          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
         </is>
       </c>
     </row>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>godkjent_produktivitet</t>
+          <t>subsidiaer_godkjent_belop</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Godkjent produktivitetsbeløp</t>
+          <t>Subsidiært godkjent beløp</t>
         </is>
       </c>
     </row>
@@ -15647,12 +15647,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_triggers</t>
+          <t>subsidiaer_begrunnelse</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -15662,51 +15662,51 @@
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Triggere for subsidiær vurdering (f.eks. 'grunnlag_bestridt')</t>
+          <t>Begrunnelse for subsidiært standpunkt</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_godkjent_belop</t>
+          <t>dato_stoppet</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Subsidiært godkjent beløp</t>
+          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>forsering_respons</t>
+          <t>forsering_stoppet</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>subsidiaer_begrunnelse</t>
+          <t>paalopte_kostnader</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for subsidiært standpunkt</t>
+          <t>Påløpte kostnader ved stopp i NOK</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>dato_stoppet</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -15738,19 +15738,19 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Dato forsering ble stoppet (YYYY-MM-DD)</t>
+          <t>Begrunnelse for stopp</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -15765,24 +15765,24 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader ved stopp i NOK</t>
+          <t>Påløpte kostnader i NOK</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>forsering_stoppet</t>
+          <t>forsering_kostnader_oppdatert</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -15797,24 +15797,24 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for stopp</t>
+          <t>Kommentar til kostnadsoppdatering</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>paalopte_kostnader</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -15824,19 +15824,19 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Påløpte kostnader i NOK</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>forsering_kostnader_oppdatert</t>
+          <t>forsering_koe_lagt_til</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -15851,14 +15851,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Kommentar til kostnadsoppdatering</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_lagt_til</t>
+          <t>forsering_koe_fjernet</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -15912,12 +15912,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -15927,24 +15927,24 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>forsering_koe_fjernet</t>
+          <t>sak_opprettet</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -15954,12 +15954,12 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Sakstittel</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>sakstype</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -16008,12 +16008,12 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel</t>
+          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
         </is>
       </c>
     </row>
@@ -16025,7 +16025,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>prosjekt_navn</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Prosjektnavn fra Catenda</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>sakstype</t>
+          <t>byggherre</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Sakstype: 'standard' (KOE), 'endringsordre' (EO), eller 'forsering'</t>
+          <t>Byggherre (BH) - fra topic custom field</t>
         </is>
       </c>
     </row>
@@ -16079,7 +16079,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_navn</t>
+          <t>leverandor</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Prosjektnavn fra Catenda</t>
+          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
         </is>
       </c>
     </row>
@@ -16106,12 +16106,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>byggherre</t>
+          <t>forsering_data</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>objekt</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -16121,19 +16121,19 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Byggherre (BH) - fra topic custom field</t>
+          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>leverandor</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -16143,29 +16143,29 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Leverandør/Entreprenør (TE) - fra topic custom field</t>
+          <t>Notat-tekst</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>sak_opprettet</t>
+          <t>internt_notat</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>forsering_data</t>
+          <t>spor</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>objekt</t>
+          <t>SporType</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -16175,26 +16175,26 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Forsering-data inkl. avslatte_fristkrav, dato_varslet, estimert_kostnad (kun for forsering-saker)</t>
+          <t>Hvilket spor notatet gjelder</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
+          <t>eo_nummer</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
           <t>tekst</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>tekst</t>
-        </is>
-      </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
           <t>ja</t>
@@ -16202,34 +16202,34 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Notat-tekst</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>internt_notat</t>
+          <t>eo_opprettet</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>spor</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>SporType</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Hvilket spor notatet gjelder</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -16241,22 +16241,22 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Sakstittel for EO-saken</t>
         </is>
       </c>
     </row>
@@ -16295,12 +16295,12 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Prosjekt-ID</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>catenda_topic_id</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -16337,19 +16337,19 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Sakstittel for EO-saken</t>
+          <t>Catenda topic GUID</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>koe_sak_id</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -16359,24 +16359,24 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Prosjekt-ID</t>
+          <t>SAK-ID til KOE som legges til/fjernes</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>eo_opprettet</t>
+          <t>eo_koe_lagt_til</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_id</t>
+          <t>koe_tittel</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -16391,14 +16391,14 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Catenda topic GUID</t>
+          <t>Tittel på KOE for visning</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -16425,7 +16425,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_lagt_til</t>
+          <t>eo_koe_fjernet</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -16452,12 +16452,12 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>koe_sak_id</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -16472,24 +16472,24 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til KOE som legges til/fjernes</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>eo_koe_fjernet</t>
+          <t>eo_utstedt</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>koe_tittel</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Tittel på KOE for visning</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -16538,12 +16538,12 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -16565,22 +16565,22 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -16592,12 +16592,12 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -16619,12 +16619,12 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -16673,12 +16673,12 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -16700,12 +16700,12 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -16727,12 +16727,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -16754,12 +16754,12 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
@@ -16781,12 +16781,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -16808,12 +16808,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -16823,7 +16823,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
@@ -16835,12 +16835,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
@@ -16862,22 +16862,22 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
@@ -16889,22 +16889,22 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
@@ -16916,12 +16916,12 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -16931,19 +16931,19 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>akseptert</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -16953,78 +16953,78 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>Om TE aksepterer</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>eo_utstedt</t>
+          <t>eo_akseptert</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>kommentar</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>TEs kommentar</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>akseptert</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Om TE aksepterer</t>
+          <t>Begrunnelse for bestridelse</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>eo_akseptert</t>
+          <t>eo_bestridt</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>kommentar</t>
+          <t>nytt_koe_sak_id</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -17039,24 +17039,24 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>TEs kommentar</t>
+          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>ny_revisjon_nummer</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
@@ -17066,19 +17066,19 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Begrunnelse for bestridelse</t>
+          <t>Nytt revisjonsnummer</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>eo_bestridt</t>
+          <t>eo_revidert</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>nytt_koe_sak_id</t>
+          <t>endringer_beskrivelse</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>SAK-ID til nytt KOE som fremmes som alternativ</t>
+          <t>Beskrivelse av endringene</t>
         </is>
       </c>
     </row>
@@ -17105,66 +17105,66 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>ny_revisjon_nummer</t>
+          <t>oppdatert_data</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>EOUtstedtData</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Nytt revisjonsnummer</t>
+          <t>Oppdatert EO-data (hvis endret)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>endringer_beskrivelse</t>
+          <t>sha</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringene</t>
+          <t>SHA-konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>eo_revidert</t>
+          <t>Delmodell EOKonsekvenser</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>oppdatert_data</t>
+          <t>kvalitet</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>EOUtstedtData</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Oppdatert EO-data (hvis endret)</t>
+          <t>Kvalitetskonsekvenser</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>sha</t>
+          <t>fremdrift</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>SHA-konsekvenser</t>
+          <t>Fremdriftskonsekvenser</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>kvalitet</t>
+          <t>pris</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Kvalitetskonsekvenser</t>
+          <t>Priskonsekvenser</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>fremdrift</t>
+          <t>annet</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -17255,51 +17255,51 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Fremdriftskonsekvenser</t>
+          <t>Andre konsekvenser</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>pris</t>
+          <t>eo_nummer</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Priskonsekvenser</t>
+          <t>Endringsordre-nummer</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOKonsekvenser</t>
+          <t>Delmodell EOUtstedtData</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>annet</t>
+          <t>revisjon_nummer</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>Andre konsekvenser</t>
+          <t>Revisjonsnummer</t>
         </is>
       </c>
     </row>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>eo_nummer</t>
+          <t>beskrivelse</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -17336,7 +17336,7 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Endringsordre-nummer</t>
+          <t>Beskrivelse av endringen</t>
         </is>
       </c>
     </row>
@@ -17348,12 +17348,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>revisjon_nummer</t>
+          <t>vedlegg_ids</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Revisjonsnummer</t>
+          <t>Vedlegg-IDer</t>
         </is>
       </c>
     </row>
@@ -17375,22 +17375,22 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>beskrivelse</t>
+          <t>konsekvenser</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>EOKonsekvenser</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av endringen</t>
+          <t>Konsekvenser av endringen</t>
         </is>
       </c>
     </row>
@@ -17402,12 +17402,12 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_ids</t>
+          <t>konsekvens_beskrivelse</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Vedlegg-IDer</t>
+          <t>Beskrivelse av konsekvensene</t>
         </is>
       </c>
     </row>
@@ -17429,12 +17429,12 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>konsekvenser</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>EOKonsekvenser</t>
+          <t>VederlagKompensasjon</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Konsekvenser av endringen</t>
+          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
         </is>
       </c>
     </row>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>konsekvens_beskrivelse</t>
+          <t>oppgjorsform</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Beskrivelse av konsekvensene</t>
+          <t>DEPRECATED: Bruk vederlag.metode</t>
         </is>
       </c>
     </row>
@@ -17483,12 +17483,12 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>kompensasjon_belop</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>VederlagKompensasjon</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>Vederlagskompensasjon (metode, beløp, fradrag) - konsistent med VederlagData</t>
+          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
         </is>
       </c>
     </row>
@@ -17510,12 +17510,12 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>oppgjorsform</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.metode</t>
+          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
         </is>
       </c>
     </row>
@@ -17537,12 +17537,12 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>kompensasjon_belop</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.belop_direkte</t>
+          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
         </is>
       </c>
     </row>
@@ -17564,12 +17564,12 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>frist_dager</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>heltall</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.fradrag_belop</t>
+          <t>Fristforlengelse i dager</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17591,12 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>ny_sluttdato</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>DEPRECATED: Bruk vederlag.er_estimat</t>
+          <t>Ny sluttdato (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
@@ -17618,12 +17618,12 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>frist_dager</t>
+          <t>relaterte_koe_saker</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>heltall</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>Fristforlengelse i dager</t>
+          <t>SAK-IDs til KOE-er som inngår</t>
         </is>
       </c>
     </row>
@@ -17645,12 +17645,12 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>ny_sluttdato</t>
+          <t>relaterte_sak_ids</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>Ny sluttdato (YYYY-MM-DD)</t>
+          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
         </is>
       </c>
     </row>
@@ -17672,22 +17672,22 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>relaterte_koe_saker</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>SAK-IDs til KOE-er som inngår</t>
+          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
         </is>
       </c>
     </row>
@@ -17699,22 +17699,22 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>relaterte_sak_ids</t>
+          <t>har_priskonsekvens</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Alias for relaterte_koe_saker (for bakoverkompatibilitet)</t>
+          <t>Sjekker om EO har priskonsekvens</t>
         </is>
       </c>
     </row>
@@ -17726,12 +17726,12 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>netto_belop</t>
+          <t>har_fristkonsekvens</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -17741,61 +17741,61 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Beregner netto beløp. Prioriterer vederlag-feltet, faller tilbake til legacy-felter.</t>
+          <t>Sjekker om EO har fristkonsekvens</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>har_priskonsekvens</t>
+          <t>vederlag</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har priskonsekvens</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Delmodell EOUtstedtData</t>
+          <t>Delmodell KonsekvensVarsler</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>har_fristkonsekvens</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>beregnet</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>Sjekker om EO har fristkonsekvens</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>vederlag</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>frist</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -17856,12 +17856,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>navn</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Delmodell KonsekvensVarsler</t>
+          <t>Delmodell LetterParty</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>frist</t>
+          <t>rolle</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17915,7 +17915,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>navn</t>
+          <t>adresse</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>rolle</t>
+          <t>orgnr</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17964,12 +17964,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>adresse</t>
+          <t>sakId</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17991,12 +17991,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterParty</t>
+          <t>Delmodell LetterReferences</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>orgnr</t>
+          <t>sakstittel</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>sakId</t>
+          <t>eventId</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -18050,7 +18050,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>sakstittel</t>
+          <t>sporType</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -18077,7 +18077,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>eventId</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>sporType</t>
+          <t>kravDato</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18126,12 +18126,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>dato</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -18153,12 +18153,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterReferences</t>
+          <t>Delmodell LetterSection</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>kravDato</t>
+          <t>originalTekst</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>redigertTekst</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -18207,17 +18207,17 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>originalTekst</t>
+          <t>innledning</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -18234,17 +18234,17 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSection</t>
+          <t>Delmodell LetterSections</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>redigertTekst</t>
+          <t>begrunnelse</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterSection</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>innledning</t>
+          <t>avslutning</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -18288,17 +18288,17 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>begrunnelse</t>
+          <t>tittel</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -18315,17 +18315,17 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSections</t>
+          <t>Delmodell LetterSnapshot</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>avslutning</t>
+          <t>mottaker</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>LetterSection</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -18347,12 +18347,12 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>tittel</t>
+          <t>avsender</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>LetterParty</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -18374,12 +18374,12 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>mottaker</t>
+          <t>referanser</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>LetterReferences</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -18401,12 +18401,12 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>avsender</t>
+          <t>seksjoner</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>LetterParty</t>
+          <t>LetterSections</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -18423,71 +18423,71 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>referanser</t>
+          <t>rigg_drift</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>LetterReferences</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Delmodell LetterSnapshot</t>
+          <t>Delmodell SaerskiltKrav</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>seksjoner</t>
+          <t>produktivitet</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>LetterSections</t>
+          <t>SaerskiltKravItem</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>rigg_drift</t>
+          <t>belop</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -18497,24 +18497,24 @@
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>Rigg/drift krav (§34.1.3 første ledd)</t>
+          <t>Beløp for dette særskilte kravet</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKrav</t>
+          <t>Delmodell SaerskiltKravItem</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>produktivitet</t>
+          <t>dato_klar_over</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>SaerskiltKravItem</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -18524,24 +18524,24 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Produktivitetstap krav (§34.1.3 annet ledd)</t>
+          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>belop</t>
+          <t>dato_sendt</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>tekst</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -18551,24 +18551,24 @@
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>Beløp for dette særskilte kravet</t>
+          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Delmodell SaerskiltKravItem</t>
+          <t>Delmodell VarselInfo</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>dato_klar_over</t>
+          <t>metode</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>liste av tekst</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -18578,51 +18578,51 @@
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>Når TE ble klar over at utgifter ville påløpe (YYYY-MM-DD). Brukes til 7-dagers varslingssjekk.</t>
+          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>dato_sendt</t>
+          <t>metode</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>tekst</t>
+          <t>VederlagsMetode</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>Når varselet faktisk ble sendt til BH (YYYY-MM-DD)</t>
+          <t>Vederlagsmetode etter NS 8407 (§34)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Delmodell VarselInfo</t>
+          <t>Delmodell VederlagKompensasjon</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>belop_direkte</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>liste av tekst</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>Metoder brukt for å varsle (f.eks. ['epost', 'byggemote', 'telefon'])</t>
+          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
         </is>
       </c>
     </row>
@@ -18644,22 +18644,22 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>kostnads_overslag</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>VederlagsMetode</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nei</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>Vederlagsmetode etter NS 8407 (§34)</t>
+          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
         </is>
       </c>
     </row>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>belop_direkte</t>
+          <t>fradrag_belop</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>For ENHETSPRISER/FASTPRIS_TILBUD: Beløp i NOK</t>
+          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
         </is>
       </c>
     </row>
@@ -18698,12 +18698,12 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>kostnads_overslag</t>
+          <t>er_estimat</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>ja/nei</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>For REGNINGSARBEID (§30.2): Kostnadsoverslag i NOK</t>
+          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>fradrag_belop</t>
+          <t>netto_belop</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>Fradrag i NOK (§34.4) - reduksjon for besparelser</t>
+          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
         </is>
       </c>
     </row>
@@ -18752,74 +18752,20 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>er_estimat</t>
+          <t>krevd_belop</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>ja/nei</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>nei</t>
+          <t>beregnet</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>Om beløpet er et estimat (endelig oppgjør senere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B367" s="2" t="inlineStr">
-        <is>
-          <t>netto_belop</t>
-        </is>
-      </c>
-      <c r="C367" s="2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="D367" s="2" t="inlineStr">
-        <is>
-          <t>beregnet</t>
-        </is>
-      </c>
-      <c r="E367" s="2" t="inlineStr">
-        <is>
-          <t>Beregner netto beløp basert på metode. For ENHETSPRISER/FASTPRIS_TILBUD: belop_direkte - fradrag For REGNINGSARBEID: kostnads_overslag - fradrag</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="2" t="inlineStr">
-        <is>
-          <t>Delmodell VederlagKompensasjon</t>
-        </is>
-      </c>
-      <c r="B368" s="2" t="inlineStr">
-        <is>
-          <t>krevd_belop</t>
-        </is>
-      </c>
-      <c r="C368" s="2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="D368" s="2" t="inlineStr">
-        <is>
-          <t>beregnet</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
         <is>
           <t>Alias for netto_belop - brukes i state-modellen. Returnerer det totale kravet/kompensasjonen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -14042,7 +14042,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6). None hvis ikke vurdert (KA-U4).</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Er spesifisert krav sendt i tide? (§33.6)</t>
+          <t>Er spesifisert krav sendt i tide? (§33.6). None hvis ikke vurdert (KA-U4).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8124,7 +8124,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TE godtar BHs svar på ett spor, angitt i `spor`.</t>
+          <t>TE godtar BHs svar på ett spor, angitt i `spor`. `refererer_til_event_id` (kolonnen `referstoid`) er svaret som godtas, og det må være sporets gjeldende svar (KA-U1). Kommandoen er streng: et ukjent felt avvises. En aksept lagret før #272 har ingen referanse og leses som før. Kontrakten står i docs/domenetabell/kontrakt.json.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Når en forsering opprettes gjennom `/api/forsering/opprett`, og når en endringsordre opprettes eller KOE-er legges til eller fjernes fra den (forsering- og endringsordretjenesten). Å legge til eller fjerne KOE-er fra en forsering endrer bare Catenda, ikke denne tabellen (dataflyten, C11). Skriptet `scripts/backfill_relations.py` kaller lageret uten autorisert prosjekt, og over PostgreSQL avvises da hver skriving (`krev_autorisert_prosjekt`).</t>
+          <t>Når en forsering opprettes gjennom `/api/forsering/opprett`, og når en endringsordre opprettes eller KOE-er legges til eller fjernes fra den (forsering- og endringsordretjenesten). Å legge til eller fjerne KOE-er fra en forsering endrer bare Catenda, ikke denne tabellen (dataflyten, C11).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: én rad per sak, med prosjekt, sakstype, hvem som opprettet den, og koblingen til topic, board og prosjekt i Catenda. I tillegg ti `cached_*`-kolonner og `last_event_at` med tall regnet ut av hendelsene, til lister og rapportering. Tabellen blander register og projeksjon; skillet er planlagt (MS-06, MS-07).</t>
+          <t>Saksregisteret: én rad per sak, med prosjekt, sakstype, hvem som opprettet den, og koblingen til topic, board og prosjekt i Catenda. I tillegg ti `cached_*`-kolonner og `last_event_at` med tall regnet ut av hendelsene, til lister og rapportering. Fem `kjerne_*`-kolonner er bufferen TS-kjernen regner ut av journalen: visningen og de fire versjonene den er regnet med (B-10, #316). Tabellen blander register og projeksjon; skillet er planlagt (MS-06, MS-07).</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning).</t>
+          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (event_id); unik (sak_id, versjon). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); actorid → app_users.id (uten fremmednøkkel); actorteam → catenda_contract_teams.team_id (uten fremmednøkkel); referstoid → hendelse.event_id (uten fremmednøkkel); data → vedlegg_ids[] → vedlegg.vedlegg_id (uten fremmednøkkel). Vises til fra: approvals.body → items[].claimId (uten fremmednøkkel); approvals.body → packages[].eventIds[] (uten fremmednøkkel); catenda_delivery_status.event_id (uten fremmednøkkel); notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (event_id); unik (sak_id, versjon). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); actorid → app_users.id (uten fremmednøkkel); actorteam → catenda_contract_teams.team_id (uten fremmednøkkel); referstoid → hendelse.event_id (uten fremmednøkkel); data → vedlegg_ids[] → vedlegg.vedlegg_id (uten fremmednøkkel). Vises til fra: approvals.body → items[].claimId (uten fremmednøkkel); approvals.body → packages[].eventIds[] (uten fremmednøkkel); catenda_delivery_status.event_id (uten fremmednøkkel); leveringsoppdrag.event_id (fremmednøkkel, ON DELETE CASCADE); notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -561,12 +561,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>leveringsoppdrag</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Interne notater i en sak. Synlige bare for forfatterens eget team, ikke for motparten og ikke for andre team på samme side. Ligger utenfor journalen: et notat er ikke et kontraktsvarsel og flytter ikke sakens versjon (MS-05).</t>
+          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#ISSUE-LEVERING). Bare testmiljøet skriver tabellen (#347).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Når en bruker skriver et internt notat i en sak (hendelsesruta). Forfatteren kan slette notatet.</t>
+          <t>Når TS-serveren lagrer et brev: i samme transaksjon som hendelsen i `hendelse`. Slettes bare med saken eller hendelsen (kaskade).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `aktor_rolle` og `aktor_team_id` er utledet av teammedlemskapet i Catenda da notatet ble skrevet. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
+          <t>Nei. Målet (prosjekt, bibliotek, mappe og topic) leses fra prosjektets Catenda-konfigurasjon og saksregisteret når brevet lagres. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); aktor_id → app_users.id (uten fremmednøkkel); aktor_team_id → catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); event_id → hendelse.event_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -611,44 +611,44 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på forfatteren. `tekst` og `kommentar` er fritekst.</t>
+          <t>`innhold` har avsenderens `aktor_id` og brevets fritekst.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>notat</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: én rad per sak, med prosjekt, sakstype, hvem som opprettet den, og koblingen til topic, board og prosjekt i Catenda. I tillegg ti `cached_*`-kolonner og `last_event_at` med tall regnet ut av hendelsene, til lister og rapportering. Fem `kjerne_*`-kolonner er bufferen TS-kjernen regner ut av journalen: visningen og de fire versjonene den er regnet med (B-10, #316). Tabellen blander register og projeksjon; skillet er planlagt (MS-06, MS-07).</t>
+          <t>Interne notater i en sak. Synlige bare for forfatterens eget team, ikke for motparten og ikke for andre team på samme side. Ligger utenfor journalen: et notat er ikke et kontraktsvarsel og flytter ikke sakens versjon (MS-05).</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Når en bruker skriver et internt notat i en sak (hendelsesruta). Forfatteren kan slette notatet.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Delvis</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_topic_id`, `catenda_board_id` og `catenda_project_id` er ID-er fra Catenda. Dataflyt: fra Catenda i C01, C15; til Catenda i C01, C15 (arket Dataflyt).</t>
+          <t>Delvis. `aktor_rolle` og `aktor_team_id` er utledet av teammedlemskapet i Catenda da notatet ble skrevet. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); created_by → app_users.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel); catenda_board_id → catenda_topic_board_configs.topic_board_id (uten fremmednøkkel). Vises til fra: approval_outbox.case_id (uten fremmednøkkel); approvals.case_id (uten fremmednøkkel); catenda_delivery_status.case_id (uten fremmednøkkel); eo_approvals.body → packages[].sakId (uten fremmednøkkel); eo_approvals.body → packages[].request.koe_sak_ids[] (uten fremmednøkkel); hendelse.sak_id (fremmednøkkel, ON DELETE CASCADE); magic_links.sak_id (fremmednøkkel, ON DELETE CASCADE); notat.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_bim_links.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_relations.source_sak_id (uten fremmednøkkel); sak_relations.target_sak_id (uten fremmednøkkel); utkast.case_id (uten fremmednøkkel); vedlegg.case_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE); prosjekt_id → projects.id (uten fremmednøkkel); aktor_id → app_users.id (uten fremmednøkkel); aktor_team_id → catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>grunndata, avledet</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,19 +668,19 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>`created_by` identifiserer den som opprettet saken (tre verdiformer, MG-04).</t>
+          <t>`aktor_id` peker på forfatteren. `tekst` og `kommentar` er fritekst.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sak_relations</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Koblinger mellom saker, for eksempel hvilke KOE-er en forsering eller en endringsordre omfatter. Én rad per kobling, med type.</t>
+          <t>Saksregisteret: én rad per sak, med prosjekt, sakstype, hvem som opprettet den, og koblingen til topic, board og prosjekt i Catenda. I tillegg ti `cached_*`-kolonner og `last_event_at` med tall regnet ut av hendelsene, til lister og rapportering. Fem `kjerne_*`-kolonner er bufferen TS-kjernen regner ut av journalen: visningen og de fire versjonene den er regnet med (B-10, #316). Tabellen blander register og projeksjon; skillet er planlagt (MS-06, MS-07).</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -690,22 +690,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Når en forsering opprettes gjennom `/api/forsering/opprett`, og når en endringsordre opprettes eller KOE-er legges til eller fjernes fra den (forsering- og endringsordretjenesten). Å legge til eller fjerne KOE-er fra en forsering endrer bare Catenda, ikke denne tabellen (dataflyten, C11).</t>
+          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Delvis</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Delvis. En forsering opprettet gjennom `/api/forsering/opprett` får topicens GUID fra Catenda som sak-ID. Ellers er koblingene appens egne. Dataflyt: fra Catenda i C10 (arket Dataflyt).</t>
+          <t>Delvis. `catenda_topic_id`, `catenda_board_id` og `catenda_project_id` er ID-er fra Catenda. Dataflyt: fra Catenda i C01, C15; til Catenda i C01, C15 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (source_sak_id, target_sak_id, relation_type). Viser til: source_sak_id → sak_metadata.sak_id (uten fremmednøkkel); target_sak_id → sak_metadata.sak_id (uten fremmednøkkel); prosjekt_id → projects.id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); created_by → app_users.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel); catenda_board_id → catenda_topic_board_configs.topic_board_id (uten fremmednøkkel). Vises til fra: approval_outbox.case_id (uten fremmednøkkel); approvals.case_id (uten fremmednøkkel); catenda_delivery_status.case_id (uten fremmednøkkel); eo_approvals.body → packages[].sakId (uten fremmednøkkel); eo_approvals.body → packages[].request.koe_sak_ids[] (uten fremmednøkkel); hendelse.sak_id (fremmednøkkel, ON DELETE CASCADE); leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE CASCADE); magic_links.sak_id (fremmednøkkel, ON DELETE CASCADE); notat.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_bim_links.sak_id (fremmednøkkel, ON DELETE CASCADE); sak_relations.source_sak_id (uten fremmednøkkel); sak_relations.target_sak_id (uten fremmednøkkel); utkast.case_id (uten fremmednøkkel); vedlegg.case_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>grunndata, avledet</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -725,19 +725,19 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>`created_by` identifiserer den som opprettet saken (tre verdiformer, MG-04).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>sak_relations</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene i appen, med navn, beskrivelse, innstillinger, om prosjektet er aktivt, og organisasjonen det hører til (MS-10).</t>
+          <t>Koblinger mellom saker, for eksempel hvilke KOE-er en forsering eller en endringsordre omfatter. Én rad per kobling, med type.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -747,22 +747,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Registreres av drift gjennom databasefunksjonen `koe_register_project` (`scripts/catenda_admin.py`). `POST /api/projects` svarer 403 utenfor utviklingsmodus. En prosjektadministrator kan endre navn, beskrivelse og innstillinger og deaktivere prosjektet (`PATCH`). Driftsskriptet `catenda_admin.py sync-name` oppdaterer navnet direkte fra Catenda, utenom databasefunksjonen. At runtime-rollen heller ikke skal kunne kalle funksjonen, gjelder databaserettighetene og hører til F1 (B-02 punkt 4). En migrasjon legger inn prosjektet `oslobygg`, og det er i dag basens eneste prosjekt (DM-03).</t>
+          <t>Når en forsering opprettes gjennom `/api/forsering/opprett`, og når en endringsordre opprettes eller KOE-er legges til eller fjernes fra den (forsering- og endringsordretjenesten). Å legge til eller fjerne KOE-er fra en forsering endrer bare Catenda, ikke denne tabellen (dataflyten, C11).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Navnet kan hentes fra Catenda-prosjektet når drift registrerer prosjektet eller kjører `sync-name`. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`. Dataflyt: fra Catenda i C18, C20 (arket Dataflyt).</t>
+          <t>Delvis. En forsering opprettet gjennom `/api/forsering/opprett` får topicens GUID fra Catenda som sak-ID. Ellers er koblingene appens egne. Dataflyt: fra Catenda i C10 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: app_membership_sync.project_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); approval_outbox.project (uten fremmednøkkel); approvals.project (uten fremmednøkkel); catenda_delivery_status.project (uten fremmednøkkel); catenda_models_cache.prosjekt_id (uten fremmednøkkel); catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); eo_approvals.project (uten fremmednøkkel); hendelse.prosjekt_id (uten fremmednøkkel); notat.prosjekt_id (uten fremmednøkkel); project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.prosjekt_id (uten fremmednøkkel); sak_relations.prosjekt_id (uten fremmednøkkel); utkast.project (uten fremmednøkkel); vedlegg.project (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (source_sak_id, target_sak_id, relation_type). Viser til: source_sak_id → sak_metadata.sak_id (uten fremmednøkkel); target_sak_id → sak_metadata.sak_id (uten fremmednøkkel); prosjekt_id → projects.id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -782,19 +782,19 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>`created_by` identifiserer den som opprettet prosjektet.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>project_memberships</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Eldre medlemsliste per prosjekt, etter e-post. Erstattet av `app_project_memberships` og skal fjernes (MS-15) når `viewer` finnes der (DB-05).</t>
+          <t>Prosjektene i appen, med navn, beskrivelse, innstillinger, om prosjektet er aktivt, og organisasjonen det hører til (MS-10).</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `trg_auto_membership_on_project_create` legger inn en rad når et prosjekt opprettes. Koden som ser ut til å skrive tabellen, treffer en unik-skranke (AGENTS.md). Ingen leser den (DA-10).</t>
+          <t>Registreres av drift gjennom databasefunksjonen `koe_register_project` (`scripts/catenda_admin.py`). `POST /api/projects` svarer 403 utenfor utviklingsmodus. En prosjektadministrator kan endre navn, beskrivelse og innstillinger og deaktivere prosjektet (`PATCH`). Driftsskriptet `catenda_admin.py sync-name` oppdaterer navnet direkte fra Catenda, utenom databasefunksjonen. At runtime-rollen heller ikke skal kunne kalle funksjonen, gjelder databaserettighetene og hører til F1 (B-02 punkt 4). En migrasjon legger inn prosjektet `oslobygg`, og det er i dag basens eneste prosjekt (DM-03).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Navnet kan hentes fra Catenda-prosjektet når drift registrerer prosjektet eller kjører `sync-name`. Koblingen til Catenda-prosjektet ligger i `catenda_project_configs`. Dataflyt: fra Catenda i C18, C20 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (project_id, user_email). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: app_membership_sync.project_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); approval_outbox.project (uten fremmednøkkel); approvals.project (uten fremmednøkkel); catenda_delivery_status.project (uten fremmednøkkel); catenda_models_cache.prosjekt_id (uten fremmednøkkel); catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); eo_approvals.project (uten fremmednøkkel); hendelse.prosjekt_id (uten fremmednøkkel); leveringsoppdrag.prosjekt_id (uten fremmednøkkel); notat.prosjekt_id (uten fremmednøkkel); project_memberships.project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.prosjekt_id (uten fremmednøkkel); sak_relations.prosjekt_id (uten fremmednøkkel); utkast.project (uten fremmednøkkel); vedlegg.project (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>`user_email`, `display_name`, `external_id`.</t>
+          <t>`created_by` identifiserer den som opprettet prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>project_memberships</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Brukerne. Én rad per person, med e-post og navn. `id` er identiteten journalen bærer i `aktor_id`.</t>
+          <t>Eldre medlemsliste per prosjekt, etter e-post. Erstattet av `app_project_memberships` og skal fjernes (MS-15) når `viewer` finnes der (DB-05).</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bare gjennom databasefunksjonen `koe_resolve_identity`. Den kalles ved innlogging, når en webhook fra Catenda har en forfatter, og for hvert medlem når medlemslisten synkroniseres. E-post og navn oppdateres fra Catenda hver gang.</t>
+          <t>Triggeren `trg_auto_membership_on_project_create` legger inn en rad når et prosjekt opprettes. Koden som ser ut til å skrive tabellen, treffer en unik-skranke (AGENTS.md). Ingen leser den (DA-10).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ja. E-post og navn kommer fra Catenda-profilen og medlemslisten. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: app_identities.user_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.user_id (fremmednøkkel, ON DELETE CASCADE); app_sessions.user_id (fremmednøkkel, ON DELETE CASCADE); hendelse.actorid (uten fremmednøkkel); notat.aktor_id (uten fremmednøkkel); sak_metadata.created_by (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (project_id, user_email). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -891,24 +891,24 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>`email` og `name`.</t>
+          <t>`user_email`, `display_name`, `external_id`.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>app_identities</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Kobler en bruker til en ekstern identitet: tilbyder, utsteder og subjekt i Catenda. Sørger for at samme person får samme brukerrad uansett vei inn.</t>
+          <t>Brukerne. Én rad per person, med e-post og navn. `id` er identiteten journalen bærer i `aktor_id`.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bare gjennom `koe_resolve_identity`, som også er eneste leser. Ingen Python-kode leser eller skriver tabellen direkte (DA-07).</t>
+          <t>Bare gjennom databasefunksjonen `koe_resolve_identity`. Den kalles ved innlogging, når en webhook fra Catenda har en forfatter, og for hvert medlem når medlemslisten synkroniseres. E-post og navn oppdateres fra Catenda hver gang.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ja. Subjektet er Catenda-ID-en. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
+          <t>Ja. E-post og navn kommer fra Catenda-profilen og medlemslisten. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_project_memberships.catenda_subject (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: app_identities.user_id (fremmednøkkel, ON DELETE CASCADE); app_project_memberships.user_id (fremmednøkkel, ON DELETE CASCADE); app_sessions.user_id (fremmednøkkel, ON DELETE CASCADE); hendelse.actorid (uten fremmednøkkel); notat.aktor_id (uten fremmednøkkel); sak_metadata.created_by (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,19 +953,19 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>`subject` er en ekstern identifikator for en person.</t>
+          <t>`email` og `name`.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>app_sessions</t>
+          <t>app_identities</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer en hash av sesjonstokenet, CSRF-tokenet og når sesjonen utløper.</t>
+          <t>Kobler en bruker til en ekstern identitet: tilbyder, utsteder og subjekt i Catenda. Sørger for at samme person får samme brukerrad uansett vei inn.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -975,22 +975,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Opprettes ved innlogging og slettes ved utlogging (innloggingsrutene). Utløpte rader ryddes av `scripts/sync_catenda_memberships.py`. Om skriptet kjører noe sted, er ikke kontrollert.</t>
+          <t>Bare gjennom `koe_resolve_identity`, som også er eneste leser. Ingen Python-kode leser eller skriver tabellen direkte (DA-07).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja. Subjektet er Catenda-ID-en. Dataflyt: fra Catenda i C01, C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_project_memberships.catenda_subject (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1010,19 +1010,19 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`.</t>
+          <t>`subject` er en ekstern identifikator for en person.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>app_oauth_attempts</t>
+          <t>app_sessions</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Påbegynte innlogginger mot Catenda (OAuth). Kortlevde rader som binder tilbakekallet til nettleseren som startet innloggingen.</t>
+          <t>Innloggingssesjoner. Lagrer en hash av sesjonstokenet, CSRF-tokenet og når sesjonen utløper.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Opprettes når innloggingen starter, og brukes opp når Catenda sender brukeren tilbake (innloggingsrutene).</t>
+          <t>Opprettes ved innlogging og slettes ved utlogging (innloggingsrutene). Utløpte rader ryddes av `scripts/sync_catenda_memberships.py`. Om skriptet kjører noe sted, er ikke kontrollert.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente; bare hasher og en returadresse.</t>
+          <t>Knyttet til en bruker gjennom `user_id`.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>app_project_memberships</t>
+          <t>app_oauth_attempts</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hvem som er medlem av hvilket prosjekt, med rolle, og om medlemskapet er aktivt. En kopi av medlemslisten i Catenda, pluss appens egen `viewer_override`.</t>
+          <t>Påbegynte innlogginger mot Catenda (OAuth). Kortlevde rader som binder tilbakekallet til nettleseren som startet innloggingen.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1089,22 +1089,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Databasefunksjonen `koe_reconcile_memberships` synkroniserer mot Catenda ved innlogging, fra medlemsruta og fra skriptet `scripts/sync_catenda_memberships.py`. Medlemsruta setter `viewer_override`. Innloggingen kan også deaktivere medlemskap.</t>
+          <t>Opprettes når innloggingen starter, og brukes opp når Catenda sender brukeren tilbake (innloggingsrutene).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Delvis</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Ja. Medlemslisten hentes fra Catenda-prosjektet. Dataflyt: fra Catenda i C03, C04 (arket Dataflyt).</t>
+          <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (project_id, catenda_subject); unik (project_id, user_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE); catenda_subject → app_identities.subject (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>grunndata, kopi</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1124,19 +1124,19 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>`user_email`, `display_name` og `catenda_subject`.</t>
+          <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>app_membership_sync</t>
+          <t>app_project_memberships</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for et prosjekt sist ble synkronisert fra Catenda. Hindrer at en eldre synkronisering overskriver en nyere.</t>
+          <t>Hvem som er medlem av hvilket prosjekt, med rolle, og om medlemskapet er aktivt. En kopi av medlemslisten i Catenda, pluss appens egen `viewer_override`.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1146,22 +1146,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Av `koe_reconcile_memberships`, samtidig med medlemskapene.</t>
+          <t>Databasefunksjonen `koe_reconcile_memberships` synkroniserer mot Catenda ved innlogging, fra medlemsruta og fra skriptet `scripts/sync_catenda_memberships.py`. Medlemsruta setter `viewer_override`. Innloggingen kan også deaktivere medlemskap.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Delvis</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_project_id` er en Catenda-ID. Dataflyt: fra Catenda i C04 (arket Dataflyt).</t>
+          <t>Ja. Medlemslisten hentes fra Catenda-prosjektet. Dataflyt: fra Catenda i C03, C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (project_id, catenda_subject); unik (project_id, user_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); user_id → app_users.id (fremmednøkkel, ON DELETE CASCADE); catenda_subject → app_identities.subject (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata, kopi</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1181,19 +1181,19 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>`user_email`, `display_name` og `catenda_subject`.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>app_membership_sync</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Kobler et prosjekt i appen til prosjektet, dokumentbiblioteket og mappen i Catenda.</t>
+          <t>Når medlemslisten for et prosjekt sist ble synkronisert fra Catenda. Hindrer at en eldre synkronisering overskriver en nyere.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Av `koe_register_project`, som drift kaller gjennom `scripts/catenda_admin.py`.</t>
+          <t>Av `koe_reconcile_memberships`, samtidig med medlemskapene.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ja. ID-ene er Catenda-ID-er, oppgitt ved registrering. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. `catenda_project_id` er en Catenda-ID. Dataflyt: fra Catenda i C04 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → projects.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_membership_sync.catenda_project_id (uten fremmednøkkel); catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE CASCADE); catenda_models_cache.catenda_project_id (uten fremmednøkkel); catenda_topic_board_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.catenda_project_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → projects.id (fremmednøkkel, ON DELETE CASCADE); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_board_configs</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Hvilke topic boards i Catenda som hører til et prosjekt. Brukes blant annet til å finne prosjektet når en webhook kommer.</t>
+          <t>Kobler et prosjekt i appen til prosjektet, dokumentbiblioteket og mappen i Catenda.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Ja. `topic_board_id` er en Catenda-ID. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja. ID-ene er Catenda-ID-er, oppgitt ved registrering. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (topic_board_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: sak_metadata.catenda_board_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → projects.id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: app_membership_sync.catenda_project_id (uten fremmednøkkel); catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE CASCADE); catenda_models_cache.catenda_project_id (uten fremmednøkkel); catenda_topic_board_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE); sak_metadata.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>catenda_topic_board_configs</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hvilke Catenda-team som representerer TE og BH i et prosjekt. Appen utleder en brukers kontraktsside og team herfra og fra medlemskapet i Catenda.</t>
+          <t>Hvilke topic boards i Catenda som hører til et prosjekt. Brukes blant annet til å finne prosjektet når en webhook kommer.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Av `koe_set_contract_teams` og `koe_register_project`, som drift kaller gjennom `scripts/catenda_admin.py`. Etter B-02 punkt 4 er det bare drift som skal gjøre dette.</t>
+          <t>Av `koe_register_project`, som drift kaller gjennom `scripts/catenda_admin.py`.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Ja. `team_id` er en Catenda-ID. Dataflyt: fra Catenda i C18, C19 (arket Dataflyt).</t>
+          <t>Ja. `topic_board_id` er en Catenda-ID. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: hendelse.actorteam (uten fremmednøkkel); notat.aktor_team_id (uten fremmednøkkel); utkast.team (uten fremmednøkkel); vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (topic_board_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: sak_metadata.catenda_board_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>catenda_models_cache</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ment som kopi av BIM-modellene i Catenda per prosjekt, med fag. Tre BIM-ruter leser den og gir tomme lister når den er tom.</t>
+          <t>Hvilke Catenda-team som representerer TE og BH i et prosjekt. Appen utleder en brukers kontraktsside og team herfra og fra medlemskapet i Catenda.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ikke funnet. Ingen kode, databasefunksjon eller trigger skriver tabellen, og `upsert_cached_models` har ingen kaller (DM-02, foreløpig).</t>
+          <t>Av `koe_set_contract_teams` og `koe_register_project`, som drift kaller gjennom `scripts/catenda_admin.py`. Etter B-02 punkt 4 er det bare drift som skal gjøre dette.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Ja, etter formålet. Hvordan den skulle fylles, er ikke kjent. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja. `team_id` er en Catenda-ID. Dataflyt: fra Catenda i C18, C19 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (catenda_project_id, model_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE CASCADE). Vises til fra: hendelse.actorteam (uten fremmednøkkel); notat.aktor_team_id (uten fremmednøkkel); utkast.team (uten fremmednøkkel); vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>kopi</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1416,22 +1416,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>sak_bim_links</t>
+          <t>catenda_models_cache</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kobler en sak til et objekt i en BIM-modell, med modell, objekt-ID, IFC-type, egenskaper og hvem som koblet. Formålet er å se hvilke komponenter som fører til tvist (P2, P3).</t>
+          <t>Ment som kopi av BIM-modellene i Catenda per prosjekt, med fag. Tre BIM-ruter leser den og gir tomme lister når den er tom.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Når en bruker kobler et objekt til en sak eller fjerner koblingen (BIM-rutene).</t>
+          <t>Ikke funnet. Ingen kode, databasefunksjon eller trigger skriver tabellen, og `upsert_cached_models` har ingen kaller (DM-02, foreløpig).</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Modell- og objekt-ID-ene er fra Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, etter formålet. Hvordan den skulle fylles, er ikke kjent. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik indeks (sak_id, fag, COALESCE(model_id, ''::text), COALESCE(object_global_id, ''::text)). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (id); unik (catenda_project_id, model_id). Viser til: prosjekt_id → projects.id (uten fremmednøkkel); catenda_project_id → catenda_project_configs.catenda_project_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1456,54 +1456,54 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>kopi</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>`linked_by` identifiserer den som koblet (e-post, lest i ruta).</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>magic_links</t>
+          <t>sak_bim_links</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Etterlatenskap fra en eldre innlogging med lenke på e-post. Magic links utgår (P1), og tabellen skal fjernes (MS-15).</t>
+          <t>Kobler en sak til et objekt i en BIM-modell, med modell, objekt-ID, IFC-type, egenskaper og hvem som koblet. Formålet er å se hvilke komponenter som fører til tvist (P2, P3).</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Når en bruker kobler et objekt til en sak eller fjerner koblingen (BIM-rutene).</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Ingen kode leser eller skriver tabellen (DA-09). `MagicLinkManager` i `lib/auth/magic_link.py` lagrer i en JSON-fil, ikke her.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Modell- og objekt-ID-ene er fra Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (sak_id, fag, COALESCE(model_id, ''::text), COALESCE(object_global_id, ''::text)). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1513,29 +1513,29 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>`email`.</t>
+          <t>`linked_by` identifiserer den som koblet (e-post, lest i ruta).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>user_groups</t>
+          <t>magic_links</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Etterlatenskap: brukergrupper med roller og leder. Ingen kode bruker den, og den skal fjernes (MS-15).</t>
+          <t>Etterlatenskap fra en eldre innlogging med lenke på e-post. Magic links utgår (P1), og tabellen skal fjernes (MS-15).</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ingen. To databasefunksjoner, `get_user_role` og `get_user_role_by_email`, leser tabellen, men ingen kaller dem (DA-08).</t>
+          <t>Ingen kode leser eller skriver tabellen (DA-09). `MagicLinkManager` i `lib/auth/magic_link.py` lagrer i en JSON-fil, ikke her.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (user_id). Viser til: manager_id → user_groups.id (fremmednøkkel, ON DELETE SET NULL); user_id → auth.users.id (fremmednøkkel, ON DELETE CASCADE).</t>
+          <t>Nøkler: primærnøkkel (token). Viser til: sak_id → sak_metadata.sak_id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1580,19 +1580,19 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>`display_name`, `department` og koblingen til en bruker.</t>
+          <t>`email`.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>utkast</t>
+          <t>user_groups</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Teamets arbeidsutkast til et svar eller krav, per sak, spor og revisjon. Utkastet tilhører teamet, ikke personen, og er skjult for alle andre. `versjon` avviser samtidige lagringer.</t>
+          <t>Etterlatenskap: brukergrupper med roller og leder. Ingen kode bruker den, og den skal fjernes (MS-15).</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1602,64 +1602,64 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Når en bruker skriver i et skjema: utkastrutene (`GET`, `PUT` og `DELETE` på `/api/cases/&lt;sak_id&gt;/utkast/&lt;spor&gt;`).</t>
+          <t>Ingen. To databasefunksjoner, `get_user_role` og `get_user_role_by_email`, leser tabellen, men ingen kaller dem (DA-08).</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Teamet og kontraktssiden er utledet av teammedlemskapet i Catenda. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project, case_id, spor, revisjon, team). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); team → catenda_contract_teams.team_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id); unik (user_id). Viser til: manager_id → user_groups.id (fremmednøkkel, ON DELETE SET NULL); user_id → auth.users.id (fremmednøkkel, ON DELETE CASCADE).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SQLite</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>`oppdatert_av` og fritekst i `innhold`.</t>
+          <t>`display_name`, `department` og koblingen til en bruker.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>utkast</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Byggherrens interne godkjenning av svar i en sak: poster, godkjenningspakker og kommandoer, lagret som ett JSON-dokument per sak. Når en pakke er godkjent og publisert, skrives svarene til journalen.</t>
+          <t>Teamets arbeidsutkast til et svar eller krav, per sak, spor og revisjon. Utkastet tilhører teamet, ikke personen, og er skjult for alle andre. `versjon` avviser samtidige lagringer.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Godkjenningsrutene, gjennom `ApprovalService`.</t>
+          <t>Når en bruker skriver i et skjema: utkastrutene (`GET`, `PUT` og `DELETE` på `/api/cases/&lt;sak_id&gt;/utkast/&lt;spor&gt;`).</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Teamet og kontraktssiden er utledet av teammedlemskapet i Catenda. Innholdet kommer fra brukeren. Dataflyt: fra Catenda i C05 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project, case_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); body → items[].claimId → hendelse.event_id (uten fremmednøkkel); body → packages[].eventIds[] → hendelse.event_id (uten fremmednøkkel). Vises til fra: approval_outbox.id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project, case_id, spor, revisjon, team). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); team → catenda_contract_teams.team_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1694,44 +1694,44 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Godkjennere og saksbehandlere i JSON-dokumentet; ikke kontrollert i detalj.</t>
+          <t>`oppdatert_av` og fritekst i `innhold`.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>approval_outbox</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Kø for varsling etter at en godkjenningspakke er publisert. Én rad per pakke, med status (`pending`, `sending`, `delivered`, `failed`, `not_configured`).</t>
+          <t>Byggherrens interne godkjenning av svar i en sak: poster, godkjenningspakker og kommandoer, lagret som ett JSON-dokument per sak. Når en pakke er godkjent og publisert, skrives svarene til journalen.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenningsrutene, gjennom `ApprovalService`.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Av `ApprovalService` ved publisering og levering.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: kvittering for kall til Catenda i C07 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Viser til: id → approvals.body → packages[].id (uten fremmednøkkel); project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project, case_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); body → items[].claimId → hendelse.event_id (uten fremmednøkkel); body → packages[].eventIds[] → hendelse.event_id (uten fremmednøkkel). Vises til fra: approval_outbox.id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1751,29 +1751,29 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Godkjennere og saksbehandlere i JSON-dokumentet; ikke kontrollert i detalj.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>eo_approvals</t>
+          <t>approval_outbox</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Godkjenning av endringsordrer før utstedelse, lagret som ett JSON-dokument per prosjekt.</t>
+          <t>Kø for varsling etter at en godkjenningspakke er publisert. Én rad per pakke, med status (`pending`, `sending`, `delivered`, `failed`, `not_configured`).</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Endringsordrerutene, gjennom `EOApprovalService`.</t>
+          <t>Av `ApprovalService` ved publisering og levering.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: kvittering for kall til Catenda i C07 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project). Viser til: project → projects.id (uten fremmednøkkel); body → packages[].sakId → sak_metadata.sak_id (uten fremmednøkkel); body → packages[].request.koe_sak_ids[] → sak_metadata.sak_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (id). Viser til: id → approvals.body → packages[].id (uten fremmednøkkel); project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1808,19 +1808,19 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Godkjennere i JSON-dokumentet; ikke kontrollert i detalj.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>vedlegg</t>
+          <t>eo_approvals</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Register over vedlegg i en sak, med status: `staged` (valgt, ikke sendt), `pending` (sendt i en lagret hendelse, venter på Catenda) og `delivered` (lastet opp og koblet i Catenda). Filinnholdet mellomlagres her fram til opplastingen.</t>
+          <t>Godkjenning av endringsordrer før utstedelse, lagret som ett JSON-dokument per prosjekt.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Vedleggsrutene og hendelsesrutene, gjennom `VedleggRegistry`.</t>
+          <t>Endringsordrerutene, gjennom `EOApprovalService`.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting. Dataflyt: fra Catenda i C05, C08; til Catenda i C08; kvittering for kall til Catenda i C08 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project, case_id, vedlegg_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); lastet_opp_team → catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: hendelse.data → vedlegg_ids[] (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project). Viser til: project → projects.id (uten fremmednøkkel); body → packages[].sakId → sak_metadata.sak_id (uten fremmednøkkel); body → packages[].request.koe_sak_ids[] → sak_metadata.sak_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1865,62 +1865,119 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Filinnholdet kan inneholde personopplysninger; ikke kontrollert.</t>
+          <t>Godkjennere i JSON-dokumentet; ikke kontrollert i detalj.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>vedlegg</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Register over vedlegg i en sak, med status: `staged` (valgt, ikke sendt), `pending` (sendt i en lagret hendelse, venter på Catenda) og `delivered` (lastet opp og koblet i Catenda). Filinnholdet mellomlagres her fram til opplastingen.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Vedleggsrutene og hendelsesrutene, gjennom `VedleggRegistry`.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Delvis. `catenda_item_id` er Catendas ID etter opplasting. Dataflyt: fra Catenda i C05, C08; til Catenda i C08; kvittering for kall til Catenda i C08 (arket Dataflyt).</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (project, case_id, vedlegg_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); lastet_opp_team → catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: hendelse.data → vedlegg_ids[] (uten fremmednøkkel).</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>SQLite</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Filinnholdet kan inneholde personopplysninger; ikke kontrollert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>catenda_delivery_status</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Kvittering per hendelse for levering til Catenda (`pending`, `failed`, `delivered`), vist i banneret på saken. Ikke en kø for nye forsøk.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Hendelsesrutene.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Nei, men statusen gjelder et kall til Catenda. Dataflyt: kvittering for kall til Catenda i C06 (arket Dataflyt).</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (project, case_id, event_id). Viser til: project → projects.id (uten fremmednøkkel); case_id → sak_metadata.sak_id (uten fremmednøkkel); event_id → hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>SQLite</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente.</t>
         </is>
@@ -1937,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2037,7 +2094,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>leveringsoppdrag</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2072,29 +2129,29 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Saken notatet er skrevet i.</t>
+          <t>Saken brevet er sendt i. Slettes saken, slettes oppdraget med (ON DELETE CASCADE).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>sak_bim_links</t>
+          <t>leveringsoppdrag</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2104,7 +2161,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2114,14 +2171,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Saken BIM-objektet er koblet til.</t>
+          <t>Brevet oppdraget leverer. Unik, så hvert brev har ett oppdrag. Triggeren `leveringsoppdrag_vakt` avviser et oppdrag med en annen sak eller et annet prosjekt enn hendelsen.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>magic_links</t>
+          <t>notat</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2156,29 +2213,29 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Saken lenken gjaldt. Tabellen er en rest (MS-15).</t>
+          <t>Saken notatet er skrevet i.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>sak_bim_links</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2188,7 +2245,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2198,29 +2255,29 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet koblingen til Catenda gjelder. Én konfigurasjon per prosjekt.</t>
+          <t>Saken BIM-objektet er koblet til.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_board_configs</t>
+          <t>magic_links</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2240,14 +2297,14 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet topic boardet hører til. Et prosjekt kan ha flere boards.</t>
+          <t>Saken lenken gjaldt. Tabellen er en rest (MS-15).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -2257,12 +2314,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2272,7 +2329,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2282,29 +2339,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet teamet representerer TE eller BH i.</t>
+          <t>Prosjektet koblingen til Catenda gjelder. Én konfigurasjon per prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>app_identities</t>
+          <t>catenda_topic_board_configs</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2324,29 +2381,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Brukeren den eksterne identiteten tilhører.</t>
+          <t>Prosjektet topic boardet hører til. Et prosjekt kan ha flere boards.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>app_sessions</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2366,24 +2423,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Brukeren som er logget inn.</t>
+          <t>Prosjektet teamet representerer TE eller BH i.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>app_project_memberships</t>
+          <t>app_identities</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2408,14 +2465,14 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet medlemskapet gjelder.</t>
+          <t>Brukeren den eksterne identiteten tilhører.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>app_project_memberships</t>
+          <t>app_sessions</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2450,14 +2507,14 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Brukeren som er medlem. Én rad per prosjekt og bruker (UNIQUE).</t>
+          <t>Brukeren som er logget inn.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>app_membership_sync</t>
+          <t>app_project_memberships</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2482,7 +2539,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2492,24 +2549,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet synkroniseringen gjelder. Én rad per prosjekt.</t>
+          <t>Prosjektet medlemskapet gjelder.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>project_memberships</t>
+          <t>app_project_memberships</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2534,24 +2591,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet i den eldre medlemslisten. Tabellen er en rest (MS-15).</t>
+          <t>Brukeren som er medlem. Én rad per prosjekt og bruker (UNIQUE).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>user_groups</t>
+          <t>app_membership_sync</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>user_groups</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2566,34 +2623,34 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>SET NULL</t>
+          <t>CASCADE</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Lederen i brukergruppen. Tabellen er en rest (MS-15).</t>
+          <t>Prosjektet synkroniseringen gjelder. Én rad per prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>user_groups</t>
+          <t>project_memberships</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>auth.users</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2608,7 +2665,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2618,24 +2675,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Brukeren i Supabase-plattformens egen tabell, ikke `app_users`. Må løses om basen flyttes fra Supabase (B-12). Tabellen er en rest (MS-15).</t>
+          <t>Prosjektet i den eldre medlemslisten. Tabellen er en rest (MS-15).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>user_groups</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>manager_id</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>user_groups</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2645,7 +2702,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2653,27 +2710,31 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>SET NULL</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet hendelsen er skrevet i. Stemples av serveren fra autorisert kontekst, uten default (AGENTS.md, sikkerhetsinvariantene).</t>
+          <t>Lederen i brukergruppen. Tabellen er en rest (MS-15).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>user_groups</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>actorid</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>auth.users</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2683,18 +2744,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>CASCADE</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Den som sendte hendelsen. Verdien er `app_users.id` og aldri et navn (AGENTS.md). Kolonnen er `text`, `id` er `uuid`.</t>
+          <t>Brukeren i Supabase-plattformens egen tabell, ikke `app_users`. Må løses om basen flyttes fra Supabase (B-12). Tabellen er en rest (MS-15).</t>
         </is>
       </c>
     </row>
@@ -2706,17 +2771,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>actorteam</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2732,7 +2797,7 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, utledet fra teammedlemskapet i Catenda da hendelsen ble skrevet. Tom når teamet ikke var entydig. Lagres som 32 heksadesimaler uten bindestreker (`catenda_id`), mens `team_id` er `uuid`; en sammenstilling må normalisere.</t>
+          <t>Prosjektet hendelsen er skrevet i. Stemples av serveren fra autorisert kontekst, uten default (AGENTS.md, sikkerhetsinvariantene).</t>
         </is>
       </c>
     </row>
@@ -2744,17 +2809,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>referstoid</t>
+          <t>actorid</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2770,7 +2835,7 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Kravet et svar gjelder (`refererer_til_event_id`), i samme sak. Forretningsreglene for svar sammenlikner den med sporets gjeldende krav.</t>
+          <t>Den som sendte hendelsen. Verdien er `app_users.id` og aldri et navn (AGENTS.md). Kolonnen er `text`, `id` er `uuid`.</t>
         </is>
       </c>
     </row>
@@ -2782,17 +2847,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>data → vedlegg_ids[]</t>
+          <t>actorteam</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>vedlegg</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2802,35 +2867,35 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>mange til mange</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Vedleggene hendelsen sender. Leveringen til Catenda starter fra disse referansene etter at hendelsen er lagret. Sammenlikningen normaliserer med `catenda_id`. Går på tvers av lagene: journalen i PostgreSQL, registeret i SQLite.</t>
+          <t>Teamet avsenderen satt i, utledet fra teammedlemskapet i Catenda da hendelsen ble skrevet. Tom når teamet ikke var entydig. Lagres som 32 heksadesimaler uten bindestreker (`catenda_id`), mens `team_id` er `uuid`; en sammenstilling må normalisere.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>referstoid</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2846,29 +2911,29 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet notatet er skrevet i.</t>
+          <t>Kravet et svar gjelder (`refererer_til_event_id`), i samme sak. Forretningsreglene for svar sammenlikner den med sporets gjeldende krav.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>data → vedlegg_ids[]</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>vedlegg</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2878,35 +2943,35 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>mange til mange</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Forfatteren.</t>
+          <t>Vedleggene hendelsen sender. Leveringen til Catenda starter fra disse referansene etter at hendelsen er lagret. Sammenlikningen normaliserer med `catenda_id`. Går på tvers av lagene: journalen i PostgreSQL, registeret i SQLite.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>notat</t>
+          <t>leveringsoppdrag</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2922,7 +2987,7 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Skjermingen går på denne verdien; uten den vises notatet til ingen (AGENTS.md). Samme verdiform som `hendelse.actorteam`.</t>
+          <t>Prosjektet brevet er sendt i. Triggeren krever at det er hendelsens prosjekt.</t>
         </is>
       </c>
     </row>
@@ -2934,17 +2999,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2960,24 +3025,24 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Hendelsen notatet kommenterer, om noen.</t>
+          <t>Prosjektet notatet er skrevet i.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>notat</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2998,29 +3063,29 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet saken tilhører. Tilgangskontrollen holder hver forespørsel mot denne verdien.</t>
+          <t>Forfatteren.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>notat</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>app_users</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3036,29 +3101,29 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Den som opprettet saken. Bare delvis en kobling: verdien har tre former, og bare én av dem er `app_users.id` (MG-04).</t>
+          <t>Teamet som kan lese notatet. Skjermingen går på denne verdien; uten den vises notatet til ingen (AGENTS.md). Samme verdiform som `hendelse.actorteam`.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>notat</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3074,7 +3139,7 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Catenda-prosjektet saken ble opprettet i. Kolonnen er `text`, målet er `uuid`. Levering til Catenda bruker i dag den globale innstillingen, ikke denne verdien (INT-06).</t>
+          <t>Hendelsen notatet kommenterer, om noen.</t>
         </is>
       </c>
     </row>
@@ -3086,17 +3151,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>catenda_board_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>catenda_topic_board_configs</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>topic_board_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3112,29 +3177,29 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Topic boardet sakens topic ligger på. Kolonnen er `text`, målet er `uuid`. Levering til Catenda leser boardet herfra.</t>
+          <t>Prosjektet saken tilhører. Tilgangskontrollen holder hver forespørsel mot denne verdien.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sak_relations</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>source_sak_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>app_users</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3150,29 +3215,29 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Forseringen eller endringsordren som omfatter en annen sak. Fremmednøkkelen mangler (DB-04); hvordan relasjoner skal lagres, er B-01. Opprettes en forsering gjennom `/api/forsering/opprett`, er verdien topicens GUID, og saken har da ingen rad i `sak_metadata`.</t>
+          <t>Den som opprettet saken. Bare delvis en kobling: verdien har tre former, og bare én av dem er `app_users.id` (MG-04).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sak_relations</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>target_sak_id</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3188,29 +3253,29 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>KOE-saken som inngår i forseringen eller endringsordren.</t>
+          <t>Catenda-prosjektet saken ble opprettet i. Kolonnen er `text`, målet er `uuid`. Levering til Catenda bruker i dag den globale innstillingen, ikke denne verdien (INT-06).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>sak_relations</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>catenda_board_id</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>catenda_topic_board_configs</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>topic_board_id</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3226,29 +3291,29 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet relasjonen er skrevet i, stemplet fra autorisert kontekst.</t>
+          <t>Topic boardet sakens topic ligger på. Kolonnen er `text`, målet er `uuid`. Levering til Catenda leser boardet herfra.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>app_project_memberships</t>
+          <t>sak_relations</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>catenda_subject</t>
+          <t>source_sak_id</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>app_identities</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3264,29 +3329,29 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Personen i Catenda. `koe_reconcile_memberships` løser subjektet til `user_id` gjennom `koe_resolve_identity`, så de to kolonnene peker på samme person. Kontraktssiden slås opp med subjektet.</t>
+          <t>Forseringen eller endringsordren som omfatter en annen sak. Fremmednøkkelen mangler (DB-04); hvordan relasjoner skal lagres, er B-01. Opprettes en forsering gjennom `/api/forsering/opprett`, er verdien topicens GUID, og saken har da ingen rad i `sak_metadata`.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>app_membership_sync</t>
+          <t>sak_relations</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>target_sak_id</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3296,20 +3361,20 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Catenda-prosjektet synkroniseringen hentet fra. `ensure_fresh` godtar bare en synkronisering av prosjektets nåværende Catenda-prosjekt.</t>
+          <t>KOE-saken som inngår i forseringen eller endringsordren.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>catenda_models_cache</t>
+          <t>sak_relations</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -3340,29 +3405,29 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet modellene gjelder. BIM-rutene slår opp på denne. Tabellen fylles ikke (DM-02).</t>
+          <t>Prosjektet relasjonen er skrevet i, stemplet fra autorisert kontekst.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>catenda_models_cache</t>
+          <t>app_project_memberships</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>catenda_subject</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_configs</t>
+          <t>app_identities</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>catenda_project_id</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3378,29 +3443,29 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Catenda-prosjektet modellene ligger i. Kolonnen er `text`, målet er `uuid`.</t>
+          <t>Personen i Catenda. `koe_reconcile_memberships` løser subjektet til `user_id` gjennom `koe_resolve_identity`, så de to kolonnene peker på samme person. Kontraktssiden slås opp med subjektet.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>utkast</t>
+          <t>app_membership_sync</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3410,35 +3475,35 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet utkastet er skrevet i.</t>
+          <t>Catenda-prosjektet synkroniseringen hentet fra. `ensure_fresh` godtar bare en synkronisering av prosjektets nåværende Catenda-prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>utkast</t>
+          <t>catenda_models_cache</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3454,29 +3519,29 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Saken utkastet gjelder.</t>
+          <t>Prosjektet modellene gjelder. BIM-rutene slår opp på denne. Tabellen fylles ikke (DM-02).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>utkast</t>
+          <t>catenda_models_cache</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>catenda_project_configs</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>catenda_project_id</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3492,14 +3557,14 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Teamet som eier utkastet. Uten entydig team finnes det ikke noe utkast. Samme verdiform som `hendelse.actorteam`.</t>
+          <t>Catenda-prosjektet modellene ligger i. Kolonnen er `text`, målet er `uuid`.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>utkast</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3530,14 +3595,14 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet godkjenningen hører til.</t>
+          <t>Prosjektet utkastet er skrevet i.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>utkast</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -3562,35 +3627,35 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Saken. Ett dokument per prosjekt og sak.</t>
+          <t>Saken utkastet gjelder.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>utkast</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>body → items[].claimId</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3606,7 +3671,7 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Kravet en forberedt svarpost gjelder. Posten er ugyldig om et nyere krav eller en tilbaketrekking er kommet i sporet. Ved publisering blir verdien `refererer_til_event_id` i svaret.</t>
+          <t>Teamet som eier utkastet. Uten entydig team finnes det ikke noe utkast. Samme verdiform som `hendelse.actorteam`.</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3683,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>body → packages[].eventIds[]</t>
+          <t>project</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3638,35 +3703,35 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>mange til mange</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Hendelsene en publisert pakke ble til i journalen.</t>
+          <t>Prosjektet godkjenningen hører til.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>approval_outbox</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>case_id</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>body → packages[].id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3682,29 +3747,29 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Pakken varslingsjobben gjelder. Én jobb per pakke.</t>
+          <t>Saken. Ett dokument per prosjekt og sak.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>approval_outbox</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>body → items[].claimId</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3720,29 +3785,29 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet.</t>
+          <t>Kravet en forberedt svarpost gjelder. Posten er ugyldig om et nyere krav eller en tilbaketrekking er kommet i sporet. Ved publisering blir verdien `refererer_til_event_id` i svaret.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>approval_outbox</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>body → packages[].eventIds[]</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>hendelse</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3752,35 +3817,35 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>mange til mange</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Saken.</t>
+          <t>Hendelsene en publisert pakke ble til i journalen.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>eo_approvals</t>
+          <t>approval_outbox</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>projects</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>body → packages[].id</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3796,29 +3861,29 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet. Ett dokument per prosjekt med alle endringsordrene til godkjenning.</t>
+          <t>Pakken varslingsjobben gjelder. Én jobb per pakke.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>eo_approvals</t>
+          <t>approval_outbox</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>body → packages[].sakId</t>
+          <t>project</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>sak_metadata</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3828,25 +3893,25 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Saks-ID-en endringsordren er reservert under. Saken finnes først når ordren er utstedt; fram til da peker verdien på en sak som ikke finnes.</t>
+          <t>Prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>eo_approvals</t>
+          <t>approval_outbox</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>body → packages[].request.koe_sak_ids[]</t>
+          <t>case_id</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3866,20 +3931,20 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>mange til mange</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>KOE-sakene endringsordren skal omfatte.</t>
+          <t>Saken.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>vedlegg</t>
+          <t>eo_approvals</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3904,25 +3969,25 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet.</t>
+          <t>Prosjektet. Ett dokument per prosjekt med alle endringsordrene til godkjenning.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>vedlegg</t>
+          <t>eo_approvals</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>case_id</t>
+          <t>body → packages[].sakId</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3942,35 +4007,35 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Nedlasting krever at vedlegget står på nøyaktig denne saken.</t>
+          <t>Saks-ID-en endringsordren er reservert under. Saken finnes først når ordren er utstedt; fram til da peker verdien på en sak som ikke finnes.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>vedlegg</t>
+          <t>eo_approvals</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>body → packages[].request.koe_sak_ids[]</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>sak_metadata</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3980,20 +4045,20 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>mange til mange</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Teamet som lastet opp. Et vedlegg som ikke er sendt, er synlig bare for dette teamet. Samme verdiform som `hendelse.actorteam`.</t>
+          <t>KOE-sakene endringsordren skal omfatte.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>catenda_delivery_status</t>
+          <t>vedlegg</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4031,7 +4096,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>catenda_delivery_status</t>
+          <t>vedlegg</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4062,29 +4127,29 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Saken banneret vises på.</t>
+          <t>Saken vedlegget er lastet opp i. Nedlasting krever at vedlegget står på nøyaktig denne saken.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>catenda_delivery_status</t>
+          <t>vedlegg</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>hendelse</t>
+          <t>catenda_contract_teams</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4094,11 +4159,125 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som lastet opp. Et vedlegg som ikke er sendt, er synlig bare for dette teamet. Samme verdiform som `hendelse.actorteam`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>projects</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>sak_metadata</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Saken banneret vises på.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>catenda_delivery_status</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>hendelse</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Hendelsen kvitteringen gjelder. Kvitteringen skrives før hendelsen lagres; ved lesing teller bare kvitteringer for hendelser som finnes i journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
+          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/utledning/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#ISSUE-LEVERING). Bare testmiljøet skriver tabellen (#347).</t>
+          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#371). Bare testmiljøet skriver tabellen (#347).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -7551,7 +7551,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TE trekker ansvarsgrunnlaget, og med det kravene i saken.</t>
+          <t>TE trekker grunnlaget, og med det kravene i saken.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BH svarer på ansvarsgrunnlaget: godkjent, avslått eller frafalt pålegg, og om grunnlaget er varslet i tide.</t>
+          <t>BH svarer på grunnlaget: godkjent, avslått eller frafalt pålegg, og om grunnlaget er varslet i tide.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BH endrer sitt svar på ansvarsgrunnlaget («snuoperasjon»).</t>
+          <t>BH endrer sitt svar på grunnlaget («snuoperasjon»).</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1983,6 +1983,576 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Én rad per person. `id` er aktøren i journalen og notatet (AGENTS.md). Svarer til `app_users` i PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Delvis. Navn og e-post kommer fra Catenda-identiteten. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>grunndata</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Navn og e-post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_identities</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Identitetene til en bruker, unike på leverandør, issuer og subjekt. En Catenda-identitet har issueren og subjektformen basen kontrollerer, så samme person ikke får to brukerrader (AGENTS.md).</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>`koe.resolve_identity`, sammen med brukeren.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Ja, for leverandøren `catenda`: subjektet er Catenda-ID-en. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: app_identities.user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>grunndata</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Subjektet identifiserer en person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md).</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>ikke kontrollert Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>grunndata</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Delvis</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Ja, medlemslisten i Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: app_project_memberships.project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); app_project_memberships.user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>grunndata, kopi</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>E-post og visningsnavn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes i appen. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: catenda_contract_teams.internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel).</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>grunndata</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: sak_metadata.prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); sak_metadata.created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>`created_by` peker på en bruker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: hendelse.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); hendelse.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); hendelse.aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); hendelse.aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); hendelse.refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: notat.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); notat.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); notat.aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); notat.aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); notat.refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: leveringsoppdrag.event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag.sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag.prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: kjernebuffer.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); kjernebuffer.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>avledet</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Som journalen den er regnet fra.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1994,7 +2564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4280,6 +4850,872 @@
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Hendelsen kvitteringen gjelder. Kvitteringen skrives før hendelsen lagres; ved lesing teller bare kvitteringer for hendelser som finnes i journalen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_identities</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren identiteten hører til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet medlemskapet gjelder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_project_memberships</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren som er medlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>internal_project_id</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet teamet er knyttet til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Brukeren som opprettet saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Forfatteren, `app_users.id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Brevet oppdraget leverer. Unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Saken, i den sammensatte nøkkelen mot brevet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet, i den sammensatte nøkkelen mot brevet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>sak_id</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Saken bufferen er regnet for. Primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: app_identities.user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: app_project_memberships.project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); app_project_memberships.user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: catenda_contract_teams.internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: sak_metadata.prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); sak_metadata.created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: hendelse.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); hendelse.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); hendelse.aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); hendelse.aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); hendelse.refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: notat.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); notat.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); notat.aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); notat.aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); notat.refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: leveringsoppdrag.event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag.sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag.prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: kjernebuffer.sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); kjernebuffer.prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees.</t>
+          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees. Ingen inngang i `server/` kaller den ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, sammen med brukeren.</t>
+          <t>`koe.resolve_identity`, sammen med brukeren. Ingen inngang i `server/` kaller den ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2499,55 +2499,112 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>koe.skrivetidspunkt</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med transaksjonens ID som nøkkel. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (transaksjon). Ingen relasjoner til andre tabeller.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>koe.kjernebuffer</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (sak_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>avledet</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>uavklart</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>Som journalen den er regnet fra.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med transaksjonens ID som nøkkel. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med transaksjonens ID som nøkkel, og økta og når den logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` sletter den når transaksjons-ID-en brukes igjen.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` sletter den når transaksjons-ID-en brukes igjen.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` sletter den neste gang samme økt-ID eller transaksjons-ID fører et tidspunkt.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med transaksjonens ID som nøkkel, og økta og når den logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` sletter den neste gang samme økt-ID eller transaksjons-ID fører et tidspunkt.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (transaksjon). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `deactivated_at` er når medlemskapet sist ble gjort inaktivt; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). Ingen inngang kaller modulen ennå.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2271,37 +2271,37 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_project_configs</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Settes av driften. Ingen prosedyre skriver tabellen.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-en til Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2311,54 +2311,54 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>`created_by` peker på en bruker.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4). Svarer til `app_membership_sync` i PostgreSQL.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`. Ingen inngang kaller modulen ennå.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2378,19 +2378,19 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
+          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2430,24 +2430,24 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
+          <t>`created_by` peker på en bruker.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2492,36 +2492,36 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2539,72 +2539,186 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>koe.skrivetidspunkt</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>koe.kjernebuffer</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (sak_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>avledet</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>uavklart</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Som journalen den er regnet fra.</t>
         </is>
@@ -2621,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5039,7 +5153,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.catenda_project_configs</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -5064,7 +5178,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -5074,19 +5188,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet teamet er knyttet til.</t>
+          <t>Prosjektet i appen som er koblet til Catenda-prosjektet. Settes av driften (arbeidsvalget 16.10 i #53).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5106,7 +5220,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5116,24 +5230,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
+          <t>Prosjektet medlemslisten ble skrevet for (DL-U7).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5158,29 +5272,29 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Brukeren som opprettet saken.</t>
+          <t>Prosjektet teamet er knyttet til.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5200,29 +5314,29 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
+          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5242,7 +5356,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+          <t>Brukeren som opprettet saken.</t>
         </is>
       </c>
     </row>
@@ -5254,17 +5368,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5284,19 +5398,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
+          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5306,7 +5420,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5326,29 +5440,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`.</t>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5368,7 +5482,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -5380,17 +5494,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5410,29 +5524,29 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Forfatteren, `app_users.id`.</t>
+          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5442,7 +5556,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5452,29 +5566,29 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Brevet oppdraget leverer. Unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`.</t>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5494,7 +5608,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Saken, i den sammensatte nøkkelen mot brevet.</t>
+          <t>Forfatteren, `app_users.id`.</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5620,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5516,7 +5630,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5526,7 +5640,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5536,14 +5650,14 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot brevet.</t>
+          <t>Brevet oppdraget leverer. Unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5553,7 +5667,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5568,7 +5682,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -5578,14 +5692,14 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. Primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Saken, i den sammensatte nøkkelen mot brevet.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5595,7 +5709,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5620,72 +5734,76 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+          <t>Prosjektet, i den sammensatte nøkkelen mot brevet.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken bufferen er regnet for. Primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5693,17 +5811,21 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5734,14 +5856,14 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5771,6 +5893,82 @@
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.event_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.sak_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: event_id → koe.hendelse.event_id (fremmednøkkel, ON DELETE NO ACTION); sak_id → koe.hendelse.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.hendelse.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: sak_id → koe.sak_metadata.sak_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_id → koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5410,17 +5410,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5440,29 +5440,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
+          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`, så notatet står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
@@ -5494,17 +5494,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5524,29 +5524,29 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`.</t>
+          <t>Forfatteren, `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5566,29 +5566,29 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
+          <t>Brevet oppdraget leverer. `event_id` er unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`, så oppdraget står i brevets sak og prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5608,61 +5608,57 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Forfatteren, `app_users.id`.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Brevet oppdraget leverer. Unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5672,12 +5668,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5685,41 +5681,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Saken, i den sammensatte nøkkelen mot brevet.</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5727,248 +5719,46 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot brevet.</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Saken bufferen er regnet for. Primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>koe.kjernebuffer</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>prosjekt_id</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>koe.sak_metadata</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>prosjekt_id</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Fremmednøkkel</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Prosjektet, i den sammensatte nøkkelen mot saken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>koe.hendelse</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>aktor_team_id</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>koe.catenda_contract_teams</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>team_id</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Uten fremmednøkkel</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>koe.hendelse</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>refererer_til_event_id</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>koe.hendelse</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Uten fremmednøkkel</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>koe.notat</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>aktor_team_id</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>koe.catenda_contract_teams</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>team_id</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Uten fremmednøkkel</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>koe.notat</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>refererer_til_event_id</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>koe.hendelse</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Uten fremmednøkkel</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `deactivated_at` er når medlemskapet sist ble gjort inaktivt; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). Ingen inngang kaller modulen ennå.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Ingen inngang kaller modulen ennå.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_sync</t>
+          <t>koe.app_membership_absences</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4). Svarer til `app_membership_sync` i PostgreSQL.</t>
+          <t>Prosjektene der innloggingens liste over brukerens Catenda-prosjekter viste at brukeren ikke er med, for en bruker uten medlemskap der (DL-U9). `observed_at` er når innloggingens liste ble hentet, etter basens klokke. En medlemsliste hentet samtidig eller før gir ikke brukeren et nytt medlemskap. Har ingen tabell i PostgreSQL.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`. Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Ingen inngang kaller modulen ennå.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2385,37 +2385,37 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4). Svarer til `app_membership_sync` i PostgreSQL.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`. Ingen inngang kaller modulen ennå.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2435,19 +2435,19 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>`created_by` peker på en bruker.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
+          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2492,19 +2492,19 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
+          <t>`created_by` peker på en bruker.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
+          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2544,24 +2544,24 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2601,49 +2601,49 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2663,62 +2663,119 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>koe.skrivetidspunkt</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>koe.kjernebuffer</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>avledet</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>uavklart</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Som journalen den er regnet fra.</t>
         </is>
@@ -2735,7 +2792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5195,7 +5252,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_sync</t>
+          <t>koe.app_membership_absences</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -5220,7 +5277,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5230,24 +5287,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet medlemslisten ble skrevet for (DL-U7).</t>
+          <t>Prosjektet innloggingen viste at brukeren ikke er med i (DL-U9).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.app_membership_absences</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5272,19 +5329,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet teamet er knyttet til.</t>
+          <t>Brukeren som logget inn.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5304,7 +5361,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5314,24 +5371,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
+          <t>Prosjektet medlemslisten ble skrevet for (DL-U7).</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -5356,29 +5413,29 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Brukeren som opprettet saken.</t>
+          <t>Prosjektet teamet er knyttet til.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5398,19 +5455,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
+          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5440,14 +5497,14 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
+          <t>Brukeren som opprettet saken.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -5482,14 +5539,14 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`, så notatet står i sakens prosjekt.</t>
+          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -5524,29 +5581,29 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Forfatteren, `app_users.id`.</t>
+          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5556,7 +5613,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5566,29 +5623,29 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Brevet oppdraget leverer. `event_id` er unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`, så oppdraget står i brevets sak og prosjekt.</t>
+          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`, så notatet står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5598,7 +5655,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5608,90 +5665,98 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Forfatteren, `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>koe.leveringsoppdrag</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>(event_id, sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
           <t>koe.hendelse</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>aktor_team_id</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>koe.catenda_contract_teams</t>
-        </is>
-      </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Brevet oppdraget leverer. `event_id` er unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`, så oppdraget står i brevets sak og prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5722,14 +5787,14 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5759,6 +5824,82 @@
       </c>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med prosjektene brukeren ikke er med i og tidspunktene for innloggingene (`observed_at`, `updated_at`).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2778,6 +2778,120 @@
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>Som journalen den er regnet fra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`; ingen HTTP-inngang kaller modulen ennå (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_oauth_attempts</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`; ingen HTTP-inngang kaller modulen ennå (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5336,17 +5450,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_sync</t>
+          <t>koe.app_sessions</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>project_id</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5361,7 +5475,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5371,19 +5485,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet medlemslisten ble skrevet for (DL-U7).</t>
+          <t>Brukeren sesjonen er logget inn som.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>internal_project_id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5403,7 +5517,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5413,19 +5527,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet teamet er knyttet til.</t>
+          <t>Prosjektet medlemslisten ble skrevet for (DL-U7).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>internal_project_id</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5455,7 +5569,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
+          <t>Prosjektet teamet er knyttet til.</t>
         </is>
       </c>
     </row>
@@ -5467,12 +5581,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -5497,29 +5611,29 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Brukeren som opprettet saken.</t>
+          <t>Prosjektet saken hører til, uten standardverdi (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5539,7 +5653,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
+          <t>Brukeren som opprettet saken.</t>
         </is>
       </c>
     </row>
@@ -5551,17 +5665,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5581,29 +5695,29 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
+          <t>Saken brevet hører til. Sammensatt med `prosjekt_id`, så brevet står i sakens prosjekt. Kaskaderer ikke.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5623,7 +5737,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`, så notatet står i sakens prosjekt.</t>
+          <t>Avsenderen, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -5635,17 +5749,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -5665,29 +5779,29 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Forfatteren, `app_users.id`.</t>
+          <t>Saken notatet er skrevet i. Sammensatt med `prosjekt_id`, så notatet står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -5697,7 +5811,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5707,29 +5821,29 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Brevet oppdraget leverer. `event_id` er unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`, så oppdraget står i brevets sak og prosjekt.</t>
+          <t>Forfatteren, `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -5749,45 +5863,49 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Brevet oppdraget leverer. `event_id` er unik, så hvert brev har ett oppdrag. Sammensatt med `sak_id` og `prosjekt_id`, så oppdraget står i brevets sak og prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
@@ -5799,17 +5917,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5825,29 +5943,29 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5863,7 +5981,7 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
@@ -5875,17 +5993,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5900,6 +6018,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`.</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med tidspunktet for innloggingen (`created_at`, `expires_at`).</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`.</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med tidspunktet for innloggingen (`created_at`, `expires_at`).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -1067,7 +1067,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med tidspunktet for innloggingen (`created_at`, `expires_at`).</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med tidspunktet for innloggingen (`created_at`, `expires_at`).</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL.</t>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658).</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen.</t>
+          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen. `server/autorisasjon.ts` leser prosjektets kontraktsteam med `koe_api.kontraktsteam`, bare for en aktør med aktivt medlemskap uten leserollen (#658).</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt.</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/autorisasjon.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4). Svarer til `app_membership_sync` i PostgreSQL.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2). Svarer til `app_membership_sync` i PostgreSQL.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees. Ingen inngang i `server/` kaller den ennå (#53, del 3).</t>
+          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees. Tilbakekallet fra innloggingen kaller den fra `catendaIdentitet` i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, sammen med brukeren. Ingen inngang i `server/` kaller den ennå (#53, del 3).</t>
+          <t>`koe.resolve_identity`, sammen med brukeren, kalt gjennom `koe_api.catenda_identitet` fra tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`; ingen HTTP-inngang kaller modulen ennå (F0b-5a, #659).</t>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`; ingen HTTP-inngang kaller modulen ennå (F0b-5a, #659).</t>
+          <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md).</t>
+          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md). `server/prosjekter.ts` leser prosjektene aktøren er aktivt medlem i med `koe_api.brukerens_prosjekter`, og ett av dem med `koe_api.prosjekt` (#660). Tabellen har ikke `settings` og `created_by` fra PostgreSQL.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10).</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/autorisasjon.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658).</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10). Den tomme Catenda-ID-en er ikke lov; den merker synkroniseringsraden etter en slik endring.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Innloggingen kaller modulen fra tilbakekallet i `server/innlogging.ts` (F0b-5b).</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2). Svarer til `app_membership_sync` i PostgreSQL.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden den tomme Catenda-ID-en og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10).</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`. Ingen inngang kaller modulen ennå.</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, og triggeren `koe.catenda_project_configs_kobling_endret` når koblingen endres.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658).</t>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660).</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/autorisasjon.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658).</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/autorisasjon.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658). `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2). Svarer til `app_membership_sync` i PostgreSQL.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. Ingen HTTP-inngang kaller dem ennå (#53).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661); ingen HTTP-inngang oppretter saker ennå (#370).</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661).</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2685,22 +2685,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Ingen prosedyre skriver den ennå (#370, #371).</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2710,29 +2710,29 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2767,29 +2767,29 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2824,72 +2824,129 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -2906,7 +2963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5870,7 +5927,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5905,45 +5962,49 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
@@ -5955,17 +6016,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -5981,29 +6042,29 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6019,7 +6080,7 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
@@ -6031,17 +6092,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -6056,6 +6117,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#371). Bare testmiljøet skriver tabellen (#347).</t>
+          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#371). Ingen skriver tabellen lenger: TS-serveren skriver oppdraget i `koe.leveringsoppdrag` i SQL Server (F0b-7, #661).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Når TS-serveren lagrer et brev: i samme transaksjon som hendelsen i `hendelse`. Slettes bare med saken eller hendelsen (kaskade).</t>
+          <t>Ingen steder etter F0b-7 (#661). Fram til da skrev TS-serveren oppdraget i samme transaksjon som hendelsen i `hendelse`. Slettes bare med saken eller hendelsen (kaskade).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev TS-serveren skriver (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#371). Ingen skriver tabellen lenger: TS-serveren skriver oppdraget i `koe.leveringsoppdrag` i SQL Server (F0b-7, #661).</t>
+          <t>Leveringsoppdraget for et brev TS-serveren skrev fram til F0b-7 (LV-U1, B-03, dokumentet). Én rad per brev, og ett brev er ett dokument i Catenda. `innhold` fryser det som skal leveres: brevet slik det ble lagret, målet i Catenda, statusetiketten og versjonene. Raden er uforanderlig; et nytt leveringsforsøk sender samme innhold. Et lagret oppdrag beviser ikke at brevet er sendt eller mottatt. Forsøk, feil og kvitteringer er ikke bygget (#371). Ingen skriver tabellen lenger: TS-serveren skriver oppdraget i `koe.leveringsoppdrag` i SQL Server (F0b-7, #661).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`. Ingen HTTP-inngang kaller den ennå (#53).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661); ingen HTTP-inngang oppretter saker ennå (#370).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661), og `koe_api.opprett_sak` fra `POST /api/kjerne/saker` (#370).</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ingen prosedyre skriver den ennå (#370, #371).</t>
+          <t>Ingen prosedyre skriver den ennå (#741, #371).</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10). Den tomme Catenda-ID-en er ikke lov; den merker synkroniseringsraden etter en slik endring.</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10). Den tomme Catenda-ID-en er ikke lov; den merker synkroniseringsraden etter en slik endring. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-en til Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2613,22 +2613,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
+          <t>`koe_api.opprett_sak`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2663,19 +2663,19 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+          <t>Sakstittelen kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661).</t>
+          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `kobling_endret` eller `startet_paa_nytt`, med innloggingen som startet jobben på nytt. Raden endres ikke.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2685,22 +2685,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Ingen prosedyre skriver den ennå (#741, #371).</t>
+          <t>Prosedyrene for jobbkjøreren og driftsverktøyet i `database/migrasjoner/20261018100000_jobber.sql`.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Meldingen er fra klienten i `server/catenda.ts`, uten svarkropp. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2710,54 +2710,54 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Innloggingen til den i driften som startet en jobb på nytt.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2891,62 +2891,176 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>avledet</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Som journalen den er regnet fra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -2963,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5927,7 +6041,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5952,7 +6066,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -5962,29 +6076,29 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Saken jobben gjelder. Sammensatt med `prosjekt_id`, så jobben står i sakens prosjekt. En sak har høyst én jobb `catenda_topic` (#741).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>jobb_id</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>jobb_id</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -5994,7 +6108,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6004,143 +6118,155 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Jobben forsøket gjelder. Fremmednøkkelen hindrer også TRUNCATE av jobbene (#582).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>siste_forsoek</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Det siste forsøket på jobben. Fremmednøkkelen hindrer også TRUNCATE av forsøkene (#582).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6155,6 +6281,120 @@
       </c>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
+          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
+          <t>`koe_api.opprett_sak` og triggeren `koe.leveringsoppdrag_levering`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.kvitter_levering`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `kobling_endret` eller `startet_paa_nytt`, med innloggingen som startet jobben på nytt. Raden endres ikke.</t>
+          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med innloggingen som startet jobben på nytt. Raden endres ikke.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2784,29 +2784,29 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2881,29 +2881,29 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2938,29 +2938,29 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,72 +2995,129 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3077,7 +3134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6167,22 +6224,22 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6202,29 +6259,29 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Oppdraget en jobb `levering` leverer (#371). Hvert oppdrag har høyst én jobb.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -6234,7 +6291,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6244,67 +6301,71 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(leveringsoppdrag_id, forutsetning)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(leveringsoppdrag_id, operasjon)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme oppdrag.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6320,81 +6381,241 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen for dokumentet, så det er ingen fremmednøkkel.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t>koe.notat</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>refererer_til_event_id</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>koe.hendelse</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Uten fremmednøkkel</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen per kommando (invariant 4, #418): kommando-ID-en klienten gir, summen av innholdet serveren regner ut, og saken og brevet kommandoen ga. Lagres i samme transaksjon som brevet. Nøkkelen er prosjektet, aktøren og kommando-ID-en, så kvitteringen gjelder aktøren. Samme ID med samme sum gir brevet fra kvitteringen, og samme ID med en annen sum avvises (51410).</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.skriv_hendelse` og `koe_api.opprett_sak`, og leses av `koe_api.kvittering`, kalt fra `skrivHendelse` og `opprettSak` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker` og `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer`.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2834,36 +2834,36 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Aktørens `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,22 +2913,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2938,29 +2938,29 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3052,72 +3052,129 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3134,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6098,27 +6155,27 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>koe.jobb</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -6126,36 +6183,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Saken jobben gjelder. Sammensatt med `prosjekt_id`, så jobben står i sakens prosjekt. En sak har høyst én jobb `catenda_topic` (#741).</t>
+          <t>Aktøren som sendte kommandoen, `app_users.id`. Triggeren `koe.kvittering_samme_transaksjon` krever at den er lik `aktor_id` i brevet, så det er ingen egen fremmednøkkel.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>jobb_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>koe.jobb</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>jobb_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6165,7 +6218,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6175,7 +6228,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Jobben forsøket gjelder. Fremmednøkkelen hindrer også TRUNCATE av jobbene (#582).</t>
+          <t>Brevet kommandoen ga (#418). `event_id` er unik, så hvert brev har høyst én kvittering. Sammensatt med `sak_id` og `prosjekt_id`, så kvitteringen står i brevets sak og prosjekt.</t>
         </is>
       </c>
     </row>
@@ -6187,17 +6240,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>siste_forsoek</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>forsoek_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6207,7 +6260,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6217,29 +6270,29 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Det siste forsøket på jobben. Fremmednøkkelen hindrer også TRUNCATE av forsøkene (#582).</t>
+          <t>Saken jobben gjelder. Sammensatt med `prosjekt_id`, så jobben står i sakens prosjekt. En sak har høyst én jobb `catenda_topic` (#741).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>koe.jobbforsoek</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>jobb_id</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
           <t>koe.jobb</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>leveringsoppdrag_id</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>koe.leveringsoppdrag</t>
-        </is>
-      </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>jobb_id</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6249,7 +6302,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6259,29 +6312,29 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget en jobb `levering` leverer (#371). Hvert oppdrag har høyst én jobb.</t>
+          <t>Jobben forsøket gjelder. Fremmednøkkelen hindrer også TRUNCATE av jobbene (#582).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>leveringsoppdrag_id</t>
+          <t>siste_forsoek</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -6291,7 +6344,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6301,29 +6354,29 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
+          <t>Det siste forsøket på jobben. Fremmednøkkelen hindrer også TRUNCATE av forsøkene (#582).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>(leveringsoppdrag_id, forutsetning)</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>(leveringsoppdrag_id, operasjon)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6343,7 +6396,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme oppdrag.</t>
+          <t>Oppdraget en jobb `levering` leverer (#371). Hvert oppdrag har høyst én jobb.</t>
         </is>
       </c>
     </row>
@@ -6355,22 +6408,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>forsoek_id</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>forsoek_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6378,32 +6431,36 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen for dokumentet, så det er ingen fremmednøkkel.</t>
+          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(leveringsoppdrag_id, forutsetning)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(leveringsoppdrag_id, operasjon)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -6423,132 +6480,136 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme oppdrag.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen for dokumentet, så det er ingen fremmednøkkel.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -6579,14 +6640,14 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -6616,6 +6677,82 @@
       </c>
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>PDF-en av brevet i et leveringsoppdrag (#371 del 2, merknaden 12.10): bytene og SHA-256 av dem, lagret én gang per oppdrag før første opplasting. Kjøreren har kontrollert at PDF-en gjengir den frosne brevteksten tro (LV-U2), og laster opp den lagrede. Basen regner summen etter. Raden endres ikke, og bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2891,36 +2891,36 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Brevteksten kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2970,22 +2970,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3052,29 +3052,29 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3109,72 +3109,129 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3191,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6403,7 +6460,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -6428,7 +6485,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6438,49 +6495,45 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
+          <t>Oppdraget PDF-en gjengir. Det er én PDF per oppdrag (#371 del 2).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>(leveringsoppdrag_id, forutsetning)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>(leveringsoppdrag_id, operasjon)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme oppdrag.</t>
+          <t>Leasen PDF-en ble lagret med. Forsøket med samme ID lagres når forsøket er over, så det er ingen fremmednøkkel.</t>
         </is>
       </c>
     </row>
@@ -6492,22 +6545,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>forsoek_id</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>forsoek_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6515,32 +6568,36 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen for dokumentet, så det er ingen fremmednøkkel.</t>
+          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(leveringsoppdrag_id, forutsetning)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(leveringsoppdrag_id, operasjon)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6560,132 +6617,136 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme oppdrag.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen for dokumentet, så det er ingen fremmednøkkel.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -6716,14 +6777,14 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -6753,6 +6814,82 @@
       </c>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>koe.notat</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>refererer_til_event_id</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` når `koe_api.lagret_brevdokument` ikke gir noen PDF for oppdraget (#795 punkt 4).</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.lastet_opp_av (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel); koe.vedlegg.(bundet_av_event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2898,12 +2898,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. Bindingen kommer i V-2 og slettingen av innholdet etter levering i V-3.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2948,36 +2948,36 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Filen og filnavnet kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3052,29 +3052,29 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3109,29 +3109,29 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3166,72 +3166,129 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3248,7 +3305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6892,6 +6949,170 @@
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>koe.vedlegg</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>koe.vedlegg</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>lastet_opp_av</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>koe.vedlegg</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>(event_id, sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>koe.vedlegg</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>lastet_opp_team</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.lastet_opp_av (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.bruker_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningshandling.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningspakke.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.godkjenner_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.lastet_opp_av (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.aktor_team_id (uten fremmednøkkel); koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2955,37 +2955,37 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (runde 7 i #764). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, bruker_id); unik (prosjekt_id, plass). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3005,19 +3005,19 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Hvem som har fullmakt, med tittel og beløpsgrense.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Dagmulktssatsen i prosjektet, som fristdagene verdsettes med i fullmakten (GFK-06). Uten rad mangler satsen, og fristdagene kan ikke verdsettes (B-06). Driften setter den opp som fullmaktene.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
+          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3057,49 +3057,49 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ingen.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Et svar fra byggherren til intern godkjenning (S-1a, #818): brevet, grunnlaget fullmakten ble regnet av, saksbehandleren og teamet. Pakken er et utkast som bare teamet som laget den, ser, og uten team finnes den ikke (AGENTS.md). Den endres ikke; en ny pakke kan erstatte en returnert eller trukket.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3119,44 +3119,44 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Saksbehandleren (`aktor_id`) og innholdet i svaret.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Godkjennerne i en pakke i kjedens rekkefølge, regnet av `server/fullmakt.ts` da pakken ble laget. Endres ikke.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, steg); unik (pakke_id, godkjenner_id). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); godkjenner_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningshandling.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3166,46 +3166,46 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Godkjennerne (`godkjenner_id`).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.godkjenningshandling</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Hver godkjenning, retur og trekking av en pakke, i rekkefølge. En godkjenning fryser tittelen og grensen godkjenneren hadde da den ble gitt, så den står om fullmakten endres senere (B-04 punkt 2). Endres ikke.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.registrer_godkjenningshandling`, kalt fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3233,62 +3233,347 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Den som handlet (`aktor_id`) og begrunnelsen for en retur.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>koe.leveringskvittering</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>transaksjon</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Nei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_catenda_topic</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>grunndata</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Nei.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>koe.skrivetidspunkt</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Ingen kjente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>avledet</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Som journalen den er regnet fra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3305,7 +3590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7113,6 +7398,506 @@
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>koe.fullmakt</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (runde 7 i #764).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>koe.fullmakt</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>bruker_id</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Personen som har fullmakten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>koe.dagmulktssats</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>prosjekt_id</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>koe.projects</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>forrige_pakke_id</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>pakke_id</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>godkjenner_id</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenneren i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660).</t>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660). `koe_api.medlemmer`, også kalt derfra, leser de aktive medlemmene for en aktør med aktivt medlemskap (#820).</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10).</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10). `koe_api.sett_leserolle`, kalt fra `server/prosjekter.ts`, setter `viewer_override` for et annet aktivt medlem når aktøren er aktiv admin uten leserolle (#820).</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. Bindingen kommer i V-2 og slettingen av innholdet etter levering i V-3.</t>
+          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2); bindingen er den eneste endringen triggeren `koe.vedlegg_uten_endring` slipper gjennom. Slettingen av innholdet etter levering kommer i V-3.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`.</t>
+          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, og `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (runde 7 i #764). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
+          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (GFK-U1). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (runde 7 i #764).</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id); unik indeks (forrige_pakke_id) WHERE ([forrige_pakke_id] IS NOT NULL). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Én rad per person. `id` er aktøren i journalen og notatet (AGENTS.md). Svarer til `app_users` i PostgreSQL.</t>
+          <t>Én rad per person. `id` er aktøren i journalen og notatet (AGENTS.md). Svarer til `app_users` i PostgreSQL. Navnet leses for visningen av saken gjennom `koe_api.aktornavn`, bare for aktørene i en sak leseren kan lese (F-1b, #104), fra `lesAktornavn` i `server/lager.ts`.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>ikke kontrollert Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Navnet oppgis av driften; i Python kan det hentes fra Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764).</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes i appen. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes av driften. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Settes av driften. Ingen prosedyre skriver tabellen.</t>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet, biblioteket, mappen og boardet og gjør koblingen aktiv.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3451,29 +3451,29 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,72 +3508,129 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3590,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7046,22 +7103,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7081,45 +7138,49 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
@@ -7131,17 +7192,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7157,29 +7218,29 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7195,7 +7256,7 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
@@ -7207,17 +7268,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7233,34 +7294,34 @@
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7268,14 +7329,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
@@ -7287,17 +7344,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7317,7 +7374,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
@@ -7329,17 +7386,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7359,7 +7416,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -7371,22 +7428,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7394,37 +7451,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7432,14 +7493,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7508,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -7481,24 +7538,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -7523,29 +7580,29 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7565,7 +7622,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
@@ -7577,17 +7634,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7607,7 +7664,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
         </is>
       </c>
     </row>
@@ -7619,17 +7676,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>forrige_pakke_id</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pakke_id</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7649,7 +7706,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
         </is>
       </c>
     </row>
@@ -7661,22 +7718,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -7684,37 +7741,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -7722,14 +7783,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -7741,17 +7798,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7771,29 +7828,29 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>godkjenner_id</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7813,7 +7870,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Godkjenneren i steget.</t>
         </is>
       </c>
     </row>
@@ -7825,17 +7882,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7855,7 +7912,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
         </is>
       </c>
     </row>
@@ -7867,35 +7924,77 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet, biblioteket, mappen og boardet og gjør koblingen aktiv.</t>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet, biblioteket og mappen og gjør koblingen aktiv. Boardet skrives over når det er oppgitt. Ellers står det hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten.</t>
+          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten; skriptet sier fra når `--organisasjon` er en annen (#836).</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764).</t>
+          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764). Byttes Catenda-prosjektet, må teamene oppgis på nytt (#836).</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet, biblioteket og mappen og gjør koblingen aktiv. Boardet skrives over når det er oppgitt. Ellers står det hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet.</t>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (provider, issuer, subject). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.app_identities_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(godkjenningshandling_pakke_id, godkjenningshandling_loepenr) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.sak_catenda_topic_sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,29 +3508,29 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3565,72 +3565,129 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3647,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7061,22 +7118,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>app_identities_id</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_identities</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7086,7 +7143,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -7096,29 +7153,29 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>brevdokument_id</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7128,7 +7185,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7138,29 +7195,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(godkjenningshandling_pakke_id, godkjenningshandling_loepenr)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.godkjenningshandling</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(pakke_id, loepenr)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7170,7 +7227,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7180,34 +7237,34 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(prosjekt_id, aktor_id, kommando_id)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7215,37 +7272,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(leveringskvittering_oppdrag_id, leveringskvittering_operasjon)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(leveringsoppdrag_id, operasjon)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7253,37 +7314,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_med_saker_id</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7291,37 +7356,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>sak_catenda_topic_sak_id</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7329,32 +7398,36 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>koe.toemmingsvern</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>vedlegg_id</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
           <t>koe.vedlegg</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>(sak_id, prosjekt_id)</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>koe.sak_metadata</t>
-        </is>
-      </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7374,29 +7447,29 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7406,7 +7479,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -7416,29 +7489,29 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7448,7 +7521,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7458,72 +7531,76 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -7531,41 +7608,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -7573,41 +7646,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -7615,41 +7684,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -7657,36 +7722,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7706,19 +7767,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7748,34 +7809,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -7783,37 +7844,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -7821,31 +7886,27 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -7870,29 +7931,29 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7912,29 +7973,29 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -7954,47 +8015,379 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>(sak_id, prosjekt_id)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>forrige_pakke_id</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>pakke_id</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>aktor_id</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>aktor_team_id</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>koe.catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>team_id</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Uten fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>godkjenner_id</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenneren i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
           <t>koe.godkjenningshandling</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10). Den tomme Catenda-ID-en er ikke lov; den merker synkroniseringsraden etter en slik endring. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden den tomme Catenda-ID-en og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10).</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden ingen Catenda-ID (NULL) og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10, #726). Den tomme Catenda-ID-en er ikke lov.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel); koe.vedleggskvittering.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` når `koe_api.lagret_brevdokument` ikke gir noen PDF for oppdraget (#795 punkt 4).</t>
+          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` med PDF-en når samme prosedyre uten PDF ikke gir noen lagret for oppdraget (#795 punkt 4, #805 punkt 5).</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2); bindingen er den eneste endringen triggeren `koe.vedlegg_uten_endring` slipper gjennom. Slettingen av innholdet etter levering kommer i V-3.</t>
+          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2). Når Catenda har kvittert for dokumentet, setter `koe_api.kvitter_vedlegg` innholdet til NULL og beholder filnavnet og summen (LV-U12, V-3). Triggeren `koe.vedlegg_uten_endring` slipper bare gjennom de to endringene.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, og `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`.</t>
+          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`, og `koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.vedleggskvittering.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Et registrert brev har ingen rader (LV-U11); vedleggene kvitteres i `koe.vedleggskvittering`. Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3297,29 +3297,29 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver operasjon i leveringen av et vedlegg (V-3, del av #790, invariant 7): `dokument` når vedlegget ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Kvitteringen gjelder vedlegget, ikke oppdraget, så et vedlegg et senere brev viser til igjen, leveres ikke på nytt. Raden har leasen, oppdraget som leverte og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. `koe_api.kvitter_levering` kvitterer leveringen som fullført først når hvert vedlegg i brevet har en referanse.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3394,29 +3394,29 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,29 +3508,29 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3565,72 +3565,129 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3647,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7061,22 +7118,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7086,7 +7143,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -7096,29 +7153,29 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Vedlegget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (V-3, #790).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(vedlegg_id, forutsetning)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(vedlegg_id, operasjon)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7138,29 +7195,29 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
+          <t>Referansen på topicen forutsetter at dokumentet er kvittert for samme vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>leveringsoppdrag_id</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7170,7 +7227,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7180,29 +7237,29 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Oppdraget som leverte vedlegget. Et senere oppdrag som viser til samme vedlegg, får ingen ny rad.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>forsoek_id</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7218,148 +7275,160 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Leasen kvitteringen ble skrevet med. Forsøket med samme ID lagres når forsøket er over, etter kvitteringen, så det er ingen fremmednøkkel.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7367,41 +7436,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7409,41 +7474,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7451,36 +7512,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7496,29 +7553,29 @@
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7538,19 +7595,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7580,29 +7637,29 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7622,34 +7679,34 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -7657,36 +7714,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7706,19 +7759,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7748,34 +7801,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -7783,32 +7836,36 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7828,29 +7885,29 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>forrige_pakke_id</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pakke_id</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7870,29 +7927,29 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -7912,34 +7969,34 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -7947,54 +8004,218 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>godkjenner_id</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenneren i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
           <t>koe.godkjenningshandling</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Mappen fjernes også når biblioteket er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8667,7 +8667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11551,12 +11551,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>C19.1</t>
+          <t>C18.3</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>C19 Kontraktsteam endres av drift</t>
+          <t>C18 Prosjekt registreres av drift</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -11566,77 +11566,124 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>`scripts/catenda_admin.py contract-teams` med `--bh` og `--te`.</t>
+          <t>`scripts/catenda_admin.py register`.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Catenda: team og teammedlemmer</t>
+          <t>Catenda: topic board</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>catenda_contract_teams</t>
+          <t>Appen, lagres ikke</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>GET /v2/projects/{catenda_project_id}/teams</t>
+          <t>GET /opencde/bcf/3.0/projects?bimsync_project_id={catenda_project_id}</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>backend/scripts/catenda_admin.py:cmd_contract_teams; backend/repositories/auth_repository.py:AuthRepository.set_contract_teams; databasefunksjon:koe_set_contract_teams</t>
+          <t>server/registrering.ts:kjoer; server/catenda.ts:CatendaOAuth</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet.</t>
+          <t>Kontroll av at boardet drift oppgir, hører til Catenda-prosjektet. Bare TS-skriptet kontrollerer det (#836).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>C19.1</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>C19 Kontraktsteam endres av drift</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>`scripts/catenda_admin.py contract-teams` med `--bh` og `--te`.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>catenda_contract_teams</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>backend/scripts/catenda_admin.py:cmd_contract_teams; backend/repositories/auth_repository.py:AuthRepository.set_contract_teams; databasefunksjon:koe_set_contract_teams</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Kontroll av at teamene drift oppgir, finnes i Catenda-prosjektet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>C20.1</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>C20 Prosjektnavn hentes på nytt av drift</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>inn</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>`scripts/catenda_admin.py sync-name`.</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Catenda: prosjekter</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>projects</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>GET /v2/projects/{catenda_project_id}</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>backend/scripts/catenda_admin.py:fetch_catenda_project_name; backend/scripts/catenda_admin.py:cmd_sync_name</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Prosjektnavnet i Catenda, for hvert registrert prosjekt.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>GET /opencde/bcf/3.0/projects?bimsync_project_id={catenda_project_id}</t>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Kontroll av at boardet drift oppgir, hører til Catenda-prosjektet. Bare TS-skriptet kontrollerer det (#836).</t>
+          <t>`bimsync_project_id` for boardet drift oppgir, kontrollert mot Catenda-prosjektet. Bare TS-skriptet kontrollerer det (#836).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). `koe_api.opprett_sak` låser raden før den leses, så en ny sak og en ny registrering eller nye kontraktsteam skrives etter hverandre (#868). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id); unik (id, prosjekt_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); leveringsoppdrag_id → koe.leveringsoppdrag.id (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>leveringsoppdrag_id</t>
+          <t>(leveringsoppdrag_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget en jobb `levering` leverer (#371). Hvert oppdrag har høyst én jobb.</t>
+          <t>Oppdraget en jobb `levering` leverer (#371). Hvert oppdrag har høyst én jobb. Sammensatt med `prosjekt_id`, så jobben står i oppdragets prosjekt (#783).</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>leveringsoppdrag_id</t>
+          <t>(leveringsoppdrag_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget PDF-en gjengir. Det er én PDF per oppdrag (#371 del 2).</t>
+          <t>Oppdraget PDF-en gjengir. Det er én PDF per oppdrag (#371 del 2). Sammensatt med `prosjekt_id`, så PDF-en står i oppdragets prosjekt (#783).</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>leveringsoppdrag_id</t>
+          <t>(leveringsoppdrag_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371).</t>
+          <t>Oppdraget kvitteringen gjelder: én rad for dokumentet og én for referansen på topicen (B-03, #371). Sammensatt med `prosjekt_id`, så kvitteringen står i oppdragets prosjekt (#783).</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>leveringsoppdrag_id</t>
+          <t>(leveringsoppdrag_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Oppdraget som leverte vedlegget. Et senere oppdrag som viser til samme vedlegg, får ingen ny rad.</t>
+          <t>Oppdraget som leverte vedlegget. Et senere oppdrag som viser til samme vedlegg, får ingen ny rad. Sammensatt med `prosjekt_id`, så kvitteringen står i oppdragets prosjekt (#783).</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2675,7 +2675,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med innloggingen som startet jobben på nytt. Raden endres ikke.</t>
+          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med SID-en til innloggingen som startet jobben på nytt (`sid:0x…`, eller `driften uten SID`). Raden endres ikke.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Prosedyrene for jobbkjøreren og driftsverktøyet i `database/migrasjoner/20261018100000_jobber.sql`.</t>
+          <t>Prosedyrene for jobbkjøreren i `database/migrasjoner/20261018100000_jobber.sql`, og driftsverktøyet `koe_api.start_jobb_paa_nytt`, sist definert i `20261020121000_oppretter_tid_og_oppdragsnoekkel.sql`.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3411,12 +3411,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Behandlingen kommer i W-1b.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.motta_hendelse`, kalt av webhooken i `server/webhook.ts`.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, hele kroppen er Catendas. Dataflyt: fra Catenda i C21 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3461,19 +3461,19 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Ja: kroppen har navnet og e-postadressen til den som laget topicen i Catenda.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.toemmingsvern</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3575,19 +3575,19 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3622,29 +3622,29 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3679,72 +3679,129 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3761,7 +3818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7554,17 +7611,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_med_saker_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7596,17 +7653,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>sak_catenda_topic_sak_id</t>
+          <t>prosjekt_med_saker_id</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7638,17 +7695,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>sak_catenda_topic_sak_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7680,17 +7737,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>koe.vedleggskvittering</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>(vedlegg_id, operasjon)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7717,22 +7774,22 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(vedlegg_id, operasjon)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7742,7 +7799,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7752,29 +7809,29 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7794,29 +7851,29 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7836,45 +7893,49 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
@@ -7886,17 +7947,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -7912,29 +7973,29 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -7950,7 +8011,7 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
@@ -7962,17 +8023,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -7988,34 +8049,34 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8023,14 +8084,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
@@ -8042,17 +8099,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8072,7 +8129,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
@@ -8084,17 +8141,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -8114,7 +8171,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -8126,22 +8183,22 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -8149,37 +8206,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8187,14 +8248,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -8206,12 +8263,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8236,24 +8293,24 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8278,29 +8335,29 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8320,7 +8377,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
@@ -8332,17 +8389,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8362,7 +8419,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
         </is>
       </c>
     </row>
@@ -8374,17 +8431,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>forrige_pakke_id</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pakke_id</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8404,7 +8461,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
         </is>
       </c>
     </row>
@@ -8416,22 +8473,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -8439,37 +8496,41 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -8477,14 +8538,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
@@ -8496,17 +8553,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8526,29 +8583,29 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>godkjenner_id</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -8568,7 +8625,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Godkjenneren i steget.</t>
         </is>
       </c>
     </row>
@@ -8580,17 +8637,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -8610,7 +8667,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
         </is>
       </c>
     </row>
@@ -8622,35 +8679,77 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>
@@ -8667,7 +8766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11686,6 +11785,53 @@
       <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Prosjektnavnet i Catenda, for hvert registrert prosjekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>C21.1</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>C21 Webhooken fra Catenda til innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Webhook fra Catenda til `POST /webhook/catenda/&lt;hemmelig sti&gt;` i TS-serveren (W-1a, #819). Alle hendelsestyper tas imot, også `bcf.*`.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>koe.innkommende_hendelse</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Innkommende POST fra Catenda</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>server/webhook.ts:taImot; server/webhook.ts:mottaHendelse</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Hele kroppen, med `event.id` og `event.type` i egne kolonner.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370), og som `server/hendelser.ts` kaller for en ny topic fra TE i innboksen (KT-U6, #819).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Saken kan være opprettet fra en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_behandling.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Sakstittelen i `sak_opprettet` kan være tittelen på en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
+          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). En sak fra en topic i innboksen får ingen jobb; den kobles til topicen (W-1b.1, #819). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). En sak fra en topic i Catenda kobles til topicen i transaksjonen som oppretter saken (W-1b.1, #819). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741).</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741), og `koe_api.koble_topic`, kalt bare fra `koe_api.opprett_sak` når saken opprettes fra en topic i innboksen (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Behandlingen kommer i W-1b.</t>
+          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Hendelsene behandles av `server/hendelser.ts`, og utfallet står i `koe.innkommende_behandling` (W-1b.1).</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Raden kan ikke endres eller slettes; en kommentar tilbake til topicen (W-1b.2) endrer ikke utfallet.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.registrer_behandling`, kalt av `behandleEnHendelse` i `server/jobber.ts` med utfallet fra `server/hendelser.ts`.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3518,19 +3518,19 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei. `melding` er en fast feiltekst fra serveren.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>koe.toemmingsvern</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3632,19 +3632,19 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); innkommende_behandling_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3679,29 +3679,29 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3736,72 +3736,129 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3818,7 +3875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7653,17 +7710,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_med_saker_id</t>
+          <t>innkommende_behandling_id</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -7695,17 +7752,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>sak_catenda_topic_sak_id</t>
+          <t>prosjekt_med_saker_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7737,17 +7794,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>sak_catenda_topic_sak_id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7779,17 +7836,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.vedleggskvittering</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>(vedlegg_id, operasjon)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7816,22 +7873,22 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>(vedlegg_id, operasjon)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7841,7 +7898,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -7851,29 +7908,29 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7893,29 +7950,29 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -7935,34 +7992,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Hendelsen i innboksen utfallet gjelder (W-1b.1, #819). Nøkkelen er primærnøkkelen, så hver hendelse har høyst ett utfall, og en hendelse uten rad er ikke behandlet.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -7970,108 +8027,120 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Saken hendelsen ga, bare med utfallet `sak_opprettet` (KT-U6). Med et annet utfall er `sak_id` tom, så nøkkelen gjelder ikke, og `prosjekt_id` er prosjektet koblingen ga, eller tom når prosjektet er ukjent.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8087,34 +8156,34 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -8122,41 +8191,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -8164,26 +8229,22 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8193,12 +8254,12 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -8206,14 +8267,10 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
@@ -8225,22 +8282,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8248,27 +8305,31 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -8293,29 +8354,29 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -8335,34 +8396,34 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -8370,36 +8431,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8419,29 +8476,29 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -8461,24 +8518,24 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -8503,7 +8560,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
@@ -8515,22 +8572,22 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -8538,22 +8595,26 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>forrige_pakke_id</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -8563,7 +8624,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>pakke_id</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8583,19 +8644,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -8625,34 +8686,34 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -8660,36 +8721,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8709,47 +8766,173 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>godkjenner_id</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenneren i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>koe.godkjenningshandling</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>
@@ -8766,7 +8949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11832,6 +12015,288 @@
       <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Hele kroppen, med `event.id` og `event.type` i egne kolonner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>C22.1</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: innlogget bruker</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/user</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Integrasjonens egen Catenda-ID (`egenId`), som skiller topics integrasjonen laget. Lagres ikke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>C22.2</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: team og teammedlemmer</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/autorisasjon.ts:kontraktssideUtenSesjon; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Forfatterens side og team. Blir `aktor_rolle` og `aktor_team_id` i `sak_opprettet`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>C22.3</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_metadata</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>C22.3</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>C22.3</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_catenda_topic</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>C22.4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>koe.innkommende_behandling</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:registrerBehandling</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Utfallet, med prosjektet, saken og topicen når de er kjent.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -8949,7 +8949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Catenda: team og teammedlemmer</t>
+          <t>Catenda: topics</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12098,17 +12098,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
+          <t>GET /opencde/bcf/3.0/projects/{topic_board_id}/topics/{topic_guid}</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/autorisasjon.ts:kontraktssideUtenSesjon; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Forfatterens side og team. Blir `aktor_rolle` og `aktor_team_id` i `sak_opprettet`.</t>
+          <t>Topicens tittel, type og forfatter (`bimsync_creation_author.user.ref`), med integrasjonens token. Kroppen fra webhooken leses ikke for dem. 404 gir utfallet `ugyldig_hendelse` uten sak.</t>
         </is>
       </c>
     </row>
@@ -12135,34 +12135,34 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Catenda: webhook-varsel</t>
+          <t>Catenda: prosjektmedlemmer</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>Appen, lagres ikke</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Hendelsen i innboksen</t>
+          <t>GET /v2/projects/{catenda_project_id}/members?userType=user (sidevis)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+          <t>Om forfatteren er medlem av prosjektet, og navnet og e-posten som sendes til `koe_api.catenda_identitet`. Uten medlemskap løses ingen identitet.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>C22.3</t>
+          <t>C22.4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -12182,34 +12182,34 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Catenda: webhook-varsel</t>
+          <t>Catenda: team og teammedlemmer</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>Appen, lagres ikke</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Hendelsen i innboksen</t>
+          <t>GET /v2/projects/{catenda_project_id}/teams/{team_id}/members (sidevis), for hvert kontraktsteam</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/autorisasjon.ts:kontraktssideUtenSesjon; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+          <t>Forfatterens side og team. Blir `aktor_rolle` og `aktor_team_id` i `sak_opprettet`.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>C22.3</t>
+          <t>C22.5</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -12249,14 +12249,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad som ved innlogging.</t>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad med navnet og e-posten fra medlemslisten, som ved medlemssynkroniseringen, og bare for et medlem.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>C22.4</t>
+          <t>C22.5</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -12281,20 +12281,114 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
+          <t>koe.hendelse</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad med navnet og e-posten fra medlemslisten, som ved medlemssynkroniseringen, og bare for et medlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>C22.5</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>koe.sak_catenda_topic</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:behandle; server/kommandoer.ts:opprettSak</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Topicens tittel blir sakstittelen i `sak_opprettet`, og topicen og boardet blir koblingen i `koe.sak_catenda_topic`, skrevet av `koe_api.koble_topic` fra `koe_api.opprett_sak`. Kvitteringen i `koe.kvittering` har en kommando-ID avledet av hendelsen i innboksen. Forfatteren løses til en brukerrad med navnet og e-posten fra medlemslisten, som ved medlemssynkroniseringen, og bare for et medlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>C22.6</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>koe.innkommende_behandling</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Hendelsen i innboksen</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:registrerBehandling</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Utfallet, med prosjektet, saken og topicen når de er kjent.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_forsoek.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Raden kan ikke endres eller slettes; en kommentar tilbake til topicen (W-1b.2) endrer ikke utfallet.</t>
+          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Boardet topicen ble slått opp på, står med utfallet, så kommentaren skrives på samme board. Raden kan ikke endres eller slettes; kommentaren tilbake til topicen (W-1b.2) står i `koe.topic_kommentar` og endrer ikke utfallet.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22; til Catenda i C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION); koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_forsoek</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.registrer_innkommende_forsoek`, kalt av `behandleEnHendelse` og `skrivEnKommentar` i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. `melding` kan være feilmeldingen fra Catenda. Dataflyt: fra Catenda i C22, C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_forsoek_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3575,19 +3575,19 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei. `melding` er feilklassen og meldingen fra Catenda eller basen, uten saksdata.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.topic_kommentar</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Kvitteringen for kommentaren løkka skrev tilbake på topicen i Catenda (W-1b.2, #819), én rad per utfall. Utfallet `sak_opprettet` gir en kommentar med lenke og saksnummer (KT-U6), `topic_fra_bh` (KT-U7) og `sakstype_ikke_stoettet` (arbeidsvalget under OV-U1 i #819) en kommentar om hvorfor ingen sak er opprettet. Kommentarene på topicen leses først, og står teksten der alt, kvitteres den, så samme tekst skrives én gang. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.kvitter_kommentar`. Raden kan ikke endres eller slettes.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>`koe_api.kvitter_kommentar`, kalt av `skrivEnKommentar` i `server/jobber.ts` etter at kommentaren er funnet eller skrevet i Catenda.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-en til kommentaren er Catendas. Dataflyt: fra Catenda i C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.topic_kommentar_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3632,19 +3632,19 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>koe.toemmingsvern</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); innkommende_behandling_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3689,19 +3689,19 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3736,29 +3736,29 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); innkommende_behandling_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); innkommende_forsoek_id → koe.innkommende_forsoek.id (fremmednøkkel, ON DELETE NO ACTION); topic_kommentar_id → koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3803,62 +3803,176 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>koe.kjernebuffer</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>avledet</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>uavklart</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Som journalen den er regnet fra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>
@@ -3875,7 +3989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7752,17 +7866,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_med_saker_id</t>
+          <t>innkommende_forsoek_id</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_forsoek</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7794,17 +7908,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>sak_catenda_topic_sak_id</t>
+          <t>topic_kommentar_id</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.topic_kommentar</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>sak_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -7836,17 +7950,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>prosjekt_med_saker_id</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>vedlegg_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -7878,17 +7992,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
+          <t>sak_catenda_topic_sak_id</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>koe.vedleggskvittering</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>(vedlegg_id, operasjon)</t>
+          <t>sak_id</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -7915,22 +8029,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>vedlegg_id</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -7940,7 +8054,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -7950,29 +8064,29 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_behandling</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>innkommende_hendelse_id</t>
+          <t>(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_hendelse</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(vedlegg_id, operasjon)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -7982,7 +8096,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -7992,14 +8106,14 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Hendelsen i innboksen utfallet gjelder (W-1b.1, #819). Nøkkelen er primærnøkkelen, så hver hendelse har høyst ett utfall, og en hendelse uten rad er ikke behandlet.</t>
+          <t>Vernet mot TRUNCATE (#582). `koe.toemmingsvern` har ingen rader, så nøkkelen viser aldri til en rad.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_behandling</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -8024,7 +8138,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
+          <t>én til én</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8034,24 +8148,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Saken hendelsen ga, bare med utfallet `sak_opprettet` (KT-U6). Med et annet utfall er `sak_id` tom, så nøkkelen gjelder ikke, og `prosjekt_id` er prosjektet koblingen ga, eller tom når prosjektet er ukjent.</t>
+          <t>Saken topicen hører til. `sak_id` er primærnøkkelen, så hver sak har høyst én topic. Sammensatt med `prosjekt_id`, så raden står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8076,14 +8190,14 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
+          <t>Hendelsen i innboksen utfallet gjelder (W-1b.1, #819). Nøkkelen er primærnøkkelen, så hver hendelse har høyst ett utfall, og en hendelse uten rad er ikke behandlet.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -8108,7 +8222,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>én til én</t>
+          <t>mange til én</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8118,34 +8232,34 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
+          <t>Saken hendelsen ga, bare med utfallet `sak_opprettet` (KT-U6). Med et annet utfall er `sak_id` tom, så nøkkelen gjelder ikke, og `prosjekt_id` er prosjektet koblingen ga, eller tom når prosjektet er ukjent.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.innkommende_forsoek</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8153,151 +8267,167 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
+          <t>Hendelsen i innboksen forsøket gjelder (W-1b.2, #819). En hendelse kan ha mange forsøk, for behandlingen og for kommentaren.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.topic_kommentar</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>innkommende_hendelse_id</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Brevet dette brevet svarer på eller viser til.</t>
+          <t>Utfallet kommentaren hører til (W-1b.2, #819). Nøkkelen er primærnøkkelen, så hvert utfall har høyst én kvittering.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
+          <t>Prosjektet som har saker. `prosjekt_id` er primærnøkkelen, så hvert prosjekt står høyst én gang (F-1, #820).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>refererer_til_event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>event_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>mange til én</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
+          <t>én til én</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
+          <t>Saken bufferen er regnet for. `sak_id` er primærnøkkel, så én buffer per sak. Sammensatt med `prosjekt_id`.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -8305,41 +8435,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
+          <t>Teamet avsenderen satt i, i `catenda_id()`-formen. Tom når teamet ikke var entydig (DL-U4).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_av</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -8347,41 +8473,37 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
+          <t>Brevet dette brevet svarer på eller viser til.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>(event_id, sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -8389,36 +8511,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
+          <t>Teamet som kan lese notatet. Basen avviser et notat uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>lastet_opp_team</t>
+          <t>refererer_til_event_id</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>event_id</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -8434,29 +8552,29 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
+          <t>Brevet notatet gjelder, uten fremmednøkkel, så notatet kan slettes uten å røre journalen.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -8476,19 +8594,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
+          <t>Saken vedlegget er lastet opp i. Sammensatt med `prosjekt_id`, så vedlegget står i sakens prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>bruker_id</t>
+          <t>lastet_opp_av</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8518,29 +8636,29 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Personen som har fullmakten.</t>
+          <t>Den som lastet opp vedlegget, `app_users.id` (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>prosjekt_id</t>
+          <t>(bundet_av_event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>(event_id, sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -8560,34 +8678,34 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
+          <t>Den første hendelsen som viser til vedlegget (arbeidsvalg 4 i #790), i samme sak og prosjekt. Tom for et ubundet vedlegg.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>lastet_opp_team</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>(sak_id, prosjekt_id)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -8595,36 +8713,32 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
+          <t>Teamet som ser og sletter vedlegget før det er bundet. Basen avviser et vedlegg uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>forrige_pakke_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>pakke_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -8644,19 +8758,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
+          <t>Prosjektet fullmakten gjelder i. Driften setter den opp (GFK-U1).</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>aktor_id</t>
+          <t>bruker_id</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -8686,34 +8800,34 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren som utarbeidet svaret.</t>
+          <t>Personen som har fullmakten.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>aktor_team_id</t>
+          <t>prosjekt_id</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>team_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Uten fremmednøkkel</t>
+          <t>Fremmednøkkel</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -8721,32 +8835,36 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
+          <t>Prosjektet satsen gjelder i. Uten rad mangler satsen (B-06).</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>(sak_id, prosjekt_id)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -8766,29 +8884,29 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+          <t>Saken svaret i pakken gjelder, i samme prosjekt.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>godkjenner_id</t>
+          <t>forrige_pakke_id</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>koe.app_users</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pakke_id</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -8808,29 +8926,29 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Godkjenneren i steget.</t>
+          <t>Pakken som ble returnert eller trukket, og som denne erstatter.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>aktor_id</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.app_users</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -8850,34 +8968,34 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+          <t>Saksbehandleren som utarbeidet svaret.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>aktor_team_id</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>(pakke_id, steg)</t>
+          <t>team_id</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Fremmednøkkel</t>
+          <t>Uten fremmednøkkel</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -8885,54 +9003,218 @@
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>NO ACTION</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+          <t>Teamet som ser pakken. Basen avviser en pakke uten team (AGENTS.md).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Pakken steget hører til, med samme prosjekt og team, så radsikkerheten leser dem i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>godkjenner_id</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>koe.app_users</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Godkjenneren i steget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>koe.godkjenningshandling</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningspakke</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, prosjekt_id, aktor_team_id)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Pakken handlingen gjelder, med samme prosjekt og team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningssteg</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>(pakke_id, steg)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Fremmednøkkel</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>mange til én</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>NO ACTION</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Steget som er godkjent eller returnert. En trekking har ikke steg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>koe.godkjenningshandling</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>aktor_id</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>koe.app_users</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fremmednøkkel</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>mange til én</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>NO ACTION</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Den som godkjente, returnerte eller trakk pakken.</t>
         </is>
@@ -8949,7 +9231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12036,7 +12318,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -12083,7 +12365,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -12130,7 +12412,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -12177,7 +12459,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -12224,7 +12506,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -12271,7 +12553,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -12318,7 +12600,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -12365,7 +12647,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall (W-1b.1, #819).</t>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -12390,7 +12672,242 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Utfallet, med prosjektet, saken og topicen når de er kjent.</t>
+          <t>Utfallet, med prosjektet, saken, topicen og boardet når de er kjent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>C22.7</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>C22 Behandlingen av innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>inn</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter jobbene: `behandleEnHendelse` i `server/jobber.ts` tar den eldste hendelsen i `koe.innkommende_hendelse` uten utfall som ikke venter etter et forsøk (W-1b.1, #819).</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: webhook-varsel</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>koe.innkommende_forsoek</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Hendelsen i innboksen</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:behandleEnHendelse; server/hendelser.ts:registrerForsoek</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Steget `behandling` og feilklassen med meldingen, når Catenda eller basen ikke svarte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>C23.1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>C23 Kommentaren tilbake til topicen fra innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter behandlingen av innboksen: `skrivEnKommentar` i `server/jobber.ts` tar det eldste utfallet i `koe.innkommende_behandling` som skal ha en kommentar, ikke har en kvittering og ikke venter etter et forsøk (W-1b.2, #819).</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Appen, lagres ikke</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>GET /opencde/bcf/3.0/projects/{catenda_board_id}/topics/{catenda_topic_id}/comments</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:skrivEnKommentar; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Kommentarene på topicen, med ID og tekst. Står samme tekst der, brukes den kommentarens ID. Lagres ikke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>C23.2</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>C23 Kommentaren tilbake til topicen fra innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter behandlingen av innboksen: `skrivEnKommentar` i `server/jobber.ts` tar det eldste utfallet i `koe.innkommende_behandling` som skal ha en kommentar, ikke har en kvittering og ikke venter etter et forsøk (W-1b.2, #819).</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>koe.innkommende_behandling</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>POST /opencde/bcf/3.0/projects/{catenda_board_id}/topics/{catenda_topic_id}/comments</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:skrivEnKommentar; server/catenda.ts:innboksintegrasjon; server/catenda.ts:CatendaOAuth</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Kommentaren for utfallet (`comment`), bare når samme tekst ikke står på topicen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>C23.3</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>C23 Kommentaren tilbake til topicen fra innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter behandlingen av innboksen: `skrivEnKommentar` i `server/jobber.ts` tar det eldste utfallet i `koe.innkommende_behandling` som skal ha en kommentar, ikke har en kvittering og ikke venter etter et forsøk (W-1b.2, #819).</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>koe.topic_kommentar</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Svaret fra Catenda</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:skrivEnKommentar; server/hendelser.ts:kvitterKommentar</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>ID-en til kommentaren i Catenda, funnet eller skrevet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>C23.4</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>C23 Kommentaren tilbake til topicen fra innboksen i TS-serveren</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>ut</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Løkka i jobbkjøreren, etter behandlingen av innboksen: `skrivEnKommentar` i `server/jobber.ts` tar det eldste utfallet i `koe.innkommende_behandling` som skal ha en kommentar, ikke har en kvittering og ikke venter etter et forsøk (W-1b.2, #819).</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Catenda: kommentarer</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>koe.innkommende_forsoek</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Svaret fra Catenda, eller at det mangler</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>server/jobber.ts:skrivEnKommentar; server/hendelser.ts:registrerForsoek</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Steget `kommentar` og feilklassen med meldingen, når Catenda eller basen ikke svarte.</t>
         </is>
       </c>
     </row>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
+          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `topic_ikke_funnet` merker forsøkene der Catenda ikke fant topicen; bare de teller mot grensen for `ugyldig_hendelse`. `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives bare av bufferen i TS-kjernen (`kjerne/utledning/buffer.ts`, lageret i `sprakprove/kjernelagring/bane.ts` til skrivestien i #310).</t>
+          <t>Opprettes når en sak lages, gjennom `SakCreationService`: fra hendelsesrutene, for endringsordrer, og fra en ny topic i Catenda via webhook. Hvordan en forseringssak får sin rad, er ikke kontrollert. `cached_*` oppdateres etter lagrede hendelser (hendelsesrutene, forsering og godkjenning). `kjerne_*` skrives ikke lenger: bufferen i TS-kjernen lagres i SQL Server (#932).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en identitet sees. Tilbakekallet fra innloggingen kaller den fra `catendaIdentitet` i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet` eller `koe_api.entra_identitet`, oppretter brukeren første gang en identitet sees. Tilbakekallet fra innloggingen kaller den fra `catendaIdentitet` i `server/innlogging.ts` (F0b-5a, #659) og `entraIdentitet` i `server/entra.ts` (S-1c del 1, #831).</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Identitetene til en bruker, unike på leverandør, issuer og subjekt. En Catenda-identitet har issueren og subjektformen basen kontrollerer, så samme person ikke får to brukerrader (AGENTS.md).</t>
+          <t>Identitetene til en bruker, unike på leverandør, issuer og subjekt. En Catenda-identitet og en Entra-identitet har issueren og subjektformen basen kontrollerer, så samme person ikke får to brukerrader (AGENTS.md). For Entra er issueren v2-formen for tenanten og subjektet `oid`, begge i små bokstaver (#831).</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, sammen med brukeren, kalt gjennom `koe_api.catenda_identitet` fra tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>`koe.resolve_identity`, sammen med brukeren, kalt gjennom `koe_api.catenda_identitet` fra tilbakekallet i `server/innlogging.ts` (F0b-5a, #659) og gjennom `koe_api.entra_identitet` fra tilbakekallet for Entra ID (S-1c del 1, #831).</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Ja, for leverandøren `catenda`: subjektet er Catenda-ID-en. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, for leverandøren `catenda`: subjektet er Catenda-ID-en. For `entra` kommer subjektet fra ID-tokenet fra Entra ID. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.entra_tenant</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md). `server/prosjekter.ts` leser prosjektene aktøren er aktivt medlem i med `koe_api.brukerens_prosjekter`, og ett av dem med `koe_api.prosjekt` (#660). Tabellen har ikke `settings` og `created_by` fra PostgreSQL.</t>
+          <t>Tenantene i Entra ID driften har godkjent for innloggingen (S-1c del 1, #831). `koe_api.entra_identitet` avviser en issuer for en tenant som ikke står her. Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten; skriptet sier fra når `--organisasjon` er en annen (#836).</t>
+          <t>Driften, som eier. Lest av `koe_api.entra_identitet` fra `server/entra.ts`.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Navnet oppgis av driften; i Python kan det hentes fra Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (tenant_id). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2145,24 +2145,24 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>koe.app_project_memberships</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660). `koe_api.medlemmer`, også kalt derfra, leser de aktive medlemmene for en aktør med aktivt medlemskap (#820).</t>
+          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md). `server/prosjekter.ts` leser prosjektene aktøren er aktivt medlem i med `koe_api.brukerens_prosjekter`, og ett av dem med `koe_api.prosjekt` (#660). Tabellen har ikke `settings` og `created_by` fra PostgreSQL.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2172,22 +2172,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10). `koe_api.sett_leserolle`, kalt fra `server/prosjekter.ts`, setter `viewer_override` for et annet aktivt medlem når aktøren er aktiv admin uten leserolle (#820).</t>
+          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten; skriptet sier fra når `--organisasjon` er en annen (#836).</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Delvis</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Ja, medlemslisten i Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Navnet oppgis av driften; i Python kan det hentes fra Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2197,29 +2197,29 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>grunndata, kopi</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>E-post og visningsnavn.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.app_project_memberships</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen. `server/autorisasjon.ts` leser prosjektets kontraktsteam med `koe_api.kontraktsteam`, bare for en aktør med aktivt medlemskap uten leserollen (#658).</t>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660). `koe_api.medlemmer`, også kalt derfra, leser de aktive medlemmene for en aktør med aktivt medlemskap (#820).</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2229,22 +2229,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764). Byttes Catenda-prosjektet, må teamene oppgis på nytt (#836).</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10). `koe_api.sett_leserolle`, kalt fra `server/prosjekter.ts`, setter `viewer_override` for et annet aktivt medlem når aktøren er aktiv admin uten leserolle (#820).</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Delvis</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes av driften. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, medlemslisten i Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.aktor_team_id (uten fremmednøkkel); koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2254,29 +2254,29 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>grunndata, kopi</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>E-post og visningsnavn.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_project_configs</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). `koe_api.opprett_sak` låser raden før den leses, så en ny sak og en ny registrering eller nye kontraktsteam skrives etter hverandre (#868). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
+          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen. `server/autorisasjon.ts` leser prosjektets kontraktsteam med `koe_api.kontraktsteam`, bare for en aktør med aktivt medlemskap uten leserollen (#658).</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Mappen fjernes også når biblioteket er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
+          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764). Byttes Catenda-prosjektet, må teamene oppgis på nytt (#836).</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes av driften. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.aktor_team_id (uten fremmednøkkel); koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_absences</t>
+          <t>koe.catenda_project_configs</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene der innloggingens liste over brukerens Catenda-prosjekter viste at brukeren ikke er med, for en bruker uten medlemskap der (DL-U9). `observed_at` er når innloggingens liste ble hentet, etter basens klokke. En medlemsliste hentet samtidig eller før gir ikke brukeren et nytt medlemskap. Har ingen tabell i PostgreSQL.</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). `koe_api.opprett_sak` låser raden før den leses, så en ny sak og en ny registrering eller nye kontraktsteam skrives etter hverandre (#868). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Innloggingen kaller modulen fra tilbakekallet i `server/innlogging.ts` (F0b-5b).</t>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Mappen fjernes også når biblioteket er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id, user_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2373,24 +2373,24 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med prosjektene brukeren ikke er med i og tidspunktene for innloggingene (`observed_at`, `updated_at`).</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_sync</t>
+          <t>koe.app_membership_absences</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden ingen Catenda-ID (NULL) og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10, #726). Den tomme Catenda-ID-en er ikke lov.</t>
+          <t>Prosjektene der innloggingens liste over brukerens Catenda-prosjekter viste at brukeren ikke er med, for en bruker uten medlemskap der (DL-U9). `observed_at` er når innloggingens liste ble hentet, etter basens klokke. En medlemsliste hentet samtidig eller før gir ikke brukeren et nytt medlemskap. Har ingen tabell i PostgreSQL.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, og triggeren `koe.catenda_project_configs_kobling_endret` når koblingen endres.</t>
+          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Innloggingen kaller modulen fra tilbakekallet i `server/innlogging.ts` (F0b-5b).</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2435,44 +2435,44 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med prosjektene brukeren ikke er med i og tidspunktene for innloggingene (`observed_at`, `updated_at`).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden ingen Catenda-ID (NULL) og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10, #726). Den tomme Catenda-ID-en er ikke lov.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, og triggeren `koe.catenda_project_configs_kobling_endret` når koblingen endres.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370), og som `server/hendelser.ts` kaller for en ny topic fra TE i innboksen (KT-U6, #819).</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Saken kan være opprettet fra en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_behandling.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2492,19 +2492,19 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>`created_by` peker på en bruker.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
+          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661), og `koe_api.opprett_sak` fra `POST /api/kjerne/saker` (#370).</t>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370), og som `server/hendelser.ts` kaller for en ny topic fra TE i innboksen (KT-U6, #819).</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Sakstittelen i `sak_opprettet` kan være tittelen på en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Delvis. Saken kan være opprettet fra en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel); koe.vedlegg.(bundet_av_event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_behandling.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2549,19 +2549,19 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
+          <t>`created_by` peker på en bruker.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
+          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661), og `koe_api.opprett_sak` fra `POST /api/kjerne/saker` (#370).</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Sakstittelen i `sak_opprettet` kan være tittelen på en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel); koe.vedlegg.(bundet_av_event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2601,49 +2601,49 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>koe.jobb</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). En sak fra en topic i innboksen får ingen jobb; den kobles til topicen (W-1b.1, #819). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
+          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Ingen skriver ennå (#53, del 3).</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak` og triggeren `koe.leveringsoppdrag_levering`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.kvitter_levering`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2653,29 +2653,29 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Sakstittelen kan inneholde personopplysninger.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med SID-en til innloggingen som startet jobben på nytt (`sid:0x…`, eller `driften uten SID`). Raden endres ikke.</t>
+          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). En sak fra en topic i innboksen får ingen jobb; den kobles til topicen (W-1b.1, #819). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Prosedyrene for jobbkjøreren i `database/migrasjoner/20261018100000_jobber.sql`, og driftsverktøyet `koe_api.start_jobb_paa_nytt`, sist definert i `20261020121000_oppretter_tid_og_oppdragsnoekkel.sql`.</t>
+          <t>`koe_api.opprett_sak` og triggeren `koe.leveringsoppdrag_levering`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.kvitter_levering`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Nei. Meldingen er fra klienten i `server/catenda.ts`, uten svarkropp. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel); koe.vedleggskvittering.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2720,29 +2720,29 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Innloggingen til den i driften som startet en jobb på nytt.</t>
+          <t>Sakstittelen kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med SID-en til innloggingen som startet jobben på nytt (`sid:0x…`, eller `driften uten SID`). Raden endres ikke.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
+          <t>Prosedyrene for jobbkjøreren i `database/migrasjoner/20261018100000_jobber.sql`, og driftsverktøyet `koe_api.start_jobb_paa_nytt`, sist definert i `20261020121000_oppretter_tid_og_oppdragsnoekkel.sql`.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Meldingen er fra klienten i `server/catenda.ts`, uten svarkropp. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id); unik (id, prosjekt_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel); koe.vedleggskvittering.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+          <t>Innloggingen til den i driften som startet en jobb på nytt.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.kvittering</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen per kommando (invariant 4, #418): kommando-ID-en klienten gir, summen av innholdet serveren regner ut, og saken og brevet kommandoen ga. Lagres i samme transaksjon som brevet. Nøkkelen er prosjektet, aktøren og kommando-ID-en, så kvitteringen gjelder aktøren. Samme ID med samme sum gir brevet fra kvitteringen, og samme ID med en annen sum avvises (51410).</t>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse` og `koe_api.opprett_sak`, og leses av `koe_api.kvittering`, kalt fra `skrivHendelse` og `opprettSak` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker` og `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer`.</t>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id); unik (id, prosjekt_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Aktørens `app_users.id`.</t>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.brevdokument</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PDF-en av brevet i et leveringsoppdrag (#371 del 2, merknaden 12.10): bytene og SHA-256 av dem, lagret én gang per oppdrag før første opplasting. Kjøreren har kontrollert at PDF-en gjengir den frosne brevteksten tro (LV-U2), og laster opp den lagrede. Basen regner summen etter. Raden endres ikke, og bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en.</t>
+          <t>Kvitteringen per kommando (invariant 4, #418): kommando-ID-en klienten gir, summen av innholdet serveren regner ut, og saken og brevet kommandoen ga. Lagres i samme transaksjon som brevet. Nøkkelen er prosjektet, aktøren og kommando-ID-en, så kvitteringen gjelder aktøren. Samme ID med samme sum gir brevet fra kvitteringen, og samme ID med en annen sum avvises (51410).</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` med PDF-en når samme prosedyre uten PDF ikke gir noen lagret for oppdraget (#795 punkt 4, #805 punkt 5).</t>
+          <t>`koe_api.skriv_hendelse` og `koe_api.opprett_sak`, og leses av `koe_api.kvittering`, kalt fra `skrivHendelse` og `opprettSak` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker` og `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer`.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2891,19 +2891,19 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Brevteksten kan ha navn på personer i prosjektet.</t>
+          <t>Aktørens `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2). Når Catenda har kvittert for dokumentet, setter `koe_api.kvitter_vedlegg` innholdet til NULL og beholder filnavnet og summen (LV-U12, V-3). Triggeren `koe.vedlegg_uten_endring` slipper bare gjennom de to endringene.</t>
+          <t>PDF-en av brevet i et leveringsoppdrag (#371 del 2, merknaden 12.10): bytene og SHA-256 av dem, lagret én gang per oppdrag før første opplasting. Kjøreren har kontrollert at PDF-en gjengir den frosne brevteksten tro (LV-U2), og laster opp den lagrede. Basen regner summen etter. Raden endres ikke, og bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`, og `koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` med PDF-en når samme prosedyre uten PDF ikke gir noen lagret for oppdraget (#795 punkt 4, #805 punkt 5).</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2948,36 +2948,36 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Filen og filnavnet kan ha navn på personer i prosjektet.</t>
+          <t>Brevteksten kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (GFK-U1). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
+          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2). Når Catenda har kvittert for dokumentet, setter `koe_api.kvitter_vedlegg` innholdet til NULL og beholder filnavnet og summen (LV-U12, V-3). Triggeren `koe.vedlegg_uten_endring` slipper bare gjennom de to endringene.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`, og `koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id, bruker_id); unik (prosjekt_id, plass). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3005,19 +3005,19 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Hvem som har fullmakt, med tittel og beløpsgrense.</t>
+          <t>Filen og filnavnet kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktssatsen i prosjektet, som fristdagene verdsettes med i fullmakten (GFK-06). Uten rad mangler satsen, og fristdagene kan ikke verdsettes (B-06). Driften setter den opp som fullmaktene.</t>
+          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (GFK-U1). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, bruker_id); unik (prosjekt_id, plass). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3062,36 +3062,36 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Ingen.</t>
+          <t>Hvem som har fullmakt, med tittel og beløpsgrense.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Et svar fra byggherren til intern godkjenning (S-1a, #818): brevet, grunnlaget fullmakten ble regnet av, saksbehandleren og teamet. Pakken er et utkast som bare teamet som laget den, ser, og uten team finnes den ikke (AGENTS.md). Den endres ikke; en ny pakke kan erstatte en returnert eller trukket.</t>
+          <t>Dagmulktssatsen i prosjektet, som fristdagene verdsettes med i fullmakten (GFK-06). Uten rad mangler satsen, og fristdagene kan ikke verdsettes (B-06). Driften setter den opp som fullmaktene.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id); unik indeks (forrige_pakke_id) WHERE ([forrige_pakke_id] IS NOT NULL). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3119,19 +3119,19 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren (`aktor_id`) og innholdet i svaret.</t>
+          <t>Ingen.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Godkjennerne i en pakke i kjedens rekkefølge, regnet av `server/fullmakt.ts` da pakken ble laget. Endres ikke.</t>
+          <t>Et svar fra byggherren til intern godkjenning (S-1a, #818): brevet, grunnlaget fullmakten ble regnet av, saksbehandleren og teamet. Pakken er et utkast som bare teamet som laget den, ser, og uten team finnes den ikke (AGENTS.md). Den endres ikke; en ny pakke kan erstatte en returnert eller trukket.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id, steg); unik (pakke_id, godkjenner_id). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); godkjenner_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningshandling.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id); unik indeks (forrige_pakke_id) WHERE ([forrige_pakke_id] IS NOT NULL). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3176,19 +3176,19 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Godkjennerne (`godkjenner_id`).</t>
+          <t>Saksbehandleren (`aktor_id`) og innholdet i svaret.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Hver godkjenning, retur og trekking av en pakke, i rekkefølge. En godkjenning fryser tittelen og grensen godkjenneren hadde da den ble gitt, så den står om fullmakten endres senere (B-04 punkt 2). Endres ikke.</t>
+          <t>Godkjennerne i en pakke i kjedens rekkefølge, regnet av `server/fullmakt.ts` da pakken ble laget. Endres ikke.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.registrer_godkjenningshandling`, kalt fra `server/godkjenning.ts`.</t>
+          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(godkjenningshandling_pakke_id, godkjenningshandling_loepenr) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, steg); unik (pakke_id, godkjenner_id). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); godkjenner_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningshandling.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3233,19 +3233,19 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Den som handlet (`aktor_id`) og begrunnelsen for en retur.</t>
+          <t>Godkjennerne (`godkjenner_id`).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.godkjenningshandling</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Et registrert brev har ingen rader (LV-U11); vedleggene kvitteres i `koe.vedleggskvittering`. Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+          <t>Hver godkjenning, retur og trekking av en pakke, i rekkefølge. En godkjenning fryser tittelen og grensen godkjenneren hadde da den ble gitt, så den står om fullmakten endres senere (B-04 punkt 2). Endres ikke.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.registrer_godkjenningshandling`, kalt fra `server/godkjenning.ts`.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(godkjenningshandling_pakke_id, godkjenningshandling_loepenr) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3290,19 +3290,19 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Den som handlet (`aktor_id`) og begrunnelsen for en retur.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>koe.vedleggskvittering</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver operasjon i leveringen av et vedlegg (V-3, del av #790, invariant 7): `dokument` når vedlegget ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Kvitteringen gjelder vedlegget, ikke oppdraget, så et vedlegg et senere brev viser til igjen, leveres ikke på nytt. Raden har leasen, oppdraget som leverte og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. `koe_api.kvitter_levering` kvitterer leveringen som fullført først når hvert vedlegg i brevet har en referanse.</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Et registrert brev har ingen rader (LV-U11); vedleggene kvitteres i `koe.vedleggskvittering`. Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3354,37 +3354,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). En sak fra en topic i Catenda kobles til topicen i transaksjonen som oppretter saken (W-1b.1, #819). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Kvitteringen for hver operasjon i leveringen av et vedlegg (V-3, del av #790, invariant 7): `dokument` når vedlegget ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Kvitteringen gjelder vedlegget, ikke oppdraget, så et vedlegg et senere brev viser til igjen, leveres ikke på nytt. Raden har leasen, oppdraget som leverte og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. `koe_api.kvitter_levering` kvitterer leveringen som fullført først når hvert vedlegg i brevet har en referanse.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741), og `koe_api.koble_topic`, kalt bare fra `koe_api.opprett_sak` når saken opprettes fra en topic i innboksen (W-1b.1, #819).</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.sak_catenda_topic_sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_hendelse</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Hendelsene behandles av `server/hendelser.ts`, og utfallet står i `koe.innkommende_behandling` (W-1b.1).</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). En sak fra en topic i Catenda kobles til topicen i transaksjonen som oppretter saken (W-1b.1, #819). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3426,22 +3426,22 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.motta_hendelse`, kalt av webhooken i `server/webhook.ts`.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741), og `koe_api.koble_topic`, kalt bare fra `koe_api.opprett_sak` når saken opprettes fra en topic i innboksen (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Ja, hele kroppen er Catendas. Dataflyt: fra Catenda i C21 (arket Dataflyt).</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_forsoek.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.sak_catenda_topic_sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3451,29 +3451,29 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Ja: kroppen har navnet og e-postadressen til den som laget topicen i Catenda.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_behandling</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Boardet topicen ble slått opp på, står med utfallet, så kommentaren skrives på samme board. Raden kan ikke endres eller slettes; kommentaren tilbake til topicen (W-1b.2) står i `koe.topic_kommentar` og endrer ikke utfallet.</t>
+          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Hendelsene behandles av `server/hendelser.ts`, og utfallet står i `koe.innkommende_behandling` (W-1b.1).</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.registrer_behandling`, kalt av `behandleEnHendelse` i `server/jobber.ts` med utfallet fra `server/hendelser.ts`.</t>
+          <t>`koe_api.motta_hendelse`, kalt av webhooken i `server/webhook.ts`.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22; til Catenda i C23 (arket Dataflyt).</t>
+          <t>Ja, hele kroppen er Catendas. Dataflyt: fra Catenda i C21 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION); koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_forsoek.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3518,19 +3518,19 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Nei. `melding` er en fast feiltekst fra serveren.</t>
+          <t>Ja: kroppen har navnet og e-postadressen til den som laget topicen i Catenda.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_forsoek</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `topic_ikke_funnet` merker forsøkene der Catenda ikke fant topicen; bare de teller mot grensen for `ugyldig_hendelse`. `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
+          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Boardet topicen ble slått opp på, står med utfallet, så kommentaren skrives på samme board. Raden kan ikke endres eller slettes; kommentaren tilbake til topicen (W-1b.2) står i `koe.topic_kommentar` og endrer ikke utfallet.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.registrer_innkommende_forsoek`, kalt av `behandleEnHendelse` og `skrivEnKommentar` i `server/jobber.ts`.</t>
+          <t>`koe_api.registrer_behandling`, kalt av `behandleEnHendelse` i `server/jobber.ts` med utfallet fra `server/hendelser.ts`.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `melding` kan være feilmeldingen fra Catenda. Dataflyt: fra Catenda i C22, C23 (arket Dataflyt).</t>
+          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22; til Catenda i C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_forsoek_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION); koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3575,19 +3575,19 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Nei. `melding` er feilklassen og meldingen fra Catenda eller basen, uten saksdata.</t>
+          <t>Nei. `melding` er en fast feiltekst fra serveren.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>koe.topic_kommentar</t>
+          <t>koe.innkommende_forsoek</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for kommentaren løkka skrev tilbake på topicen i Catenda (W-1b.2, #819), én rad per utfall. Utfallet `sak_opprettet` gir en kommentar med lenke og saksnummer (KT-U6), `topic_fra_bh` (KT-U7) og `sakstype_ikke_stoettet` (arbeidsvalget under OV-U1 i #819) en kommentar om hvorfor ingen sak er opprettet. Kommentarene på topicen leses først, og står teksten der alt, kvitteres den, så samme tekst skrives én gang. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.kvitter_kommentar`. Raden kan ikke endres eller slettes.</t>
+          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `topic_ikke_funnet` merker forsøkene der Catenda ikke fant topicen; bare de teller mot grensen for `ugyldig_hendelse`. `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_kommentar`, kalt av `skrivEnKommentar` i `server/jobber.ts` etter at kommentaren er funnet eller skrevet i Catenda.</t>
+          <t>`koe_api.registrer_innkommende_forsoek`, kalt av `behandleEnHendelse` og `skrivEnKommentar` i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-en til kommentaren er Catendas. Dataflyt: fra Catenda i C23 (arket Dataflyt).</t>
+          <t>Delvis. `melding` kan være feilmeldingen fra Catenda. Dataflyt: fra Catenda i C22, C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.topic_kommentar_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_forsoek_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3632,19 +3632,19 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Nei. `melding` er feilklassen og meldingen fra Catenda eller basen, uten saksdata.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.topic_kommentar</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Kvitteringen for kommentaren løkka skrev tilbake på topicen i Catenda (W-1b.2, #819), én rad per utfall. Utfallet `sak_opprettet` gir en kommentar med lenke og saksnummer (KT-U6), `topic_fra_bh` (KT-U7) og `sakstype_ikke_stoettet` (arbeidsvalget under OV-U1 i #819) en kommentar om hvorfor ingen sak er opprettet. Kommentarene på topicen leses først, og står teksten der alt, kvitteres den, så samme tekst skrives én gang. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.kvitter_kommentar`. Raden kan ikke endres eller slettes.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.kvitter_kommentar`, kalt av `skrivEnKommentar` i `server/jobber.ts` etter at kommentaren er funnet eller skrevet i Catenda.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, ID-en til kommentaren er Catendas. Dataflyt: fra Catenda i C23 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.topic_kommentar_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3689,19 +3689,19 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>koe.skrivetidspunkt</t>
+          <t>koe.prosjekt_med_saker</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
+          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.prosjekt_med_saker_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>koe.toemmingsvern</t>
+          <t>koe.skrivetidspunkt</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
+          <t>Tidspunktet basen ga for skrivingen i en transaksjon, med økt-ID-en som nøkkel, og transaksjonen og når økta logget inn, fordi transaksjons-ID-en begynner på nytt etter en omstart. `koe_api.skriv_hendelse` godtar bare dette tidspunktet på brevet, i samme transaksjon og økt (DL-U3, svaret 16.10 i #53), og bare i 30 sekunder etter at det ble gitt (#599). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
+          <t>`koe_api.skrivetidspunkt` fører raden, og `koe_api.skriv_hendelse` sletter den i samme transaksjon. Kalt fra `skrivHendelse` i `server/kommandoer.ts`, som ruller tilbake når den ikke skriver. En kaller som committer uten å skrive, etterlater raden; `skrivetidspunkt` erstatter den neste gang samme økt-ID fører et tidspunkt. Tabellen har høyst én rad per økt-ID.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); innkommende_behandling_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); innkommende_forsoek_id → koe.innkommende_forsoek.id (fremmednøkkel, ON DELETE NO ACTION); topic_kommentar_id → koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (oekt). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3803,19 +3803,19 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>koe.kjernebuffer</t>
+          <t>koe.toemmingsvern</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
+          <t>Vernet mot TRUNCATE for de uforanderlige tabellene ingen annen fremmednøkkel viser til (#582). TRUNCATE avfyrer ingen trigger, men avvises for en tabell en fremmednøkkel viser til. En nøkkel en tabell har til seg selv, hindrer ikke TRUNCATE. Tabellen kan ikke ha rader (`toemmingsvern_tom`), og kjøretiden har ingen rett på den.</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
+          <t>Ingen. Migrasjonen lager tabellen, og skranken avviser hver rad.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: ingen. Viser til: app_identities_id → koe.app_identities.id (fremmednøkkel, ON DELETE NO ACTION); brevdokument_id → koe.brevdokument.leveringsoppdrag_id (fremmednøkkel, ON DELETE NO ACTION); (godkjenningshandling_pakke_id, godkjenningshandling_loepenr) → koe.godkjenningshandling.(pakke_id, loepenr) (fremmednøkkel, ON DELETE NO ACTION); (kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) → koe.kvittering.(prosjekt_id, aktor_id, kommando_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringskvittering_oppdrag_id, leveringskvittering_operasjon) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); innkommende_behandling_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); innkommende_forsoek_id → koe.innkommende_forsoek.id (fremmednøkkel, ON DELETE NO ACTION); topic_kommentar_id → koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); prosjekt_med_saker_id → koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); sak_catenda_topic_sak_id → koe.sak_catenda_topic.sak_id (fremmednøkkel, ON DELETE NO ACTION); vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3850,29 +3850,29 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>avledet</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Som journalen den er regnet fra.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>koe.app_sessions</t>
+          <t>koe.kjernebuffer</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+          <t>Visningen kjernen regner ut av journalen, med versjonene den er regnet med (B-10). Ingen regel og ingen bindende kommando leser den.</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3907,72 +3907,129 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>avledet</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+          <t>Som journalen den er regnet fra.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>koe.app_sessions</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Innloggingssesjoner. Lagrer SHA-256 av sesjonstokenet, CSRF-tokenet og når sesjonen utløper, 8 timer etter opprettelsen. Svarer til `app_sessions` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sesjon` oppretter, `koe_api.slett_sesjon` sletter og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av tilbakekallet og utloggingen i `server/innlogging.ts` (F0b-5a, #659).</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Nøkler: primærnøkkel (token_hash). Viser til: user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>SQL Server</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>teknisk</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>i bruk</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Knyttet til en bruker gjennom `user_id`, med når sesjonen ble opprettet (`created_at`) og når den utløper (`expires_at`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>koe.app_oauth_attempts</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Påbegynte innlogginger mot Catenda (OAuth). Lagrer SHA-256 av staten og av nettlesertokenet, returstien og når forsøket utløper, 600 sekunder etter opprettelsen. Svarer til `app_oauth_attempts` i PostgreSQL (B-19, #656). Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>`koe_api.opprett_innloggingsforsoek` oppretter, `koe_api.bruk_innloggingsforsoek` sletter raden når den brukes, og `koe_api.rydd_utloepte` sletter utløpte rader. Kalt fra `server/sesjon.ts`, av innloggingen og tilbakekallet i `server/innlogging.ts` (F0b-5a, #659).</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Nei, men raden hører til en innlogging hos Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Nøkler: primærnøkkel (state_hash). Ingen relasjoner til andre tabeller.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SQL Server</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>teknisk</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>i bruk</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>Ingen kjente; bare hasher og en returadresse.</t>
         </is>

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet` eller `koe_api.entra_identitet`, oppretter brukeren første gang en identitet sees. Tilbakekallet fra innloggingen kaller den fra `catendaIdentitet` i `server/innlogging.ts` (F0b-5a, #659) og `entraIdentitet` i `server/entra.ts` (S-1c del 1, #831).</t>
+          <t>`koe.resolve_identity`, kalt gjennom `koe_api.catenda_identitet`, oppretter brukeren første gang en Catenda-identitet sees. Tilbakekallet fra innloggingen kaller den fra `catendaIdentitet` i `server/innlogging.ts` (F0b-5a, #659). En Entra-identitet oppretter aldri en bruker ved innloggingen: driften registrerer den med `koe_drift.registrer_entra_identitet`, som ny bruker eller koblet til en eksisterende (S-1c del 1, #831). `koe_api.entra_identitet` oppdaterer navn og e-post ved innloggingen.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>`koe.resolve_identity`, sammen med brukeren, kalt gjennom `koe_api.catenda_identitet` fra tilbakekallet i `server/innlogging.ts` (F0b-5a, #659) og gjennom `koe_api.entra_identitet` fra tilbakekallet for Entra ID (S-1c del 1, #831).</t>
+          <t>`koe.resolve_identity`, sammen med brukeren, kalt gjennom `koe_api.catenda_identitet` fra tilbakekallet i `server/innlogging.ts` (F0b-5a, #659). En Entra-identitet registreres av driften med `koe_drift.registrer_entra_identitet` og slås bare opp av `koe_api.entra_identitet` ved innloggingen (S-1c del 1, #831).</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tenantene i Entra ID driften har godkjent for innloggingen (S-1c del 1, #831). `koe_api.entra_identitet` avviser en issuer for en tenant som ikke står her. Kjøretiden har ingen rett på tabellen.</t>
+          <t>Tenantene i Entra ID driften har godkjent for innloggingen (S-1c del 1, #831). `koe_api.entra_identitet` og `koe_drift.registrer_entra_identitet` avviser en tenant som ikke står her. Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">

--- a/docs/datamodell/tabellbeskrivelse.xlsx
+++ b/docs/datamodell/tabellbeskrivelse.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.bruker_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningshandling.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningspakke.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.godkjenner_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.lastet_opp_av (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_identities.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_absences.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_sessions.user_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.bruker_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningshandling.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningspakke.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.godkjenner_id (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.hr_kopi.bruker_id (fremmednøkkel, ON DELETE NO ACTION); koe.kvittering.aktor_id (uten fremmednøkkel); koe.notat.aktor_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.created_by (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.lastet_opp_av (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2157,12 +2157,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>koe.projects</t>
+          <t>koe.rolle</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md). `server/prosjekter.ts` leser prosjektene aktøren er aktivt medlem i med `koe_api.brukerens_prosjekter`, og ett av dem med `koe_api.prosjekt` (#660). Tabellen har ikke `settings` og `created_by` fra PostgreSQL.</t>
+          <t>Rollene byggherren gir fullmakt etter, med beløpsgrensen i kroner, globalt for byggherren (GFK-U6, GFK-U11; S-1c del 2, #831). Ingen grense er ubegrenset (GFK-U4). Rollen er en kode med a–z og `_`. Kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten; skriptet sier fra når `--organisasjon` er en annen (#836).</t>
+          <t>Driften, med `koe_drift.sett_rolle` og `koe_drift.fjern_rolle`.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Navnet oppgis av driften; i Python kan det hentes fra Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (rolle). Vises til fra: koe.hr_kopi.rolle (fremmednøkkel, ON DELETE NO ACTION); koe.stillingstittel.rolle (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>koe.app_project_memberships</t>
+          <t>koe.stillingstittel</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660). `koe_api.medlemmer`, også kalt derfra, leser de aktive medlemmene for en aktør med aktivt medlemskap (#820).</t>
+          <t>Hvilken stillingstittel (`jobTitle` i Graph) som gir hvilken rolle (S3 i #831). Tittelen må stemme tegn for tegn; nøkkelen er SHA-256 av tittelen, fordi `=` ser bort fra mellomrom til slutt. Kjøretiden leser titlene bare gjennom `koe_api.stillingstitler`.</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2229,22 +2229,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10). `koe_api.sett_leserolle`, kalt fra `server/prosjekter.ts`, setter `viewer_override` for et annet aktivt medlem når aktøren er aktiv admin uten leserolle (#820).</t>
+          <t>Driften, med `koe_drift.sett_stillingstittel` og `koe_drift.fjern_stillingstittel`. Lest av `koe_api.stillingstitler` og `koe_api.synkroniser_hr` fra `server/hrdata.ts`.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Delvis</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Ja, medlemslisten i Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (noekkel). Viser til: rolle → koe.rolle.rolle (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>grunndata, kopi</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2264,19 +2264,19 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>E-post og visningsnavn.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_contract_teams</t>
+          <t>koe.hr_kopi</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen. `server/autorisasjon.ts` leser prosjektets kontraktsteam med `koe_api.kontraktsteam`, bare for en aktør med aktivt medlemskap uten leserollen (#658).</t>
+          <t>HR-kopien per bruker fra Graph (S-1c del 2, #831): tenanten, `oid`, rollen, lederens `oid` og når bildet ble hentet. Hver synkronisering skriver hele bildet for tenanten; en person uten en stilling som gir rolle, eller med deaktivert konto, beholder raden uten rolle og leder (GFK-U10). Kjøretiden skriver bare gjennom `koe_api.synkroniser_hr` og har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2286,22 +2286,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764). Byttes Catenda-prosjektet, må teamene oppgis på nytt (#836).</t>
+          <t>`koe_api.synkroniser_hr`, kalt av jobbkjøreren gjennom `synkroniserHr` i `server/hrdata.ts`.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes av driften. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Fra Microsoft Graph. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.aktor_team_id (uten fremmednøkkel); koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (bruker_id); unik (tenant_id, oid). Viser til: bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); rolle → koe.rolle.rolle (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2311,29 +2311,29 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>kopi</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Ingen kjente.</t>
+          <t>Hvem som har en rolle med fullmakt, og hvem som er lederen.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>koe.catenda_project_configs</t>
+          <t>koe.projects</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). `koe_api.opprett_sak` låser raden før den leses, så en ny sak og en ny registrering eller nye kontraktsteam skrives etter hverandre (#868). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
+          <t>Prosjektene. `id` er prosjektgrensen i alle tabellene med saksdata, uten standardverdi (AGENTS.md). `server/prosjekter.ts` leser prosjektene aktøren er aktivt medlem i med `koe_api.brukerens_prosjekter`, og ett av dem med `koe_api.prosjekt` (#660). Tabellen har ikke `settings` og `created_by` fra PostgreSQL.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Mappen fjernes også når biblioteket er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
+          <t>Driften registrerer prosjektet med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt`; bare `koe_driftsrolle` kan kjøre den (F-1, #820). En ny registrering skriver over navnet og beskrivelsen og gjør prosjektet aktivt, men endrer ikke virksomheten; skriptet sier fra når `--organisasjon` er en annen (#836).</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Navnet oppgis av driften; i Python kan det hentes fra Catenda-prosjektet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id). Vises til fra: koe.app_membership_absences.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_membership_sync.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.app_project_memberships.project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_contract_teams.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.catenda_project_configs.internal_project_id (fremmednøkkel, ON DELETE NO ACTION); koe.dagmulktssats.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.fullmakt.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.prosjekt_med_saker.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION); koe.sak_metadata.prosjekt_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_absences</t>
+          <t>koe.app_project_memberships</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene der innloggingens liste over brukerens Catenda-prosjekter viste at brukeren ikke er med, for en bruker uten medlemskap der (DL-U9). `observed_at` er når innloggingens liste ble hentet, etter basens klokke. En medlemsliste hentet samtidig eller før gir ikke brukeren et nytt medlemskap. Har ingen tabell i PostgreSQL.</t>
+          <t>Medlemskapet i et prosjekt, fra Catenda. Leserollen er `viewer_override`, som i PostgreSQL. `server/autorisasjon.ts` leser aktørens aktive medlemskap med `koe_api.prosjektmedlemskap` (#658). `koe_api.brukerens_prosjekter` og `koe_api.prosjekt`, kalt fra `server/prosjekter.ts`, leser bare prosjekter der aktøren har et aktivt medlemskap (#660). `koe_api.medlemmer`, også kalt derfra, leser de aktive medlemmene for en aktør med aktivt medlemskap (#820).</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2400,22 +2400,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Innloggingen kaller modulen fra tilbakekallet i `server/innlogging.ts` (F0b-5b).</t>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, skriver medlemslisten fra Catenda og gjør medlemmer som ikke står i den, inaktive. `koe_api.deaktiver_ved_innlogging`, også kalt derfra, gjør brukerens medlemskap inaktivt i koblede prosjekter som ikke står i brukerens liste fra Catenda. `deactivated_at` er når medlemskapet sist ble gjort inaktivt, etter basens klokke; en liste hentet før det gjør det ikke aktivt igjen (DL-U8). For en bruker uten medlemskap fører innloggingen en rad i `koe.app_membership_absences`, og en liste hentet før den gir ikke et nytt medlemskap (DL-U9). Tilgangskontrollen i `server/autorisasjon.ts` og tilbakekallet i `server/innlogging.ts` kaller modulen (F0b-5b). Blir koblingen opphevet, slettet eller endret, gjør triggeren `koe.catenda_project_configs_kobling_endret` alle medlemskapene i prosjektet inaktive med `deactivated_at` satt til tidspunktet for endringen (DL-U10). `koe_api.sett_leserolle`, kalt fra `server/prosjekter.ts`, setter `viewer_override` for et annet aktivt medlem når aktøren er aktiv admin uten leserolle (#820).</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Delvis</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Ja, medlemslisten i Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id, user_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id); unik (project_id, catenda_subject). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>grunndata, kopi</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2435,19 +2435,19 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Knyttet til en bruker gjennom `user_id`, med prosjektene brukeren ikke er med i og tidspunktene for innloggingene (`observed_at`, `updated_at`).</t>
+          <t>E-post og visningsnavn.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>koe.app_membership_sync</t>
+          <t>koe.catenda_contract_teams</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden ingen Catenda-ID (NULL) og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10, #726). Den tomme Catenda-ID-en er ikke lov.</t>
+          <t>Kontraktssiden (TE eller BH) for hvert Catenda-team i et prosjekt. Teamet har `catenda_id()`-formen, som `aktor_team_id` i journalen. `server/autorisasjon.ts` leser prosjektets kontraktsteam med `koe_api.kontraktsteam`, bare for en aktør med aktivt medlemskap uten leserollen (#658).</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, og triggeren `koe.catenda_project_configs_kobling_endret` når koblingen endres.</t>
+          <t>Driften setter teamene med skriptet `server/registrering.ts`, som kontrollerer dem mot Catenda-prosjektet og kaller `koe_drift.sett_kontraktsteam`, direkte eller gjennom `koe_drift.registrer_prosjekt` (F-1, #820). Begge sider må ha minst ett team. Uten saker erstatter listen teamene; står prosjektet i `koe.prosjekt_med_saker`, kan de bare få nye team (svaret 18.10 i #764). Byttes Catenda-prosjektet, må teamene oppgis på nytt (#836).</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Team-ID-en kommer fra Catenda; kontraktssiden settes av driften. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id, team_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.aktor_team_id (uten fremmednøkkel); koe.hendelse.aktor_team_id (uten fremmednøkkel); koe.notat.aktor_team_id (uten fremmednøkkel); koe.vedlegg.lastet_opp_team (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2499,37 +2499,37 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_metadata</t>
+          <t>koe.catenda_project_configs</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
+          <t>Koblingen mellom prosjektet i appen og Catenda-prosjektet, og om den er aktiv (arbeidsvalget 16.10 i #53). Svarer til `catenda_project_configs` i PostgreSQL, uten mappene for webhooken. Synkroniseringen avviser en liste fra et annet Catenda-prosjekt. `server/medlemskap.ts` leser en aktiv kobling med `koe_api.prosjektkobling` (#658, #638), og `koe_api.koblede_prosjekter` gir prosjektene koblet til brukerens Catenda-prosjekter ved innlogging. `koe_api.brukerens_prosjekter`, kalt fra `server/prosjekter.ts`, tar bare med prosjekter med aktiv kobling (#660). Triggeren `koe.catenda_project_configs_kobling_endret` gjør medlemskapene inaktive når koblingen oppheves, slettes eller endres (DL-U10), og setter Catenda-ID-en i synkroniseringsraden til NULL. Den tomme Catenda-ID-en er ikke lov. `topic_board_id` er boardet for saker som opprettes i appen (KT-U4); uten det avviser `koe_api.opprett_sak` saken (#741). `koe_api.opprett_sak` låser raden før den leses, så en ny sak og en ny registrering eller nye kontraktsteam skrives etter hverandre (#868). Triggeren `koe.catenda_project_configs_endret` setter `updated_at` ved hver endring (#618).</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Driften registrerer koblingen med skriptet `server/registrering.ts`, som kaller `koe_drift.registrer_prosjekt` (F-1, #820). En ny registrering skriver over Catenda-prosjektet og biblioteket og gjør koblingen aktiv. Mappen og boardet skrives over når de er oppgitt. Ellers står de hvis Catenda-prosjektet er det samme, og fjernes hvis det er byttet. Mappen fjernes også når biblioteket er byttet. Har prosjektet saker, avvises bytte av Catenda-prosjekt, og uten saker krever et bytte nye kontraktsteam (#836).</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370), og som `server/hendelser.ts` kaller for en ny topic fra TE i innboksen (KT-U6, #819).</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Saken kan være opprettet fra en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_behandling.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (internal_project_id); unik (catenda_project_id). Viser til: internal_project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2539,54 +2539,54 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>`created_by` peker på en bruker.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>koe.hendelse</t>
+          <t>koe.app_membership_absences</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
+          <t>Prosjektene der innloggingens liste over brukerens Catenda-prosjekter viste at brukeren ikke er med, for en bruker uten medlemskap der (DL-U9). `observed_at` er når innloggingens liste ble hentet, etter basens klokke. En medlemsliste hentet samtidig eller før gir ikke brukeren et nytt medlemskap. Har ingen tabell i PostgreSQL.</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.deaktiver_ved_innlogging`, kalt fra `server/medlemskap.ts`, setter inn raden eller flytter `observed_at` fram. `koe_api.synkroniser_medlemskap` sletter radene i prosjektet med `observed_at` før listen den skriver. Innloggingen kaller modulen fra tilbakekallet i `server/innlogging.ts` (F0b-5b).</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661), og `koe_api.opprett_sak` fra `POST /api/kjerne/saker` (#370).</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Delvis. Sakstittelen i `sak_opprettet` kan være tittelen på en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel); koe.vedlegg.(bundet_av_event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (project_id, user_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); user_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2606,44 +2606,44 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
+          <t>Knyttet til en bruker gjennom `user_id`, med prosjektene brukeren ikke er med i og tidspunktene for innloggingene (`observed_at`, `updated_at`).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>koe.notat</t>
+          <t>koe.app_membership_sync</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
+          <t>Når medlemslisten for prosjektet sist ble hentet, og fra hvilket Catenda-prosjekt (DL-U7). En eldre liste skriver ikke over en nyere. Alderen leses av `koe_api.medlemsliste_alder` (B-04 punkt 4), kalt fra `server/autorisasjon.ts` etter at koblingen er kontrollert (#638 punkt 2), også gjennom `ferskeMedlemmer` for hvert prosjekt i lista i `server/prosjekter.ts` (#660). Svarer til `app_membership_sync` i PostgreSQL. Etter at koblingen er opphevet, slettet eller endret, har raden ingen Catenda-ID (NULL) og tidspunktet for endringen, så ingen liste fra det koblede prosjektet finnes, og en liste hentet før endringen ikke skrives (DL-U10, #726). Den tomme Catenda-ID-en er ikke lov.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.synkroniser_medlemskap`, kalt fra `server/medlemskap.ts`, og triggeren `koe.catenda_project_configs_kobling_endret` når koblingen endres.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Ingen skriver ennå (#53, del 3).</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Tidspunktet er når hentingen fra Catenda begynte. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (project_id). Viser til: project_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2653,54 +2653,54 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
+          <t>Ingen kjente.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>koe.jobb</t>
+          <t>koe.sak_metadata</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). En sak fra en topic i innboksen får ingen jobb; den kobles til topicen (W-1b.1, #819). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
+          <t>Saksregisteret: saken, prosjektet og sakstypen. En trigger avviser endring og sletting.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sak`, sammen med `sak_opprettet`, kalt fra `opprettSak` i `server/kommandoer.ts`, som `POST /api/kjerne/saker` kaller (#370), og som `server/hendelser.ts` kaller for en ny topic fra TE i innboksen (KT-U6, #819).</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.opprett_sak` og triggeren `koe.leveringsoppdrag_levering`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.kvitter_levering`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Saken kan være opprettet fra en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (sak_id, prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); created_by → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningspakke.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.hendelse.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_behandling.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.kjernebuffer.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.sak_catenda_topic.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedlegg.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2720,44 +2720,44 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Sakstittelen kan inneholde personopplysninger.</t>
+          <t>`created_by` peker på en bruker.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>koe.jobbforsoek</t>
+          <t>koe.hendelse</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med SID-en til innloggingen som startet jobben på nytt (`sid:0x…`, eller `driften uten SID`). Raden endres ikke.</t>
+          <t>Journalen: ett dokument per brev, med teksten slik den ble sendt. En trigger avviser endring og sletting. Teamet står bare når det er entydig (DL-U4).</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.opprett_sak` skriver `sak_opprettet` og `koe_api.skriv_hendelse` de andre brevene, kalt fra `server/kommandoer.ts`. `koe_api.skriv_hendelse` kalles fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661), og `koe_api.opprett_sak` fra `POST /api/kjerne/saker` (#370).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Prosedyrene for jobbkjøreren i `database/migrasjoner/20261018100000_jobber.sql`, og driftsverktøyet `koe_api.start_jobb_paa_nytt`, sist definert i `20261020121000_oppretter_tid_og_oppdragsnoekkel.sql`.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Nei. Meldingen er fra klienten i `server/catenda.ts`, uten svarkropp. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. Sakstittelen i `sak_opprettet` kan være tittelen på en topic i Catenda (KT-U6, C22). Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel); koe.vedleggskvittering.forsoek_id (uten fremmednøkkel).</t>
+          <t>Nøkler: primærnøkkel (event_id); unik (event_id, sak_id, prosjekt_id); unik (sak_id, versjon). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel). Vises til fra: koe.kvittering.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringsoppdrag.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.notat.refererer_til_event_id (uten fremmednøkkel); koe.vedlegg.(bundet_av_event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2777,19 +2777,19 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Innloggingen til den i driften som startet en jobb på nytt.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `data` kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringsoppdrag</t>
+          <t>koe.notat</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
+          <t>Interne notater, skjermet på teamet (AGENTS.md). Ikke et kontraktsvarsel, og kan endres og slettes (MS-05).</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
+          <t>Ingen skriver ennå (#53, del 3).</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id); unik (id, prosjekt_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (notat_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel); refererer_til_event_id → koe.hendelse.event_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2829,34 +2829,34 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
+          <t>`aktor_id` peker på en bruker. Fritekst i `tekst` og `kommentar`.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>koe.kvittering</t>
+          <t>koe.jobb</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen per kommando (invariant 4, #418): kommando-ID-en klienten gir, summen av innholdet serveren regner ut, og saken og brevet kommandoen ga. Lagres i samme transaksjon som brevet. Nøkkelen er prosjektet, aktøren og kommando-ID-en, så kvitteringen gjelder aktøren. Samme ID med samme sum gir brevet fra kvitteringen, og samme ID med en annen sum avvises (51410).</t>
+          <t>Jobbene jobbkjøreren gjør etter commit (B-07, arbeidsvalget 18.10 i #741). En sak fra appen får jobben `catenda_topic` i samme transaksjon, med boardet, Catenda-prosjektet og sakstittelen frosset (KT-U3, invariant 6). En sak fra en topic i innboksen får ingen jobb; den kobles til topicen (W-1b.1, #819). Et brev med tekst fra appen får jobben `levering` for leveringsoppdraget, lagt inn av triggeren `koe.leveringsoppdrag_levering` (#371). Jobben har en lease mens den gjøres, og tilstanden `venter`, `utfoert` eller `parkert`. Bare kjøreveien, `koe_jobbkjoerer`, ser og endrer jobbene; kjøretiden har ingen rett på tabellen.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.skriv_hendelse` og `koe_api.opprett_sak`, og leses av `koe_api.kvittering`, kalt fra `skrivHendelse` og `opprettSak` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker` og `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer`.</t>
+          <t>`koe_api.opprett_sak` og triggeren `koe.leveringsoppdrag_levering`, og endres av `koe_api.hent_jobb`, `koe_api.kvitter_topic`, `koe_api.kvitter_levering`, `koe_api.registrer_jobbfeil` og driftsverktøyet `koe_api.start_jobb_paa_nytt`.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Delvis. ID-ene til Catenda-prosjektet og boardet. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (jobb_id); unik indeks (lease) WHERE ([lease] IS NOT NULL); unik indeks (leveringsoppdrag_id) WHERE ([leveringsoppdrag_id] IS NOT NULL); unik indeks (sak_id) WHERE ([jobbtype]=N'catenda_topic'). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); siste_forsoek → koe.jobbforsoek.forsoek_id (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.jobbforsoek.jobb_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -2891,29 +2891,29 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Aktørens `app_users.id`.</t>
+          <t>Sakstittelen kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>koe.brevdokument</t>
+          <t>koe.jobbforsoek</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PDF-en av brevet i et leveringsoppdrag (#371 del 2, merknaden 12.10): bytene og SHA-256 av dem, lagret én gang per oppdrag før første opplasting. Kjøreren har kontrollert at PDF-en gjengir den frosne brevteksten tro (LV-U2), og laster opp den lagrede. Basen regner summen etter. Raden endres ikke, og bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en.</t>
+          <t>Hvert forsøk, hver feil, hver kvittering og hver omstart av en jobb for seg (LV-U1, invariant 7 og 8). Forsøket har leasens ID og lagres når utfallet er kjent: `utfoert`, `feilet`, `usikkert`, `avvist`, `kobling_endret` eller `startet_paa_nytt`, med SID-en til innloggingen som startet jobben på nytt (`sid:0x…`, eller `driften uten SID`). Raden endres ikke.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nei</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` med PDF-en når samme prosedyre uten PDF ikke gir noen lagret for oppdraget (#795 punkt 4, #805 punkt 5).</t>
+          <t>Prosedyrene for jobbkjøreren i `database/migrasjoner/20261018100000_jobber.sql`, og driftsverktøyet `koe_api.start_jobb_paa_nytt`, sist definert i `20261020121000_oppretter_tid_og_oppdragsnoekkel.sql`.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Meldingen er fra klienten i `server/catenda.ts`, uten svarkropp. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (forsoek_id). Viser til: jobb_id → koe.jobb.jobb_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.forsoek_id (uten fremmednøkkel); koe.jobb.siste_forsoek (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.forsoek_id (uten fremmednøkkel); koe.vedleggskvittering.forsoek_id (uten fremmednøkkel).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>teknisk</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2948,19 +2948,19 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Brevteksten kan ha navn på personer i prosjektet.</t>
+          <t>Innloggingen til den i driften som startet en jobb på nytt.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>koe.vedlegg</t>
+          <t>koe.leveringsoppdrag</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2). Når Catenda har kvittert for dokumentet, setter `koe_api.kvitter_vedlegg` innholdet til NULL og beholder filnavnet og summen (LV-U12, V-3). Triggeren `koe.vedlegg_uten_endring` slipper bare gjennom de to endringene.</t>
+          <t>Leveringsoppdraget for et brev (LV-U1, B-03), frosset i samme transaksjon som brevet. Den sammensatte fremmednøkkelen holder det i brevets sak og prosjekt.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`, og `koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.skriv_hendelse`, med brevet `dokument_registrert` i samme transaksjon, kalt fra `skrivHendelse` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer` (#661).</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei, men oppdraget gjelder en levering til Catenda. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik (dokumentnoekkel); unik (event_id); unik (id, prosjekt_id). Viser til: (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.brevdokument.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.jobb.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.leveringskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.(leveringsoppdrag_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3005,36 +3005,36 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Filen og filnavnet kan ha navn på personer i prosjektet.</t>
+          <t>Innholdet er brevet og kan inneholde personopplysninger.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>koe.fullmakt</t>
+          <t>koe.kvittering</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (GFK-U1). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
+          <t>Kvitteringen per kommando (invariant 4, #418): kommando-ID-en klienten gir, summen av innholdet serveren regner ut, og saken og brevet kommandoen ga. Lagres i samme transaksjon som brevet. Nøkkelen er prosjektet, aktøren og kommando-ID-en, så kvitteringen gjelder aktøren. Samme ID med samme sum gir brevet fra kvitteringen, og samme ID med en annen sum avvises (51410).</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.skriv_hendelse` og `koe_api.opprett_sak`, og leses av `koe_api.kvittering`, kalt fra `skrivHendelse` og `opprettSak` i `server/kommandoer.ts`, fra `POST /api/kjerne/saker` og `POST /api/kjerne/saker/&lt;sak_id&gt;/kommandoer`.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id, bruker_id); unik (prosjekt_id, plass). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, aktor_id, kommando_id); unik (event_id). Viser til: aktor_id → koe.app_users.id (uten fremmednøkkel); (event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(kvittering_prosjekt_id, kvittering_aktor_id, kvittering_kommando_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3062,36 +3062,36 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Hvem som har fullmakt, med tittel og beløpsgrense.</t>
+          <t>Aktørens `app_users.id`.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>koe.dagmulktssats</t>
+          <t>koe.brevdokument</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Dagmulktssatsen i prosjektet, som fristdagene verdsettes med i fullmakten (GFK-06). Uten rad mangler satsen, og fristdagene kan ikke verdsettes (B-06). Driften setter den opp som fullmaktene.</t>
+          <t>PDF-en av brevet i et leveringsoppdrag (#371 del 2, merknaden 12.10): bytene og SHA-256 av dem, lagret én gang per oppdrag før første opplasting. Kjøreren har kontrollert at PDF-en gjengir den frosne brevteksten tro (LV-U2), og laster opp den lagrede. Basen regner summen etter. Raden endres ikke, og bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.lagre_brevdokument`, kalt av jobbkjøreren i `server/jobber.ts` med PDF-en når samme prosedyre uten PDF ikke gir noen lagret for oppdraget (#795 punkt 4, #805 punkt 5).</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.brevdokument_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3119,19 +3119,19 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Ingen.</t>
+          <t>Brevteksten kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningspakke</t>
+          <t>koe.vedlegg</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Et svar fra byggherren til intern godkjenning (S-1a, #818): brevet, grunnlaget fullmakten ble regnet av, saksbehandleren og teamet. Pakken er et utkast som bare teamet som laget den, ser, og uten team finnes den ikke (AGENTS.md). Den endres ikke; en ny pakke kan erstatte en returnert eller trukket.</t>
+          <t>Mellomlageret for vedlegg (V-1, del av #790): filen, filnavnet, størrelsen og SHA-256 av bytene, som basen regner etter. Filen ligger her til Catenda har kvittert for den (spørsmål 1 A i #790, 18.10). Et ubundet vedlegg er et utkast som bare teamet som lastet det opp, ser og sletter. Når en hendelse viser til det, får det `bundet_av_event_id` og ses av begge kontraktssider; et bundet vedlegg slettes ikke. `koe_api.bind_vedlegg` binder vedleggene hendelsen viser til, i samme transaksjon som hendelsen (V-2). Når Catenda har kvittert for dokumentet, setter `koe_api.kvitter_vedlegg` innholdet til NULL og beholder filnavnet og summen (LV-U12, V-3). Triggeren `koe.vedlegg_uten_endring` slipper bare gjennom de to endringene.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
+          <t>`koe_api.lagre_vedlegg` og `koe_api.slett_vedlegg`, kalt fra `server/vedlegg.ts`, `koe_api.bind_vedlegg`, kalt fra `server/kommandoer.ts`, og `koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id); unik indeks (forrige_pakke_id) WHERE ([forrige_pakke_id] IS NOT NULL). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_av → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); (bundet_av_event_id, sak_id, prosjekt_id) → koe.hendelse.(event_id, sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); lastet_opp_team → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); koe.vedleggskvittering.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3176,36 +3176,36 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Saksbehandleren (`aktor_id`) og innholdet i svaret.</t>
+          <t>Filen og filnavnet kan ha navn på personer i prosjektet.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningssteg</t>
+          <t>koe.fullmakt</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Godkjennerne i en pakke i kjedens rekkefølge, regnet av `server/fullmakt.ts` da pakken ble laget. Endres ikke.</t>
+          <t>Byggherrens fullmakter i prosjektet (S-1a, #818): personen, tittelen, grensen i kroner (ingen grense er ubegrenset) og plassen i godkjenningskjeden. Driften setter dem opp etter skriftlig bestilling fra byggherren, og appen viser ikke hvem som har endret dem (GFK-U1). Kjøretiden leser dem bare gjennom `koe_api.fullmakter`, som byggherren.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id, steg); unik (pakke_id, godkjenner_id). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); godkjenner_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningshandling.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id, bruker_id); unik (prosjekt_id, plass). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION); bruker_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3233,36 +3233,36 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Godkjennerne (`godkjenner_id`).</t>
+          <t>Hvem som har fullmakt, med tittel og beløpsgrense.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>koe.godkjenningshandling</t>
+          <t>koe.dagmulktssats</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Hver godkjenning, retur og trekking av en pakke, i rekkefølge. En godkjenning fryser tittelen og grensen godkjenneren hadde da den ble gitt, så den står om fullmakten endres senere (B-04 punkt 2). Endres ikke.</t>
+          <t>Dagmulktssatsen i prosjektet, som fristdagene verdsettes med i fullmakten (GFK-06). Uten rad mangler satsen, og fristdagene kan ikke verdsettes (B-06). Driften setter den opp som fullmaktene.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>Nei</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Driften, som eier. Lest av `koe_api.fullmakter` fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.registrer_godkjenningshandling`, kalt fra `server/godkjenning.ts`.</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(godkjenningshandling_pakke_id, godkjenningshandling_loepenr) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (prosjekt_id). Viser til: prosjekt_id → koe.projects.id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>transaksjon</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3290,19 +3290,19 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Den som handlet (`aktor_id`) og begrunnelsen for en retur.</t>
+          <t>Ingen.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>koe.leveringskvittering</t>
+          <t>koe.godkjenningspakke</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Et registrert brev har ingen rader (LV-U11); vedleggene kvitteres i `koe.vedleggskvittering`. Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
+          <t>Et svar fra byggherren til intern godkjenning (S-1a, #818): brevet, grunnlaget fullmakten ble regnet av, saksbehandleren og teamet. Pakken er et utkast som bare teamet som laget den, ser, og uten team finnes den ikke (AGENTS.md). Den endres ikke; en ny pakke kan erstatte en returnert eller trukket.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id); unik (pakke_id, prosjekt_id, aktor_team_id); unik indeks (forrige_pakke_id) WHERE ([forrige_pakke_id] IS NOT NULL). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forrige_pakke_id → koe.godkjenningspakke.pakke_id (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION); aktor_team_id → koe.catenda_contract_teams.team_id (uten fremmednøkkel). Vises til fra: koe.godkjenningshandling.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); koe.godkjenningssteg.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3347,19 +3347,19 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Saksbehandleren (`aktor_id`) og innholdet i svaret.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>koe.vedleggskvittering</t>
+          <t>koe.godkjenningssteg</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for hver operasjon i leveringen av et vedlegg (V-3, del av #790, invariant 7): `dokument` når vedlegget ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Kvitteringen gjelder vedlegget, ikke oppdraget, så et vedlegg et senere brev viser til igjen, leveres ikke på nytt. Raden har leasen, oppdraget som leverte og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. `koe_api.kvitter_levering` kvitterer leveringen som fullført først når hvert vedlegg i brevet har en referanse.</t>
+          <t>Godkjennerne i en pakke i kjedens rekkefølge, regnet av `server/fullmakt.ts` da pakken ble laget. Endres ikke.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+          <t>`koe_api.lag_godkjenningspakke`, kalt fra `server/godkjenning.ts`.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, steg); unik (pakke_id, godkjenner_id). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); godkjenner_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.godkjenningshandling.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3404,44 +3404,44 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Godkjennerne (`godkjenner_id`).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>koe.sak_catenda_topic</t>
+          <t>koe.godkjenningshandling</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). En sak fra en topic i Catenda kobles til topicen i transaksjonen som oppretter saken (W-1b.1, #819). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
+          <t>Hver godkjenning, retur og trekking av en pakke, i rekkefølge. En godkjenning fryser tittelen og grensen godkjenneren hadde da den ble gitt, så den står om fullmakten endres senere (B-04 punkt 2). Endres ikke.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.registrer_godkjenningshandling`, kalt fra `server/godkjenning.ts`.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741), og `koe_api.koble_topic`, kalt bare fra `koe_api.opprett_sak` når saken opprettes fra en topic i innboksen (W-1b.1, #819).</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-ene er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
+          <t>Nei. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.sak_catenda_topic_sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (pakke_id, loepenr); unik indeks (pakke_id) WHERE ([handling]&lt;&gt;N'godkjent'); unik indeks (pakke_id, steg) WHERE ([handling]=N'godkjent'). Viser til: (pakke_id, prosjekt_id, aktor_team_id) → koe.godkjenningspakke.(pakke_id, prosjekt_id, aktor_team_id) (fremmednøkkel, ON DELETE NO ACTION); (pakke_id, steg) → koe.godkjenningssteg.(pakke_id, steg) (fremmednøkkel, ON DELETE NO ACTION); aktor_id → koe.app_users.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.(godkjenningshandling_pakke_id, godkjenningshandling_loepenr) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3451,54 +3451,54 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>grunndata</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>uavklart</t>
+          <t>i bruk</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Den som handlet (`aktor_id`) og begrunnelsen for en retur.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_hendelse</t>
+          <t>koe.leveringskvittering</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Hendelsene behandles av `server/hendelser.ts`, og utfallet står i `koe.innkommende_behandling` (W-1b.1).</t>
+          <t>Kvitteringen for hver obligatoriske operasjon i leveringen av et brev (#371 del 1, invariant 7): `dokument` når dokumentet ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Brevet er levert når begge radene finnes (B-03, arbeidsvalget 18.10 i #371). Et registrert brev har ingen rader (LV-U11); vedleggene kvitteres i `koe.vedleggskvittering`. Raden har leasen og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. Kjøretiden leser tidspunktet for `dokumentreferanse` som «levert» i visningen av saken (`lesOppdrag` i `server/lager.ts`, #764).</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_dokument` og `koe_api.kvitter_levering`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.motta_hendelse`, kalt av webhooken i `server/webhook.ts`.</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Ja, hele kroppen er Catendas. Dataflyt: fra Catenda i C21 (arket Dataflyt).</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_forsoek.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (leveringsoppdrag_id, operasjon). Viser til: (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, forutsetning) → koe.leveringskvittering.(leveringsoppdrag_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(leveringskvittering_oppdrag_id, leveringskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3518,44 +3518,44 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Ja: kroppen har navnet og e-postadressen til den som laget topicen i Catenda.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_behandling</t>
+          <t>koe.vedleggskvittering</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Boardet topicen ble slått opp på, står med utfallet, så kommentaren skrives på samme board. Raden kan ikke endres eller slettes; kommentaren tilbake til topicen (W-1b.2) står i `koe.topic_kommentar` og endrer ikke utfallet.</t>
+          <t>Kvitteringen for hver operasjon i leveringen av et vedlegg (V-3, del av #790, invariant 7): `dokument` når vedlegget ligger i biblioteket, og `dokumentreferanse` når referansen står på topicen. Kvitteringen gjelder vedlegget, ikke oppdraget, så et vedlegg et senere brev viser til igjen, leveres ikke på nytt. Raden har leasen, oppdraget som leverte og ID-en Catenda ga, og endres ikke. Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad. `koe_api.kvitter_levering` kvitterer leveringen som fullført først når hvert vedlegg i brevet har en referanse.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>`koe_api.kvitter_vedlegg`, kalt av jobbkjøreren i `server/jobber.ts`.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>`koe_api.registrer_behandling`, kalt av `behandleEnHendelse` i `server/jobber.ts` med utfallet fra `server/hendelser.ts`.</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Nei</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Delvis. ID-en til topicen er Catendas. Dataflyt: fra Catenda i C22; til Catenda i C23 (arket Dataflyt).</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: ingen kall til Catenda skriver eller leser tabellen.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION); (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_behandling_id (fremmednøkkel, ON DELETE NO ACTION); koe.topic_kommentar.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (vedlegg_id, operasjon). Viser til: vedlegg_id → koe.vedlegg.vedlegg_id (fremmednøkkel, ON DELETE NO ACTION); (vedlegg_id, forutsetning) → koe.vedleggskvittering.(vedlegg_id, operasjon) (fremmednøkkel, ON DELETE NO ACTION); (leveringsoppdrag_id, prosjekt_id) → koe.leveringsoppdrag.(id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION); forsoek_id → koe.jobbforsoek.forsoek_id (uten fremmednøkkel). Vises til fra: koe.toemmingsvern.(vedleggskvittering_vedlegg_id, vedleggskvittering_operasjon) (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>transaksjon</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3575,19 +3575,19 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Nei. `melding` er en fast feiltekst fra serveren.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>koe.innkommende_forsoek</t>
+          <t>koe.sak_catenda_topic</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Forsøkene uten utfall for en hendelse i innboksen (W-1b.2, #819), med steget: `behandling` eller `kommentar`. Et forsøk lagres når Catenda eller basen ikke svarte. Hendelsen venter da før neste forsøk, lenger for hvert forsøk (30 s, dobbelt for hvert, høyst en time), og løkka går videre, så én hendelse ikke stenger innboksen (#963). `topic_ikke_funnet` merker forsøkene der Catenda ikke fant topicen; bare de teller mot grensen for `ugyldig_hendelse`. `koe_api.neste_innkommende` og `koe_api.neste_kommentar` hopper over en hendelse som venter. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_innkommende_forsoek`. Raden kan ikke endres eller slettes.</t>
+          <t>Sakens topic i Catenda, med boardet. Én rad per sak, som bare kan legges til: topicen lages etter at saken er lagret, og saksraden er uforanderlig. `koe_api.leveringsmaal` leser den, og leveringsoppdraget fryser topicen, eller null uten rad (F0b-7, #661). Samme topic hører ikke til to saker (#741 punkt 17). En sak fra en topic i Catenda kobles til topicen i transaksjonen som oppretter saken (W-1b.1, #819). Bare kjøreveien, `koe_jobbkjoerer`, kan legge inn en rad.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3597,22 +3597,22 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.registrer_innkommende_forsoek`, kalt av `behandleEnHendelse` og `skrivEnKommentar` i `server/jobber.ts`.</t>
+          <t>`koe_api.kvitter_topic`, kalt av jobbkjøreren i `server/jobber.ts` etter at topicen er laget i Catenda (#741), og `koe_api.koble_topic`, kalt bare fra `koe_api.opprett_sak` når saken opprettes fra en topic i innboksen (W-1b.1, #819).</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Nei</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Delvis. `melding` kan være feilmeldingen fra Catenda. Dataflyt: fra Catenda i C22, C23 (arket Dataflyt).</t>
+          <t>Ja, ID-ene er Catendas. Dataflyt: fra Catenda i C22 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (id). Viser til: innkommende_hendelse_id → koe.innkommende_hendelse.id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.innkommende_forsoek_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (sak_id); unik (catenda_topic_id). Viser til: (sak_id, prosjekt_id) → koe.sak_metadata.(sak_id, prosjekt_id) (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.sak_catenda_topic_sak_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3622,29 +3622,29 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>teknisk</t>
+          <t>grunndata</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>i bruk</t>
+          <t>uavklart</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Nei. `melding` er feilklassen og meldingen fra Catenda eller basen, uten saksdata.</t>
+          <t>Nei.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>koe.topic_kommentar</t>
+          <t>koe.innkommende_hendelse</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Kvitteringen for kommentaren løkka skrev tilbake på topicen i Catenda (W-1b.2, #819), én rad per utfall. Utfallet `sak_opprettet` gir en kommentar med lenke og saksnummer (KT-U6), `topic_fra_bh` (KT-U7) og `sakstype_ikke_stoettet` (arbeidsvalget under OV-U1 i #819) en kommentar om hvorfor ingen sak er opprettet. Kommentarene på topicen leses først, og står teksten der alt, kvitteres den, så samme tekst skrives én gang. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.kvitter_kommentar`. Raden kan ikke endres eller slettes.</t>
+          <t>Innboksen for webhooken fra Catenda (W-1a, #819). Hver hendelse lagres rå, med kilden, `event.id` og `event.type`, før svaret 200, og samme ID fra samme kilde lagres én gang (INT-02). Prosjektet og saken er ikke avgjort ved mottaket, så tabellen har ingen `prosjekt_id` og ingen radsikkerhet; kjøretiden har ingen rett på den og skriver med `koe_api.motta_hendelse`. Raden kan ikke endres eller slettes. Hendelsene behandles av `server/hendelser.ts`, og utfallet står i `koe.innkommende_behandling` (W-1b.1).</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>`koe_api.kvitter_kommentar`, kalt av `skrivEnKommentar` i `server/jobber.ts` etter at kommentaren er funnet eller skrevet i Catenda.</t>
+          <t>`koe_api.motta_hendelse`, kalt av webhooken i `server/webhook.ts`.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Ja, ID-en til kommentaren er Catendas. Dataflyt: fra Catenda i C23 (arket Dataflyt).</t>
+          <t>Ja, hele kroppen er Catendas. Dataflyt: fra Catenda i C21 (arket Dataflyt).</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Nøkler: primærnøkkel (innkommende_hendelse_id). Viser til: innkommende_hendelse_id → koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION). Vises til fra: koe.toemmingsvern.topic_kommentar_id (fremmednøkkel, ON DELETE NO ACTION).</t>
+          <t>Nøkler: primærnøkkel (id); unik indeks (kilde, hendelse_id). Vises til fra: koe.innkommende_behandling.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.innkommende_forsoek.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION); koe.toemmingsvern.innkommende_hendelse_id (fremmednøkkel, ON DELETE NO ACTION).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3689,19 +3689,19 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Nei.</t>
+          <t>Ja: kroppen har navnet og e-postadressen til den som laget topicen i Catenda.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>koe.prosjekt_med_saker</t>
+          <t>koe.innkommende_behandling</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Prosjektene som har minst én sak. Radsikkerheten skjuler sakene også for eieren, så `koe_drift.sett_kontraktsteam` leser her om kontraktsteamene bare kan få nye team (svaret 18.10 i #764, F-1, #820). Raden kan ikke endres eller slettes. Hadde `koe.sak_metadata` rader da migrasjonen ble anvendt, ble hvert prosjekt ført, fordi sakene ikke kunne leses.</t>
+          <t>Utfallet for hver hendelse i innboksen, én rad når behandlingen er ferdig (W-1b.1, #819). En hendelse uten rad er ikke behandlet. Bare en ny topic laget av TE gir en sak, med topicens tittel (KT-U6); en topic fra BH gir ingen sak (KT-U7), og heller ikke en topic som alt hører til en sak eller er laget av integrasjonen (#741 punkt 17). Saken og prosjektet står bare når utfallet er `sak_opprettet`, og prosjektet når koblingen til Catenda-prosjektet og boardet ga det. Kjøretiden har ingen rett på tabellen og skriver med `koe_api.registrer_behandling`. Boardet topicen ble slått opp på, står med utfallet, så kommentaren skrives på samme board. Raden kan ikke endres eller slettes; kommentaren tilbake til topicen (W-1b.2) står i `koe.topic_kommentar` og endrer ikke utfallet.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Triggeren `koe.sak_metadata_prosjekt_med_saker`, i samme transaksjon som den første saken i prosjektet.</t>
+          <t>`koe_api.registrer_behandling`, kalt av `behandleEnHendelse` i `server/jobber.ts` med utfallet fra `server/hendels